--- a/서버정보/20260617_리소스배포_운영.xlsx
+++ b/서버정보/20260617_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2E7D4B-0C10-4E74-860E-DFE10EE0E2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A499EABF-7A6A-4C9D-A29E-48C2FDA69B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7390" uniqueCount="1111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7361" uniqueCount="1111">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -6211,7 +6211,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6555,6 +6555,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -11675,6 +11678,7 @@
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A48" s="90"/>
       <c r="B48" s="74" t="s">
         <v>23</v>
       </c>
@@ -11735,7 +11739,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A49" s="90"/>
       <c r="B49" s="74" t="s">
         <v>23</v>
       </c>
@@ -11796,7 +11801,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A50" s="90"/>
       <c r="B50" s="74" t="s">
         <v>23</v>
       </c>
@@ -11857,7 +11863,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A51" s="90"/>
       <c r="B51" s="82" t="s">
         <v>23</v>
       </c>
@@ -11918,7 +11925,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A52" s="90"/>
       <c r="B52" s="82" t="s">
         <v>23</v>
       </c>
@@ -11979,7 +11987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B53" s="102" t="s">
         <v>1083</v>
       </c>
@@ -12037,7 +12045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B54" s="102" t="s">
         <v>1083</v>
       </c>
@@ -12095,7 +12103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B55" s="102" t="s">
         <v>1083</v>
       </c>
@@ -12153,7 +12161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B56" s="102" t="s">
         <v>1083</v>
       </c>
@@ -12211,7 +12219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B57" s="102" t="s">
         <v>1083</v>
       </c>
@@ -12269,7 +12277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B58" s="102" t="s">
         <v>1083</v>
       </c>
@@ -12327,7 +12335,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A59" s="90"/>
       <c r="B59" s="74" t="s">
         <v>23</v>
       </c>
@@ -12388,7 +12397,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A60" s="90"/>
       <c r="B60" s="74" t="s">
         <v>23</v>
       </c>
@@ -12449,7 +12459,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A61" s="90"/>
       <c r="B61" s="82" t="s">
         <v>23</v>
       </c>
@@ -12510,7 +12521,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A62" s="90"/>
       <c r="B62" s="74" t="s">
         <v>23</v>
       </c>
@@ -22811,6 +22823,7 @@
       <c r="AF112" s="74"/>
     </row>
     <row r="113" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A113" s="90"/>
       <c r="B113" s="74" t="s">
         <v>23</v>
       </c>
@@ -22899,6 +22912,7 @@
       <c r="AF113" s="74"/>
     </row>
     <row r="114" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A114" s="90"/>
       <c r="B114" s="74" t="s">
         <v>23</v>
       </c>
@@ -23153,6 +23167,7 @@
       <c r="AF116" s="102"/>
     </row>
     <row r="117" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A117" s="90"/>
       <c r="B117" s="74" t="s">
         <v>23</v>
       </c>
@@ -23241,6 +23256,7 @@
       <c r="AF117" s="74"/>
     </row>
     <row r="118" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A118" s="90"/>
       <c r="B118" s="74" t="s">
         <v>23</v>
       </c>
@@ -23679,6 +23695,7 @@
       <c r="AF122" s="74"/>
     </row>
     <row r="123" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A123" s="90"/>
       <c r="B123" s="74" t="s">
         <v>23</v>
       </c>
@@ -23933,6 +23950,7 @@
       <c r="AF125" s="102"/>
     </row>
     <row r="126" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A126" s="90"/>
       <c r="B126" s="74" t="s">
         <v>23</v>
       </c>
@@ -24021,6 +24039,7 @@
       <c r="AF126" s="74"/>
     </row>
     <row r="127" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A127" s="90"/>
       <c r="B127" s="74" t="s">
         <v>23</v>
       </c>
@@ -24109,6 +24128,7 @@
       <c r="AF127" s="74"/>
     </row>
     <row r="128" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A128" s="90"/>
       <c r="B128" s="74" t="s">
         <v>23</v>
       </c>
@@ -24197,6 +24217,7 @@
       <c r="AF128" s="74"/>
     </row>
     <row r="129" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A129" s="90"/>
       <c r="B129" s="74" t="s">
         <v>23</v>
       </c>
@@ -24285,6 +24306,7 @@
       <c r="AF129" s="74"/>
     </row>
     <row r="130" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A130" s="90"/>
       <c r="B130" s="74" t="s">
         <v>23</v>
       </c>
@@ -24373,6 +24395,7 @@
       <c r="AF130" s="74"/>
     </row>
     <row r="131" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A131" s="90"/>
       <c r="B131" s="74" t="s">
         <v>23</v>
       </c>
@@ -25772,7 +25795,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:R161"/>
+  <dimension ref="A1:R159"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.25" style="75" customWidth="1"/>
@@ -32163,6 +32186,7 @@
       <c r="R120" s="73"/>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A121" s="99"/>
       <c r="B121" s="74" t="s">
         <v>23</v>
       </c>
@@ -32215,6 +32239,7 @@
       <c r="R121" s="74"/>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A122" s="99"/>
       <c r="B122" s="73" t="s">
         <v>23</v>
       </c>
@@ -32267,6 +32292,7 @@
       <c r="R122" s="73"/>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A123" s="99"/>
       <c r="B123" s="74" t="s">
         <v>23</v>
       </c>
@@ -32319,6 +32345,7 @@
       <c r="R123" s="74"/>
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A124" s="99"/>
       <c r="B124" s="73" t="s">
         <v>23</v>
       </c>
@@ -32371,6 +32398,7 @@
       <c r="R124" s="73"/>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A125" s="99"/>
       <c r="B125" s="74" t="s">
         <v>23</v>
       </c>
@@ -32423,6 +32451,7 @@
       <c r="R125" s="74"/>
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A126" s="99"/>
       <c r="B126" s="101" t="s">
         <v>23</v>
       </c>
@@ -32477,6 +32506,7 @@
       </c>
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A127" s="99"/>
       <c r="B127" s="101" t="s">
         <v>23</v>
       </c>
@@ -32529,6 +32559,7 @@
       <c r="R127" s="101"/>
     </row>
     <row r="128" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A128" s="99"/>
       <c r="B128" s="101" t="s">
         <v>23</v>
       </c>
@@ -32563,8 +32594,8 @@
       <c r="L128" s="101" t="s">
         <v>228</v>
       </c>
-      <c r="M128" s="101" t="s">
-        <v>228</v>
+      <c r="M128" s="101">
+        <v>1</v>
       </c>
       <c r="N128" s="101" t="s">
         <v>192</v>
@@ -32581,6 +32612,7 @@
       <c r="R128" s="101"/>
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A129" s="99"/>
       <c r="B129" s="74" t="s">
         <v>23</v>
       </c>
@@ -32792,6 +32824,7 @@
       <c r="R132" s="73"/>
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A133" s="99"/>
       <c r="B133" s="100" t="s">
         <v>23</v>
       </c>
@@ -32846,6 +32879,7 @@
       </c>
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A134" s="99"/>
       <c r="B134" s="100" t="s">
         <v>23</v>
       </c>
@@ -32898,6 +32932,7 @@
       <c r="R134" s="100"/>
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A135" s="99"/>
       <c r="B135" s="100" t="s">
         <v>23</v>
       </c>
@@ -32950,6 +32985,7 @@
       <c r="R135" s="100"/>
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A136" s="99"/>
       <c r="B136" s="100" t="s">
         <v>23</v>
       </c>
@@ -33002,6 +33038,7 @@
       <c r="R136" s="100"/>
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A137" s="99"/>
       <c r="B137" s="100" t="s">
         <v>23</v>
       </c>
@@ -33054,6 +33091,7 @@
       <c r="R137" s="100"/>
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A138" s="99"/>
       <c r="B138" s="100" t="s">
         <v>23</v>
       </c>
@@ -33106,42 +33144,43 @@
       <c r="R138" s="100"/>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A139" s="99"/>
       <c r="B139" s="73" t="s">
         <v>23</v>
       </c>
       <c r="C139" s="73" t="str" cm="1">
         <f t="array" ref="C139">UPPER(INDEX(_xlfn.TEXTSPLIT($D139, "-"), 3))</f>
-        <v>IF</v>
+        <v>CS</v>
       </c>
       <c r="D139" s="78" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E139" s="85" t="s">
         <v>24</v>
       </c>
       <c r="F139" s="73" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="G139" s="73" t="s">
-        <v>228</v>
+        <v>878</v>
       </c>
       <c r="H139" s="73" t="s">
-        <v>228</v>
-      </c>
-      <c r="I139" s="73" t="s">
-        <v>228</v>
+        <v>180</v>
+      </c>
+      <c r="I139" s="73">
+        <v>128</v>
       </c>
       <c r="J139" s="73" t="s">
-        <v>228</v>
+        <v>879</v>
       </c>
       <c r="K139" s="73" t="s">
-        <v>228</v>
-      </c>
-      <c r="L139" s="73" t="s">
-        <v>228</v>
-      </c>
-      <c r="M139" s="73" t="s">
-        <v>228</v>
+        <v>180</v>
+      </c>
+      <c r="L139" s="73">
+        <v>128</v>
+      </c>
+      <c r="M139" s="78">
+        <v>1</v>
       </c>
       <c r="N139" s="73" t="s">
         <v>192</v>
@@ -33158,42 +33197,43 @@
       <c r="R139" s="73"/>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A140" s="99"/>
       <c r="B140" s="74" t="s">
         <v>23</v>
       </c>
       <c r="C140" s="74" t="str" cm="1">
         <f t="array" ref="C140">UPPER(INDEX(_xlfn.TEXTSPLIT($D140, "-"), 3))</f>
-        <v>IF</v>
+        <v>CS</v>
       </c>
       <c r="D140" s="80" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E140" s="86" t="s">
         <v>24</v>
       </c>
       <c r="F140" s="74" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="G140" s="74" t="s">
-        <v>228</v>
+        <v>880</v>
       </c>
       <c r="H140" s="74" t="s">
-        <v>228</v>
-      </c>
-      <c r="I140" s="74" t="s">
-        <v>228</v>
+        <v>180</v>
+      </c>
+      <c r="I140" s="74">
+        <v>128</v>
       </c>
       <c r="J140" s="74" t="s">
-        <v>228</v>
+        <v>881</v>
       </c>
       <c r="K140" s="74" t="s">
-        <v>228</v>
-      </c>
-      <c r="L140" s="74" t="s">
-        <v>228</v>
-      </c>
-      <c r="M140" s="74" t="s">
-        <v>228</v>
+        <v>180</v>
+      </c>
+      <c r="L140" s="74">
+        <v>128</v>
+      </c>
+      <c r="M140" s="80">
+        <v>2</v>
       </c>
       <c r="N140" s="74" t="s">
         <v>192</v>
@@ -33210,6 +33250,7 @@
       <c r="R140" s="74"/>
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A141" s="99"/>
       <c r="B141" s="73" t="s">
         <v>23</v>
       </c>
@@ -33224,10 +33265,10 @@
         <v>24</v>
       </c>
       <c r="F141" s="73" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="G141" s="73" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="H141" s="73" t="s">
         <v>180</v>
@@ -33236,7 +33277,7 @@
         <v>128</v>
       </c>
       <c r="J141" s="73" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="K141" s="73" t="s">
         <v>180</v>
@@ -33262,6 +33303,7 @@
       <c r="R141" s="73"/>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A142" s="99"/>
       <c r="B142" s="74" t="s">
         <v>23</v>
       </c>
@@ -33276,10 +33318,10 @@
         <v>24</v>
       </c>
       <c r="F142" s="74" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="G142" s="74" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="H142" s="74" t="s">
         <v>180</v>
@@ -33288,7 +33330,7 @@
         <v>128</v>
       </c>
       <c r="J142" s="74" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="K142" s="74" t="s">
         <v>180</v>
@@ -33314,6 +33356,7 @@
       <c r="R142" s="74"/>
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A143" s="99"/>
       <c r="B143" s="73" t="s">
         <v>23</v>
       </c>
@@ -33328,10 +33371,10 @@
         <v>24</v>
       </c>
       <c r="F143" s="73" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="G143" s="73" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="H143" s="73" t="s">
         <v>180</v>
@@ -33340,7 +33383,7 @@
         <v>128</v>
       </c>
       <c r="J143" s="73" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="K143" s="73" t="s">
         <v>180</v>
@@ -33366,6 +33409,7 @@
       <c r="R143" s="73"/>
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A144" s="99"/>
       <c r="B144" s="74" t="s">
         <v>23</v>
       </c>
@@ -33380,10 +33424,10 @@
         <v>24</v>
       </c>
       <c r="F144" s="74" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G144" s="74" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="H144" s="74" t="s">
         <v>180</v>
@@ -33392,7 +33436,7 @@
         <v>128</v>
       </c>
       <c r="J144" s="74" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="K144" s="74" t="s">
         <v>180</v>
@@ -33418,24 +33462,25 @@
       <c r="R144" s="74"/>
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A145" s="99"/>
       <c r="B145" s="73" t="s">
         <v>23</v>
       </c>
       <c r="C145" s="73" t="str" cm="1">
         <f t="array" ref="C145">UPPER(INDEX(_xlfn.TEXTSPLIT($D145, "-"), 3))</f>
-        <v>CS</v>
+        <v>DOIP</v>
       </c>
       <c r="D145" s="78" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E145" s="85" t="s">
         <v>24</v>
       </c>
       <c r="F145" s="73" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="G145" s="73" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="H145" s="73" t="s">
         <v>180</v>
@@ -33444,7 +33489,7 @@
         <v>128</v>
       </c>
       <c r="J145" s="73" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="K145" s="73" t="s">
         <v>180</v>
@@ -33470,24 +33515,25 @@
       <c r="R145" s="73"/>
     </row>
     <row r="146" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A146" s="99"/>
       <c r="B146" s="74" t="s">
         <v>23</v>
       </c>
       <c r="C146" s="74" t="str" cm="1">
         <f t="array" ref="C146">UPPER(INDEX(_xlfn.TEXTSPLIT($D146, "-"), 3))</f>
-        <v>CS</v>
+        <v>DOIP</v>
       </c>
       <c r="D146" s="80" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E146" s="86" t="s">
         <v>24</v>
       </c>
       <c r="F146" s="74" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="G146" s="74" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="H146" s="74" t="s">
         <v>180</v>
@@ -33496,7 +33542,7 @@
         <v>128</v>
       </c>
       <c r="J146" s="74" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="K146" s="74" t="s">
         <v>180</v>
@@ -33522,6 +33568,7 @@
       <c r="R146" s="74"/>
     </row>
     <row r="147" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A147" s="99"/>
       <c r="B147" s="73" t="s">
         <v>23</v>
       </c>
@@ -33536,10 +33583,10 @@
         <v>24</v>
       </c>
       <c r="F147" s="73" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="G147" s="73" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="H147" s="73" t="s">
         <v>180</v>
@@ -33548,7 +33595,7 @@
         <v>128</v>
       </c>
       <c r="J147" s="73" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="K147" s="73" t="s">
         <v>180</v>
@@ -33574,6 +33621,7 @@
       <c r="R147" s="73"/>
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A148" s="99"/>
       <c r="B148" s="74" t="s">
         <v>23</v>
       </c>
@@ -33588,10 +33636,10 @@
         <v>24</v>
       </c>
       <c r="F148" s="74" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G148" s="74" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="H148" s="74" t="s">
         <v>180</v>
@@ -33600,7 +33648,7 @@
         <v>128</v>
       </c>
       <c r="J148" s="74" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="K148" s="74" t="s">
         <v>180</v>
@@ -33626,6 +33674,7 @@
       <c r="R148" s="74"/>
     </row>
     <row r="149" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A149" s="99"/>
       <c r="B149" s="73" t="s">
         <v>23</v>
       </c>
@@ -33640,10 +33689,10 @@
         <v>24</v>
       </c>
       <c r="F149" s="73" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G149" s="73" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="H149" s="73" t="s">
         <v>180</v>
@@ -33652,7 +33701,7 @@
         <v>128</v>
       </c>
       <c r="J149" s="73" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="K149" s="73" t="s">
         <v>180</v>
@@ -33678,6 +33727,7 @@
       <c r="R149" s="73"/>
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A150" s="99"/>
       <c r="B150" s="74" t="s">
         <v>23</v>
       </c>
@@ -33692,10 +33742,10 @@
         <v>24</v>
       </c>
       <c r="F150" s="74" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G150" s="74" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="H150" s="74" t="s">
         <v>180</v>
@@ -33704,7 +33754,7 @@
         <v>128</v>
       </c>
       <c r="J150" s="74" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="K150" s="74" t="s">
         <v>180</v>
@@ -33730,24 +33780,25 @@
       <c r="R150" s="74"/>
     </row>
     <row r="151" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A151" s="99"/>
       <c r="B151" s="73" t="s">
         <v>23</v>
       </c>
       <c r="C151" s="73" t="str" cm="1">
         <f t="array" ref="C151">UPPER(INDEX(_xlfn.TEXTSPLIT($D151, "-"), 3))</f>
-        <v>DOIP</v>
+        <v>BDP</v>
       </c>
       <c r="D151" s="78" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E151" s="85" t="s">
         <v>24</v>
       </c>
       <c r="F151" s="73" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G151" s="73" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="H151" s="73" t="s">
         <v>180</v>
@@ -33756,7 +33807,7 @@
         <v>128</v>
       </c>
       <c r="J151" s="73" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="K151" s="73" t="s">
         <v>180</v>
@@ -33782,24 +33833,25 @@
       <c r="R151" s="73"/>
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A152" s="99"/>
       <c r="B152" s="74" t="s">
         <v>23</v>
       </c>
       <c r="C152" s="74" t="str" cm="1">
         <f t="array" ref="C152">UPPER(INDEX(_xlfn.TEXTSPLIT($D152, "-"), 3))</f>
-        <v>DOIP</v>
+        <v>BDP</v>
       </c>
       <c r="D152" s="80" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E152" s="86" t="s">
         <v>24</v>
       </c>
       <c r="F152" s="74" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="G152" s="74" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="H152" s="74" t="s">
         <v>180</v>
@@ -33808,7 +33860,7 @@
         <v>128</v>
       </c>
       <c r="J152" s="74" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="K152" s="74" t="s">
         <v>180</v>
@@ -33849,10 +33901,10 @@
         <v>24</v>
       </c>
       <c r="F153" s="73" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="G153" s="73" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="H153" s="73" t="s">
         <v>180</v>
@@ -33861,7 +33913,7 @@
         <v>128</v>
       </c>
       <c r="J153" s="73" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="K153" s="73" t="s">
         <v>180</v>
@@ -33902,10 +33954,10 @@
         <v>24</v>
       </c>
       <c r="F154" s="74" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G154" s="74" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="H154" s="74" t="s">
         <v>180</v>
@@ -33914,7 +33966,7 @@
         <v>128</v>
       </c>
       <c r="J154" s="74" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="K154" s="74" t="s">
         <v>180</v>
@@ -33955,10 +34007,10 @@
         <v>24</v>
       </c>
       <c r="F155" s="73" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G155" s="73" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="H155" s="73" t="s">
         <v>180</v>
@@ -33967,7 +34019,7 @@
         <v>128</v>
       </c>
       <c r="J155" s="73" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="K155" s="73" t="s">
         <v>180</v>
@@ -34008,10 +34060,10 @@
         <v>24</v>
       </c>
       <c r="F156" s="74" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="G156" s="74" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="H156" s="74" t="s">
         <v>180</v>
@@ -34020,7 +34072,7 @@
         <v>128</v>
       </c>
       <c r="J156" s="74" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="K156" s="74" t="s">
         <v>180</v>
@@ -34061,10 +34113,10 @@
         <v>24</v>
       </c>
       <c r="F157" s="73" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G157" s="73" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="H157" s="73" t="s">
         <v>180</v>
@@ -34073,7 +34125,7 @@
         <v>128</v>
       </c>
       <c r="J157" s="73" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="K157" s="73" t="s">
         <v>180</v>
@@ -34082,7 +34134,7 @@
         <v>128</v>
       </c>
       <c r="M157" s="78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N157" s="73" t="s">
         <v>192</v>
@@ -34099,34 +34151,33 @@
       <c r="R157" s="73"/>
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A158" s="99"/>
       <c r="B158" s="74" t="s">
-        <v>23</v>
+        <v>1087</v>
       </c>
       <c r="C158" s="74" t="str" cm="1">
         <f t="array" ref="C158">UPPER(INDEX(_xlfn.TEXTSPLIT($D158, "-"), 3))</f>
-        <v>BDP</v>
+        <v>COMM</v>
       </c>
       <c r="D158" s="80" t="s">
-        <v>324</v>
+        <v>234</v>
       </c>
       <c r="E158" s="86" t="s">
         <v>24</v>
       </c>
       <c r="F158" s="74" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="G158" s="74" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="H158" s="74" t="s">
-        <v>180</v>
+        <v>709</v>
       </c>
       <c r="I158" s="74">
         <v>128</v>
       </c>
       <c r="J158" s="74" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="K158" s="74" t="s">
         <v>180</v>
@@ -34135,16 +34186,16 @@
         <v>128</v>
       </c>
       <c r="M158" s="80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N158" s="74" t="s">
         <v>192</v>
       </c>
       <c r="O158" s="74" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="P158" s="74" t="s">
-        <v>920</v>
+        <v>235</v>
       </c>
       <c r="Q158" s="74" t="b">
         <v>1</v>
@@ -34152,25 +34203,24 @@
       <c r="R158" s="74"/>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A159" s="99"/>
       <c r="B159" s="73" t="s">
-        <v>23</v>
+        <v>1087</v>
       </c>
       <c r="C159" s="73" t="str" cm="1">
         <f t="array" ref="C159">UPPER(INDEX(_xlfn.TEXTSPLIT($D159, "-"), 3))</f>
-        <v>BDP</v>
+        <v>COMM</v>
       </c>
       <c r="D159" s="78" t="s">
-        <v>324</v>
+        <v>234</v>
       </c>
       <c r="E159" s="85" t="s">
         <v>24</v>
       </c>
       <c r="F159" s="73" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G159" s="73" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="H159" s="73" t="s">
         <v>180</v>
@@ -34179,7 +34229,7 @@
         <v>128</v>
       </c>
       <c r="J159" s="73" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="K159" s="73" t="s">
         <v>180</v>
@@ -34188,125 +34238,21 @@
         <v>128</v>
       </c>
       <c r="M159" s="78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N159" s="73" t="s">
         <v>192</v>
       </c>
       <c r="O159" s="73" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="P159" s="73" t="s">
-        <v>920</v>
+        <v>235</v>
       </c>
       <c r="Q159" s="73" t="b">
         <v>1</v>
       </c>
       <c r="R159" s="73"/>
-    </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B160" s="74" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C160" s="74" t="str" cm="1">
-        <f t="array" ref="C160">UPPER(INDEX(_xlfn.TEXTSPLIT($D160, "-"), 3))</f>
-        <v>COMM</v>
-      </c>
-      <c r="D160" s="80" t="s">
-        <v>234</v>
-      </c>
-      <c r="E160" s="86" t="s">
-        <v>24</v>
-      </c>
-      <c r="F160" s="74" t="s">
-        <v>491</v>
-      </c>
-      <c r="G160" s="74" t="s">
-        <v>916</v>
-      </c>
-      <c r="H160" s="74" t="s">
-        <v>709</v>
-      </c>
-      <c r="I160" s="74">
-        <v>128</v>
-      </c>
-      <c r="J160" s="74" t="s">
-        <v>917</v>
-      </c>
-      <c r="K160" s="74" t="s">
-        <v>180</v>
-      </c>
-      <c r="L160" s="74">
-        <v>128</v>
-      </c>
-      <c r="M160" s="80">
-        <v>1</v>
-      </c>
-      <c r="N160" s="74" t="s">
-        <v>192</v>
-      </c>
-      <c r="O160" s="74" t="s">
-        <v>234</v>
-      </c>
-      <c r="P160" s="74" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q160" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="R160" s="74"/>
-    </row>
-    <row r="161" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B161" s="73" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C161" s="73" t="str" cm="1">
-        <f t="array" ref="C161">UPPER(INDEX(_xlfn.TEXTSPLIT($D161, "-"), 3))</f>
-        <v>COMM</v>
-      </c>
-      <c r="D161" s="78" t="s">
-        <v>234</v>
-      </c>
-      <c r="E161" s="85" t="s">
-        <v>24</v>
-      </c>
-      <c r="F161" s="73" t="s">
-        <v>492</v>
-      </c>
-      <c r="G161" s="73" t="s">
-        <v>918</v>
-      </c>
-      <c r="H161" s="73" t="s">
-        <v>180</v>
-      </c>
-      <c r="I161" s="73">
-        <v>128</v>
-      </c>
-      <c r="J161" s="73" t="s">
-        <v>919</v>
-      </c>
-      <c r="K161" s="73" t="s">
-        <v>180</v>
-      </c>
-      <c r="L161" s="73">
-        <v>128</v>
-      </c>
-      <c r="M161" s="78">
-        <v>1</v>
-      </c>
-      <c r="N161" s="73" t="s">
-        <v>192</v>
-      </c>
-      <c r="O161" s="73" t="s">
-        <v>234</v>
-      </c>
-      <c r="P161" s="73" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q161" s="73" t="b">
-        <v>1</v>
-      </c>
-      <c r="R161" s="73"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -38813,6 +38759,7 @@
       <c r="M112" s="73"/>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A113" s="90"/>
       <c r="B113" s="80" t="s">
         <v>23</v>
       </c>
@@ -38852,6 +38799,7 @@
       <c r="M113" s="74"/>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A114" s="90"/>
       <c r="B114" s="78" t="s">
         <v>23</v>
       </c>
@@ -38891,6 +38839,7 @@
       <c r="M114" s="73"/>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A115" s="90"/>
       <c r="B115" s="80" t="s">
         <v>23</v>
       </c>
@@ -38930,6 +38879,7 @@
       <c r="M115" s="74"/>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A116" s="115"/>
       <c r="B116" s="78" t="s">
         <v>23</v>
       </c>
@@ -38969,6 +38919,7 @@
       <c r="M116" s="73"/>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A117" s="115"/>
       <c r="B117" s="80" t="s">
         <v>23</v>
       </c>
@@ -39008,6 +38959,7 @@
       <c r="M117" s="74"/>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A118" s="90"/>
       <c r="B118" s="78" t="s">
         <v>23</v>
       </c>
@@ -39047,6 +38999,7 @@
       <c r="M118" s="73"/>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A119" s="115"/>
       <c r="B119" s="80" t="s">
         <v>23</v>
       </c>
@@ -39206,6 +39159,7 @@
       <c r="M122" s="73"/>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A123" s="90"/>
       <c r="B123" s="80" t="s">
         <v>23</v>
       </c>
@@ -39245,6 +39199,7 @@
       <c r="M123" s="74"/>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A124" s="115"/>
       <c r="B124" s="78" t="s">
         <v>23</v>
       </c>
@@ -39284,6 +39239,7 @@
       <c r="M124" s="73"/>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A125" s="115"/>
       <c r="B125" s="80" t="s">
         <v>23</v>
       </c>
@@ -39323,6 +39279,7 @@
       <c r="M125" s="74"/>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A126" s="90"/>
       <c r="B126" s="78" t="s">
         <v>23</v>
       </c>
@@ -39362,6 +39319,7 @@
       <c r="M126" s="73"/>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A127" s="90"/>
       <c r="B127" s="80" t="s">
         <v>23</v>
       </c>
@@ -39401,6 +39359,7 @@
       <c r="M127" s="74"/>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A128" s="90"/>
       <c r="B128" s="78" t="s">
         <v>23</v>
       </c>
@@ -39440,6 +39399,7 @@
       <c r="M128" s="73"/>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A129" s="90"/>
       <c r="B129" s="80" t="s">
         <v>23</v>
       </c>
@@ -39479,6 +39439,7 @@
       <c r="M129" s="74"/>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A130" s="90"/>
       <c r="B130" s="78" t="s">
         <v>23</v>
       </c>
@@ -39518,6 +39479,7 @@
       <c r="M130" s="73"/>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A131" s="90"/>
       <c r="B131" s="80" t="s">
         <v>23</v>
       </c>
@@ -39557,6 +39519,7 @@
       <c r="M131" s="74"/>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A132" s="115"/>
       <c r="B132" s="78" t="s">
         <v>23</v>
       </c>
@@ -39596,6 +39559,7 @@
       <c r="M132" s="73"/>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A133" s="115"/>
       <c r="B133" s="80" t="s">
         <v>23</v>
       </c>
@@ -39635,6 +39599,7 @@
       <c r="M133" s="74"/>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A134" s="115"/>
       <c r="B134" s="78" t="s">
         <v>23</v>
       </c>
@@ -39674,6 +39639,7 @@
       <c r="M134" s="73"/>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A135" s="115"/>
       <c r="B135" s="80" t="s">
         <v>23</v>
       </c>
@@ -39713,6 +39679,7 @@
       <c r="M135" s="74"/>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A136" s="115"/>
       <c r="B136" s="78" t="s">
         <v>23</v>
       </c>
@@ -39752,6 +39719,7 @@
       <c r="M136" s="73"/>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A137" s="115"/>
       <c r="B137" s="80" t="s">
         <v>23</v>
       </c>
@@ -39791,6 +39759,7 @@
       <c r="M137" s="74"/>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A138" s="90"/>
       <c r="B138" s="78" t="s">
         <v>23</v>
       </c>
@@ -39830,6 +39799,7 @@
       <c r="M138" s="73"/>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A139" s="90"/>
       <c r="B139" s="80" t="s">
         <v>23</v>
       </c>
@@ -40275,6 +40245,7 @@
       <c r="M150" s="73"/>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A151" s="115"/>
       <c r="B151" s="80" t="s">
         <v>23</v>
       </c>
@@ -40307,6 +40278,7 @@
       <c r="M151" s="74"/>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A152" s="115"/>
       <c r="B152" s="78" t="s">
         <v>23</v>
       </c>
@@ -40405,6 +40377,7 @@
       <c r="M154" s="73"/>
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A155" s="90"/>
       <c r="B155" s="80" t="s">
         <v>23</v>
       </c>
@@ -40437,6 +40410,7 @@
       <c r="M155" s="74"/>
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A156" s="90"/>
       <c r="B156" s="78" t="s">
         <v>23</v>
       </c>
@@ -40596,7 +40570,8 @@
       </c>
       <c r="M160" s="73"/>
     </row>
-    <row r="161" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A161" s="90"/>
       <c r="B161" s="80" t="s">
         <v>23</v>
       </c>
@@ -40628,7 +40603,8 @@
       </c>
       <c r="M161" s="74"/>
     </row>
-    <row r="162" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A162" s="90"/>
       <c r="B162" s="78" t="s">
         <v>23</v>
       </c>
@@ -40660,7 +40636,8 @@
       </c>
       <c r="M162" s="73"/>
     </row>
-    <row r="163" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A163" s="90"/>
       <c r="B163" s="80" t="s">
         <v>23</v>
       </c>
@@ -40692,7 +40669,8 @@
       </c>
       <c r="M163" s="74"/>
     </row>
-    <row r="164" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A164" s="90"/>
       <c r="B164" s="78" t="s">
         <v>23</v>
       </c>
@@ -44861,7 +44839,8 @@
         <v>p-bdp-slap-lb-bp</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A33" s="90"/>
       <c r="B33" s="74" t="s">
         <v>952</v>
       </c>
@@ -44912,7 +44891,8 @@
         <v>p-if-auth-lb-bp</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A34" s="90"/>
       <c r="B34" s="82" t="s">
         <v>23</v>
       </c>
@@ -44963,7 +44943,8 @@
         <v>p-if-proxy-lb-bp</v>
       </c>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A35" s="90"/>
       <c r="B35" s="74" t="s">
         <v>952</v>
       </c>
@@ -45014,7 +44995,8 @@
         <v>p-cs-chtap-lb-bp</v>
       </c>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A36" s="90"/>
       <c r="B36" s="82" t="s">
         <v>23</v>
       </c>
@@ -45065,7 +45047,8 @@
         <v>p-cs-chtweb-lb-bp</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A37" s="90"/>
       <c r="B37" s="74" t="s">
         <v>952</v>
       </c>
@@ -45116,7 +45099,8 @@
         <v>p-cs-chtintweb-lb-bp</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A38" s="90"/>
       <c r="B38" s="82" t="s">
         <v>23</v>
       </c>
@@ -45167,7 +45151,8 @@
         <v>p-doip-web-lb-bp</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A39" s="90"/>
       <c r="B39" s="74" t="s">
         <v>952</v>
       </c>
@@ -45218,7 +45203,8 @@
         <v>p-doip-ap-lb-bp</v>
       </c>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A40" s="90"/>
       <c r="B40" s="82" t="s">
         <v>23</v>
       </c>
@@ -45269,7 +45255,8 @@
         <v>p-doip-adm-lb-bp</v>
       </c>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A41" s="90"/>
       <c r="B41" s="74" t="s">
         <v>952</v>
       </c>
@@ -45320,7 +45307,8 @@
         <v>p-bdp-crkweb-lb-bp</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A42" s="90"/>
       <c r="B42" s="82" t="s">
         <v>23</v>
       </c>
@@ -45371,7 +45359,8 @@
         <v>p-bdp-crkap-lb-bp</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A43" s="90"/>
       <c r="B43" s="74" t="s">
         <v>952</v>
       </c>
@@ -45422,7 +45411,7 @@
         <v>p-bdp-crkml-lb-bp</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -47010,6 +46999,7 @@
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" s="90"/>
       <c r="B48" s="74" t="s">
         <v>23</v>
       </c>
@@ -47041,7 +47031,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" s="90"/>
       <c r="B49" s="74" t="s">
         <v>23</v>
       </c>
@@ -47073,7 +47064,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="90"/>
       <c r="B50" s="74" t="s">
         <v>23</v>
       </c>
@@ -47105,7 +47097,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" s="90"/>
       <c r="B51" s="82" t="s">
         <v>23</v>
       </c>
@@ -47137,7 +47130,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A52" s="90"/>
       <c r="B52" s="82" t="s">
         <v>23</v>
       </c>
@@ -47165,7 +47159,7 @@
       <c r="J52" s="82"/>
       <c r="K52" s="82"/>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B53" s="102" t="s">
         <v>1083</v>
       </c>
@@ -47194,7 +47188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B54" s="102" t="s">
         <v>1083</v>
       </c>
@@ -47223,7 +47217,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B55" s="102" t="s">
         <v>1083</v>
       </c>
@@ -47252,7 +47246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B56" s="102" t="s">
         <v>1083</v>
       </c>
@@ -47281,7 +47275,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B57" s="102" t="s">
         <v>1083</v>
       </c>
@@ -47310,7 +47304,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B58" s="102" t="s">
         <v>1083</v>
       </c>
@@ -47339,7 +47333,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59" s="90"/>
       <c r="B59" s="74" t="s">
         <v>23</v>
       </c>
@@ -47371,7 +47366,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60" s="90"/>
       <c r="B60" s="74" t="s">
         <v>23</v>
       </c>
@@ -47399,7 +47395,8 @@
       <c r="J60" s="74"/>
       <c r="K60" s="74"/>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61" s="90"/>
       <c r="B61" s="82" t="s">
         <v>23</v>
       </c>
@@ -47431,7 +47428,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62" s="90"/>
       <c r="B62" s="74" t="s">
         <v>23</v>
       </c>
@@ -47470,12 +47468,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -47623,15 +47618,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -47655,17 +47661,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260617_리소스배포_운영.xlsx
+++ b/서버정보/20260617_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A499EABF-7A6A-4C9D-A29E-48C2FDA69B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77CD9820-8EE3-40A7-8476-03E7B99CD6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -5644,14 +5644,6 @@
     <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_nginx_Base_Image/versions/0.0.9</t>
   </si>
   <si>
-    <t>10.155.161.128</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.155.161.129</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>l-if-ap-sbn</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5724,6 +5716,14 @@
   </si>
   <si>
     <t>D2ls_v5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.155.161.132</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.155.161.133</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6211,7 +6211,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6555,9 +6555,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -13321,7 +13318,7 @@
         <v>499</v>
       </c>
       <c r="H6" s="80" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="I6" s="80">
         <v>2</v>
@@ -13410,7 +13407,7 @@
         <v>500</v>
       </c>
       <c r="H7" s="80" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="I7" s="80">
         <v>2</v>
@@ -14300,7 +14297,7 @@
         <v>510</v>
       </c>
       <c r="H17" s="80" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="I17" s="80">
         <v>2</v>
@@ -14389,7 +14386,7 @@
         <v>511</v>
       </c>
       <c r="H18" s="80" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="I18" s="80">
         <v>2</v>
@@ -14478,7 +14475,7 @@
         <v>512</v>
       </c>
       <c r="H19" s="80" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="I19" s="80">
         <v>2</v>
@@ -14567,7 +14564,7 @@
         <v>513</v>
       </c>
       <c r="H20" s="80" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="I20" s="80">
         <v>2</v>
@@ -15920,7 +15917,7 @@
         <v>641</v>
       </c>
       <c r="N35" s="98" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="O35" s="74" t="str">
         <f t="shared" si="2"/>
@@ -20705,7 +20702,7 @@
         <v>438</v>
       </c>
       <c r="G89" s="80" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="H89" s="80" t="s">
         <v>638</v>
@@ -23002,7 +22999,7 @@
     </row>
     <row r="115" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B115" s="102" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C115" s="102"/>
       <c r="D115" s="104" t="s">
@@ -23085,7 +23082,7 @@
     </row>
     <row r="116" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B116" s="102" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C116" s="102"/>
       <c r="D116" s="104" t="s">
@@ -23188,7 +23185,7 @@
         <v>609</v>
       </c>
       <c r="H117" s="80" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="I117" s="80">
         <v>2</v>
@@ -23346,7 +23343,7 @@
     </row>
     <row r="119" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B119" s="102" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C119" s="102"/>
       <c r="D119" s="104" t="s">
@@ -23785,7 +23782,7 @@
     </row>
     <row r="124" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B124" s="102" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C124" s="102"/>
       <c r="D124" s="102" t="s">
@@ -23798,10 +23795,10 @@
         <v>470</v>
       </c>
       <c r="G124" s="102" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="H124" s="102" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I124" s="102">
         <v>2</v>
@@ -23816,7 +23813,7 @@
         <v>179</v>
       </c>
       <c r="M124" s="102" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="N124" s="102"/>
       <c r="O124" s="102" t="str">
@@ -23868,7 +23865,7 @@
     </row>
     <row r="125" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B125" s="102" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C125" s="102"/>
       <c r="D125" s="102" t="s">
@@ -23881,10 +23878,10 @@
         <v>471</v>
       </c>
       <c r="G125" s="102" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="H125" s="102" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I125" s="102">
         <v>2</v>
@@ -23899,7 +23896,7 @@
         <v>179</v>
       </c>
       <c r="M125" s="102" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="N125" s="102"/>
       <c r="O125" s="102" t="str">
@@ -24485,7 +24482,7 @@
     </row>
     <row r="132" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B132" s="102" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C132" s="102"/>
       <c r="D132" s="102" t="s">
@@ -24498,10 +24495,10 @@
         <v>478</v>
       </c>
       <c r="G132" s="102" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="H132" s="102" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I132" s="102">
         <v>2</v>
@@ -24516,7 +24513,7 @@
         <v>179</v>
       </c>
       <c r="M132" s="102" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="N132" s="102"/>
       <c r="O132" s="102" t="str">
@@ -24568,7 +24565,7 @@
     </row>
     <row r="133" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B133" s="102" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C133" s="102"/>
       <c r="D133" s="102" t="s">
@@ -24581,10 +24578,10 @@
         <v>479</v>
       </c>
       <c r="G133" s="102" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="H133" s="102" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I133" s="102">
         <v>2</v>
@@ -24599,7 +24596,7 @@
         <v>179</v>
       </c>
       <c r="M133" s="102" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="N133" s="102"/>
       <c r="O133" s="102" t="str">
@@ -24651,7 +24648,7 @@
     </row>
     <row r="134" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B134" s="102" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C134" s="102"/>
       <c r="D134" s="102" t="s">
@@ -24664,10 +24661,10 @@
         <v>480</v>
       </c>
       <c r="G134" s="102" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="H134" s="102" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I134" s="102">
         <v>2</v>
@@ -24682,7 +24679,7 @@
         <v>179</v>
       </c>
       <c r="M134" s="102" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="N134" s="102"/>
       <c r="O134" s="102" t="str">
@@ -24734,7 +24731,7 @@
     </row>
     <row r="135" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B135" s="102" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C135" s="102"/>
       <c r="D135" s="102" t="s">
@@ -24747,10 +24744,10 @@
         <v>481</v>
       </c>
       <c r="G135" s="102" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="H135" s="102" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I135" s="102">
         <v>2</v>
@@ -24765,7 +24762,7 @@
         <v>179</v>
       </c>
       <c r="M135" s="102" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="N135" s="102"/>
       <c r="O135" s="102" t="str">
@@ -24817,7 +24814,7 @@
     </row>
     <row r="136" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B136" s="102" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C136" s="102"/>
       <c r="D136" s="102" t="s">
@@ -24830,10 +24827,10 @@
         <v>482</v>
       </c>
       <c r="G136" s="102" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="H136" s="102" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I136" s="102">
         <v>2</v>
@@ -24848,7 +24845,7 @@
         <v>179</v>
       </c>
       <c r="M136" s="102" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="N136" s="102"/>
       <c r="O136" s="102" t="str">
@@ -24900,7 +24897,7 @@
     </row>
     <row r="137" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B137" s="102" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C137" s="102"/>
       <c r="D137" s="102" t="s">
@@ -24913,10 +24910,10 @@
         <v>483</v>
       </c>
       <c r="G137" s="102" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="H137" s="102" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I137" s="102">
         <v>2</v>
@@ -24931,7 +24928,7 @@
         <v>179</v>
       </c>
       <c r="M137" s="102" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="N137" s="102"/>
       <c r="O137" s="102" t="str">
@@ -25622,7 +25619,7 @@
         <v>491</v>
       </c>
       <c r="G145" s="80" t="s">
-        <v>1090</v>
+        <v>1109</v>
       </c>
       <c r="H145" s="80" t="s">
         <v>634</v>
@@ -25675,7 +25672,7 @@
         <v>225</v>
       </c>
       <c r="Z145" s="74" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="AA145" s="74" t="b">
         <v>1</v>
@@ -25710,7 +25707,7 @@
         <v>492</v>
       </c>
       <c r="G146" s="80" t="s">
-        <v>1091</v>
+        <v>1110</v>
       </c>
       <c r="H146" s="80" t="s">
         <v>630</v>
@@ -25763,7 +25760,7 @@
         <v>225</v>
       </c>
       <c r="Z146" s="74" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="AA146" s="74" t="b">
         <v>1</v>
@@ -37101,7 +37098,7 @@
         <v>241</v>
       </c>
       <c r="H71" s="74" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="I71" s="74" t="s">
         <v>420</v>
@@ -37141,7 +37138,7 @@
         <v>241</v>
       </c>
       <c r="H72" s="73" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="I72" s="73" t="s">
         <v>421</v>
@@ -37181,7 +37178,7 @@
         <v>241</v>
       </c>
       <c r="H73" s="74" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="I73" s="74" t="s">
         <v>422</v>
@@ -37221,7 +37218,7 @@
         <v>241</v>
       </c>
       <c r="H74" s="73" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="I74" s="73" t="s">
         <v>423</v>
@@ -38879,7 +38876,6 @@
       <c r="M115" s="74"/>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A116" s="115"/>
       <c r="B116" s="78" t="s">
         <v>23</v>
       </c>
@@ -38919,7 +38915,6 @@
       <c r="M116" s="73"/>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A117" s="115"/>
       <c r="B117" s="80" t="s">
         <v>23</v>
       </c>
@@ -38999,7 +38994,6 @@
       <c r="M118" s="73"/>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="115"/>
       <c r="B119" s="80" t="s">
         <v>23</v>
       </c>
@@ -39061,7 +39055,7 @@
         <v>241</v>
       </c>
       <c r="H120" s="73" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="I120" s="73" t="s">
         <v>233</v>
@@ -39101,7 +39095,7 @@
         <v>241</v>
       </c>
       <c r="H121" s="74" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="I121" s="74" t="s">
         <v>232</v>
@@ -39141,7 +39135,7 @@
         <v>241</v>
       </c>
       <c r="H122" s="73" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="I122" s="73" t="s">
         <v>236</v>
@@ -39199,7 +39193,6 @@
       <c r="M123" s="74"/>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A124" s="115"/>
       <c r="B124" s="78" t="s">
         <v>23</v>
       </c>
@@ -39239,7 +39232,6 @@
       <c r="M124" s="73"/>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A125" s="115"/>
       <c r="B125" s="80" t="s">
         <v>23</v>
       </c>
@@ -39519,7 +39511,6 @@
       <c r="M131" s="74"/>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A132" s="115"/>
       <c r="B132" s="78" t="s">
         <v>23</v>
       </c>
@@ -39559,7 +39550,6 @@
       <c r="M132" s="73"/>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A133" s="115"/>
       <c r="B133" s="80" t="s">
         <v>23</v>
       </c>
@@ -39599,7 +39589,6 @@
       <c r="M133" s="74"/>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A134" s="115"/>
       <c r="B134" s="78" t="s">
         <v>23</v>
       </c>
@@ -39639,7 +39628,6 @@
       <c r="M134" s="73"/>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A135" s="115"/>
       <c r="B135" s="80" t="s">
         <v>23</v>
       </c>
@@ -39679,7 +39667,6 @@
       <c r="M135" s="74"/>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A136" s="115"/>
       <c r="B136" s="78" t="s">
         <v>23</v>
       </c>
@@ -39719,7 +39706,6 @@
       <c r="M136" s="73"/>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A137" s="115"/>
       <c r="B137" s="80" t="s">
         <v>23</v>
       </c>
@@ -40059,7 +40045,7 @@
         <v>225</v>
       </c>
       <c r="H145" s="74" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="I145" s="74" t="s">
         <v>491</v>
@@ -40097,7 +40083,7 @@
         <v>225</v>
       </c>
       <c r="H146" s="73" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="I146" s="73" t="s">
         <v>492</v>
@@ -40245,7 +40231,6 @@
       <c r="M150" s="73"/>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A151" s="115"/>
       <c r="B151" s="80" t="s">
         <v>23</v>
       </c>
@@ -40278,7 +40263,6 @@
       <c r="M151" s="74"/>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A152" s="115"/>
       <c r="B152" s="78" t="s">
         <v>23</v>
       </c>
@@ -42162,7 +42146,7 @@
         <v>332</v>
       </c>
       <c r="H8" s="74" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>222</v>
@@ -42793,7 +42777,7 @@
         <v>332</v>
       </c>
       <c r="H29" s="82" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="I29" s="82" t="s">
         <v>222</v>
@@ -43152,7 +43136,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD1A3252-EF11-4361-BCDB-10417C7A0940}">
   <sheetPr>
-    <tabColor theme="8" tint="-0.249977111117893"/>
+    <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:Q44"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -47468,9 +47452,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -47618,26 +47605,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -47661,9 +47637,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260617_리소스배포_운영.xlsx
+++ b/서버정보/20260617_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77CD9820-8EE3-40A7-8476-03E7B99CD6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A306EA92-8AB3-42C2-8DFC-A02D97B6B994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -23490,7 +23490,7 @@
         <v>1</v>
       </c>
       <c r="X120" s="74" t="s">
-        <v>326</v>
+        <v>234</v>
       </c>
       <c r="Y120" s="74" t="s">
         <v>203</v>
@@ -23579,7 +23579,7 @@
         <v>1</v>
       </c>
       <c r="X121" s="74" t="s">
-        <v>326</v>
+        <v>234</v>
       </c>
       <c r="Y121" s="74" t="s">
         <v>203</v>
@@ -23668,7 +23668,7 @@
         <v>1</v>
       </c>
       <c r="X122" s="74" t="s">
-        <v>326</v>
+        <v>234</v>
       </c>
       <c r="Y122" s="74" t="s">
         <v>203</v>
@@ -25601,7 +25601,8 @@
       <c r="AE144" s="74"/>
       <c r="AF144" s="74"/>
     </row>
-    <row r="145" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A145" s="90"/>
       <c r="B145" s="74" t="s">
         <v>1087</v>
       </c>
@@ -25689,7 +25690,8 @@
       <c r="AE145" s="74"/>
       <c r="AF145" s="74"/>
     </row>
-    <row r="146" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A146" s="90"/>
       <c r="B146" s="74" t="s">
         <v>1087</v>
       </c>
@@ -34148,6 +34150,7 @@
       <c r="R157" s="73"/>
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A158" s="99"/>
       <c r="B158" s="74" t="s">
         <v>1087</v>
       </c>
@@ -34200,6 +34203,7 @@
       <c r="R158" s="74"/>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A159" s="99"/>
       <c r="B159" s="73" t="s">
         <v>1087</v>
       </c>
@@ -40025,6 +40029,7 @@
       <c r="M144" s="73"/>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A145" s="90"/>
       <c r="B145" s="80" t="s">
         <v>1087</v>
       </c>
@@ -40050,8 +40055,8 @@
       <c r="I145" s="74" t="s">
         <v>491</v>
       </c>
-      <c r="J145" s="80" t="s">
-        <v>323</v>
+      <c r="J145" s="74" t="s">
+        <v>234</v>
       </c>
       <c r="K145" s="74" t="str">
         <f t="shared" si="5"/>
@@ -40063,6 +40068,7 @@
       <c r="M145" s="74"/>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A146" s="90"/>
       <c r="B146" s="78" t="s">
         <v>1087</v>
       </c>
@@ -40088,8 +40094,8 @@
       <c r="I146" s="73" t="s">
         <v>492</v>
       </c>
-      <c r="J146" s="78" t="s">
-        <v>323</v>
+      <c r="J146" s="73" t="s">
+        <v>234</v>
       </c>
       <c r="K146" s="73" t="str">
         <f t="shared" si="5"/>

--- a/서버정보/20260617_리소스배포_운영.xlsx
+++ b/서버정보/20260617_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A306EA92-8AB3-42C2-8DFC-A02D97B6B994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C05D1A-A659-4A0C-A6A3-BB75F7E03E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7361" uniqueCount="1111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7367" uniqueCount="1114">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5578,10 +5578,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>확인 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hazr-p-dtg-cdmlap-lb</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5724,6 +5720,22 @@
   </si>
   <si>
     <t>10.155.161.133</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_nginx_Base_Image/versions/0.0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D4s_v5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_Base_Image/versions/0.1.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6211,7 +6223,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6524,15 +6536,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -6556,6 +6559,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -9645,7 +9651,7 @@
         <v>1008</v>
       </c>
       <c r="E15" s="82" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F15" s="82" t="str">
         <f t="shared" si="0"/>
@@ -10811,60 +10817,64 @@
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B34" s="102" t="s">
-        <v>1083</v>
-      </c>
-      <c r="C34" s="102"/>
-      <c r="D34" s="102" t="s">
+      <c r="A34" s="90"/>
+      <c r="B34" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="82" t="str" cm="1">
+        <f t="array" ref="C34">UPPER(INDEX(_xlfn.TEXTSPLIT($D34, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="D34" s="82" t="s">
         <v>1009</v>
       </c>
-      <c r="E34" s="102" t="s">
-        <v>1074</v>
-      </c>
-      <c r="F34" s="102" t="str">
+      <c r="E34" s="82" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F34" s="82" t="str">
         <f t="shared" si="6"/>
-        <v>p-dtg-cdmlap-lb-rule?</v>
-      </c>
-      <c r="G34" s="102" t="str">
+        <v>p-dtg-cdmlap-lb-rule3000</v>
+      </c>
+      <c r="G34" s="82" t="str">
         <f t="shared" ref="G34:G62" si="8">SUBSTITUTE(E34, "hazr-", "")&amp;"-fe"</f>
         <v>p-dtg-cdmlap-lb-fe</v>
       </c>
-      <c r="H34" s="102" t="s">
+      <c r="H34" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="I34" s="102" t="s">
-        <v>1082</v>
-      </c>
-      <c r="J34" s="102" t="b">
+      <c r="I34" s="82">
+        <v>3000</v>
+      </c>
+      <c r="J34" s="82" t="b">
         <v>0</v>
       </c>
-      <c r="K34" s="102" t="str">
+      <c r="K34" s="82" t="str">
         <f t="shared" ref="K34:K62" si="9">SUBSTITUTE(E34, "hazr-", "")&amp;"-bp"</f>
         <v>p-dtg-cdmlap-lb-bp</v>
       </c>
-      <c r="L34" s="102" t="s">
-        <v>1082</v>
-      </c>
-      <c r="M34" s="102" t="str">
+      <c r="L34" s="82">
+        <v>3000</v>
+      </c>
+      <c r="M34" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>p-dtg-cdmlap-lb-pb?</v>
-      </c>
-      <c r="N34" s="102" t="s">
+        <v>p-dtg-cdmlap-lb-pb3000</v>
+      </c>
+      <c r="N34" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="O34" s="102" t="s">
-        <v>1082</v>
-      </c>
-      <c r="P34" s="102">
+      <c r="O34" s="82">
+        <v>3000</v>
+      </c>
+      <c r="P34" s="82">
         <v>4</v>
       </c>
-      <c r="Q34" s="102" t="s">
+      <c r="Q34" s="82" t="s">
         <v>123</v>
       </c>
-      <c r="R34" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="S34" s="102" t="b">
+      <c r="R34" s="82" t="b">
+        <v>1</v>
+      </c>
+      <c r="S34" s="82" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11005,7 +11015,7 @@
         <v>1009</v>
       </c>
       <c r="E37" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F37" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11067,7 +11077,7 @@
         <v>1009</v>
       </c>
       <c r="E38" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F38" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11129,7 +11139,7 @@
         <v>1009</v>
       </c>
       <c r="E39" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F39" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11191,7 +11201,7 @@
         <v>1009</v>
       </c>
       <c r="E40" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F40" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11253,7 +11263,7 @@
         <v>1009</v>
       </c>
       <c r="E41" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F41" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11377,7 +11387,7 @@
         <v>1009</v>
       </c>
       <c r="E43" s="82" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="F43" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11501,7 +11511,7 @@
         <v>1009</v>
       </c>
       <c r="E45" s="82" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F45" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11625,7 +11635,7 @@
         <v>1010</v>
       </c>
       <c r="E47" s="82" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="F47" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11873,7 +11883,7 @@
         <v>1011</v>
       </c>
       <c r="E51" s="82" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F51" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11935,7 +11945,7 @@
         <v>1011</v>
       </c>
       <c r="E52" s="82" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F52" s="82" t="str">
         <f t="shared" si="6"/>
@@ -11986,7 +11996,7 @@
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B53" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C53" s="102"/>
       <c r="D53" s="102" t="s">
@@ -12007,7 +12017,7 @@
         <v>57</v>
       </c>
       <c r="I53" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="J53" s="102" t="b">
         <v>0</v>
@@ -12017,7 +12027,7 @@
         <v>p-cs-chtap-lb-bp</v>
       </c>
       <c r="L53" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="M53" s="102" t="str">
         <f t="shared" si="7"/>
@@ -12027,7 +12037,7 @@
         <v>57</v>
       </c>
       <c r="O53" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="P53" s="102">
         <v>4</v>
@@ -12044,14 +12054,14 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B54" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C54" s="102"/>
       <c r="D54" s="102" t="s">
         <v>1012</v>
       </c>
       <c r="E54" s="102" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F54" s="102" t="str">
         <f t="shared" si="6"/>
@@ -12065,7 +12075,7 @@
         <v>57</v>
       </c>
       <c r="I54" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="J54" s="102" t="b">
         <v>0</v>
@@ -12075,7 +12085,7 @@
         <v>p-cs-chtweb-lb-bp</v>
       </c>
       <c r="L54" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="M54" s="102" t="str">
         <f t="shared" si="7"/>
@@ -12085,7 +12095,7 @@
         <v>57</v>
       </c>
       <c r="O54" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="P54" s="102">
         <v>4</v>
@@ -12102,7 +12112,7 @@
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B55" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C55" s="102"/>
       <c r="D55" s="102" t="s">
@@ -12123,7 +12133,7 @@
         <v>57</v>
       </c>
       <c r="I55" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="J55" s="102" t="b">
         <v>0</v>
@@ -12133,7 +12143,7 @@
         <v>p-cs-chtintweb-lb-bp</v>
       </c>
       <c r="L55" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="M55" s="102" t="str">
         <f t="shared" si="7"/>
@@ -12143,7 +12153,7 @@
         <v>57</v>
       </c>
       <c r="O55" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="P55" s="102">
         <v>4</v>
@@ -12160,14 +12170,14 @@
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B56" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C56" s="102"/>
       <c r="D56" s="102" t="s">
         <v>1013</v>
       </c>
       <c r="E56" s="102" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="F56" s="102" t="str">
         <f t="shared" si="6"/>
@@ -12181,7 +12191,7 @@
         <v>57</v>
       </c>
       <c r="I56" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="J56" s="102" t="b">
         <v>0</v>
@@ -12191,7 +12201,7 @@
         <v>p-doip-web-lb-bp</v>
       </c>
       <c r="L56" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="M56" s="102" t="str">
         <f t="shared" si="7"/>
@@ -12201,7 +12211,7 @@
         <v>57</v>
       </c>
       <c r="O56" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="P56" s="102">
         <v>4</v>
@@ -12218,7 +12228,7 @@
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B57" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C57" s="102"/>
       <c r="D57" s="102" t="s">
@@ -12239,7 +12249,7 @@
         <v>57</v>
       </c>
       <c r="I57" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="J57" s="102" t="b">
         <v>0</v>
@@ -12249,7 +12259,7 @@
         <v>p-doip-ap-lb-bp</v>
       </c>
       <c r="L57" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="M57" s="102" t="str">
         <f t="shared" si="7"/>
@@ -12259,7 +12269,7 @@
         <v>57</v>
       </c>
       <c r="O57" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="P57" s="102">
         <v>4</v>
@@ -12276,14 +12286,14 @@
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B58" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C58" s="102"/>
       <c r="D58" s="102" t="s">
         <v>1013</v>
       </c>
       <c r="E58" s="102" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="F58" s="102" t="str">
         <f t="shared" si="6"/>
@@ -12297,7 +12307,7 @@
         <v>57</v>
       </c>
       <c r="I58" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="J58" s="102" t="b">
         <v>0</v>
@@ -12307,7 +12317,7 @@
         <v>p-doip-adm-lb-bp</v>
       </c>
       <c r="L58" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="M58" s="102" t="str">
         <f t="shared" si="7"/>
@@ -12317,7 +12327,7 @@
         <v>57</v>
       </c>
       <c r="O58" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="P58" s="102">
         <v>4</v>
@@ -12941,7 +12951,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" s="112"/>
+      <c r="A2" s="109"/>
       <c r="B2" s="74" t="s">
         <v>23</v>
       </c>
@@ -12980,7 +12990,7 @@
         <v>640</v>
       </c>
       <c r="N2" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O2" s="74" t="str">
         <f t="shared" ref="O2:O6" si="0">SUBSTITUTE(F2,"hazr-","")&amp;"-osdisk"</f>
@@ -13030,7 +13040,7 @@
       <c r="AF2" s="74"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" s="112"/>
+      <c r="A3" s="109"/>
       <c r="B3" s="74" t="s">
         <v>23</v>
       </c>
@@ -13069,7 +13079,7 @@
         <v>640</v>
       </c>
       <c r="N3" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O3" s="74" t="str">
         <f t="shared" si="0"/>
@@ -13158,7 +13168,7 @@
         <v>640</v>
       </c>
       <c r="N4" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O4" s="74" t="str">
         <f t="shared" si="0"/>
@@ -13247,7 +13257,7 @@
         <v>640</v>
       </c>
       <c r="N5" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O5" s="74" t="str">
         <f t="shared" si="0"/>
@@ -13318,7 +13328,7 @@
         <v>499</v>
       </c>
       <c r="H6" s="80" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="I6" s="80">
         <v>2</v>
@@ -13336,7 +13346,7 @@
         <v>640</v>
       </c>
       <c r="N6" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O6" s="74" t="str">
         <f t="shared" si="0"/>
@@ -13407,7 +13417,7 @@
         <v>500</v>
       </c>
       <c r="H7" s="80" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="I7" s="80">
         <v>2</v>
@@ -13425,7 +13435,7 @@
         <v>640</v>
       </c>
       <c r="N7" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O7" s="74" t="str">
         <f>SUBSTITUTE(F7,"hazr-","")&amp;"-osdisk"</f>
@@ -13514,7 +13524,7 @@
         <v>640</v>
       </c>
       <c r="N8" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O8" s="74" t="str">
         <f t="shared" ref="O8:O39" si="2">SUBSTITUTE(F8,"hazr-","")&amp;"-osdisk"</f>
@@ -13603,7 +13613,7 @@
         <v>640</v>
       </c>
       <c r="N9" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O9" s="74" t="str">
         <f t="shared" si="2"/>
@@ -13692,7 +13702,7 @@
         <v>640</v>
       </c>
       <c r="N10" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O10" s="74" t="str">
         <f t="shared" si="2"/>
@@ -13781,7 +13791,7 @@
         <v>640</v>
       </c>
       <c r="N11" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O11" s="74" t="str">
         <f t="shared" si="2"/>
@@ -13870,7 +13880,7 @@
         <v>640</v>
       </c>
       <c r="N12" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O12" s="74" t="str">
         <f t="shared" si="2"/>
@@ -13959,7 +13969,7 @@
         <v>640</v>
       </c>
       <c r="N13" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O13" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14048,7 +14058,7 @@
         <v>640</v>
       </c>
       <c r="N14" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O14" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14137,7 +14147,7 @@
         <v>640</v>
       </c>
       <c r="N15" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O15" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14226,7 +14236,7 @@
         <v>640</v>
       </c>
       <c r="N16" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O16" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14297,7 +14307,7 @@
         <v>510</v>
       </c>
       <c r="H17" s="80" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="I17" s="80">
         <v>2</v>
@@ -14315,7 +14325,7 @@
         <v>640</v>
       </c>
       <c r="N17" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O17" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14386,7 +14396,7 @@
         <v>511</v>
       </c>
       <c r="H18" s="80" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="I18" s="80">
         <v>2</v>
@@ -14404,7 +14414,7 @@
         <v>640</v>
       </c>
       <c r="N18" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O18" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14475,7 +14485,7 @@
         <v>512</v>
       </c>
       <c r="H19" s="80" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="I19" s="80">
         <v>2</v>
@@ -14493,7 +14503,7 @@
         <v>640</v>
       </c>
       <c r="N19" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O19" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14564,7 +14574,7 @@
         <v>513</v>
       </c>
       <c r="H20" s="80" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="I20" s="80">
         <v>2</v>
@@ -14582,7 +14592,7 @@
         <v>640</v>
       </c>
       <c r="N20" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O20" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14671,7 +14681,7 @@
         <v>640</v>
       </c>
       <c r="N21" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O21" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14760,7 +14770,7 @@
         <v>640</v>
       </c>
       <c r="N22" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O22" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14849,7 +14859,7 @@
         <v>640</v>
       </c>
       <c r="N23" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O23" s="74" t="str">
         <f t="shared" si="2"/>
@@ -14938,7 +14948,7 @@
         <v>640</v>
       </c>
       <c r="N24" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O24" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15027,7 +15037,7 @@
         <v>640</v>
       </c>
       <c r="N25" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O25" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15116,7 +15126,7 @@
         <v>640</v>
       </c>
       <c r="N26" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O26" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15205,7 +15215,7 @@
         <v>640</v>
       </c>
       <c r="N27" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O27" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15294,7 +15304,7 @@
         <v>640</v>
       </c>
       <c r="N28" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O28" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15383,7 +15393,7 @@
         <v>640</v>
       </c>
       <c r="N29" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O29" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15472,7 +15482,7 @@
         <v>640</v>
       </c>
       <c r="N30" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O30" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15561,7 +15571,7 @@
         <v>640</v>
       </c>
       <c r="N31" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O31" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15650,7 +15660,7 @@
         <v>640</v>
       </c>
       <c r="N32" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O32" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15739,7 +15749,7 @@
         <v>640</v>
       </c>
       <c r="N33" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O33" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15828,7 +15838,7 @@
         <v>640</v>
       </c>
       <c r="N34" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O34" s="74" t="str">
         <f t="shared" si="2"/>
@@ -15917,7 +15927,7 @@
         <v>641</v>
       </c>
       <c r="N35" s="98" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="O35" s="74" t="str">
         <f t="shared" si="2"/>
@@ -16006,7 +16016,7 @@
         <v>640</v>
       </c>
       <c r="N36" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O36" s="74" t="str">
         <f t="shared" si="2"/>
@@ -16095,7 +16105,7 @@
         <v>640</v>
       </c>
       <c r="N37" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O37" s="74" t="str">
         <f t="shared" si="2"/>
@@ -16184,7 +16194,7 @@
         <v>640</v>
       </c>
       <c r="N38" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O38" s="74" t="str">
         <f t="shared" si="2"/>
@@ -16273,7 +16283,7 @@
         <v>640</v>
       </c>
       <c r="N39" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O39" s="74" t="str">
         <f t="shared" si="2"/>
@@ -16362,7 +16372,7 @@
         <v>640</v>
       </c>
       <c r="N40" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O40" s="74" t="str">
         <f t="shared" ref="O40:O64" si="3">SUBSTITUTE(F40,"hazr-","")&amp;"-osdisk"</f>
@@ -16451,7 +16461,7 @@
         <v>640</v>
       </c>
       <c r="N41" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O41" s="74" t="str">
         <f t="shared" si="3"/>
@@ -16540,7 +16550,7 @@
         <v>640</v>
       </c>
       <c r="N42" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O42" s="74" t="str">
         <f t="shared" si="3"/>
@@ -16629,7 +16639,7 @@
         <v>640</v>
       </c>
       <c r="N43" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O43" s="74" t="str">
         <f t="shared" si="3"/>
@@ -16718,7 +16728,7 @@
         <v>640</v>
       </c>
       <c r="N44" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O44" s="74" t="str">
         <f t="shared" si="3"/>
@@ -16807,7 +16817,7 @@
         <v>640</v>
       </c>
       <c r="N45" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O45" s="74" t="str">
         <f t="shared" si="3"/>
@@ -16896,7 +16906,7 @@
         <v>640</v>
       </c>
       <c r="N46" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O46" s="74" t="str">
         <f t="shared" si="3"/>
@@ -16985,7 +16995,7 @@
         <v>640</v>
       </c>
       <c r="N47" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O47" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17074,7 +17084,7 @@
         <v>640</v>
       </c>
       <c r="N48" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O48" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17163,7 +17173,7 @@
         <v>640</v>
       </c>
       <c r="N49" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O49" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17252,7 +17262,7 @@
         <v>640</v>
       </c>
       <c r="N50" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O50" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17341,7 +17351,7 @@
         <v>640</v>
       </c>
       <c r="N51" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O51" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17430,7 +17440,7 @@
         <v>640</v>
       </c>
       <c r="N52" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O52" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17519,7 +17529,7 @@
         <v>640</v>
       </c>
       <c r="N53" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O53" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17608,7 +17618,7 @@
         <v>640</v>
       </c>
       <c r="N54" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O54" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17697,7 +17707,7 @@
         <v>640</v>
       </c>
       <c r="N55" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O55" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17786,7 +17796,7 @@
         <v>640</v>
       </c>
       <c r="N56" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O56" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17875,7 +17885,7 @@
         <v>640</v>
       </c>
       <c r="N57" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O57" s="74" t="str">
         <f t="shared" si="3"/>
@@ -17964,7 +17974,7 @@
         <v>640</v>
       </c>
       <c r="N58" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O58" s="74" t="str">
         <f t="shared" si="3"/>
@@ -18053,7 +18063,7 @@
         <v>640</v>
       </c>
       <c r="N59" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O59" s="74" t="str">
         <f t="shared" si="3"/>
@@ -18142,7 +18152,7 @@
         <v>640</v>
       </c>
       <c r="N60" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O60" s="74" t="str">
         <f t="shared" si="3"/>
@@ -18231,7 +18241,7 @@
         <v>640</v>
       </c>
       <c r="N61" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O61" s="74" t="str">
         <f t="shared" si="3"/>
@@ -18320,7 +18330,7 @@
         <v>640</v>
       </c>
       <c r="N62" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O62" s="74" t="str">
         <f t="shared" si="3"/>
@@ -18409,7 +18419,7 @@
         <v>640</v>
       </c>
       <c r="N63" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O63" s="74" t="str">
         <f t="shared" si="3"/>
@@ -18498,7 +18508,7 @@
         <v>640</v>
       </c>
       <c r="N64" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O64" s="74" t="str">
         <f t="shared" si="3"/>
@@ -18587,7 +18597,7 @@
         <v>640</v>
       </c>
       <c r="N65" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O65" s="74" t="str">
         <f t="shared" ref="O65:O70" si="4">SUBSTITUTE(F65,"hazr-","")&amp;"-osdisk"</f>
@@ -18676,7 +18686,7 @@
         <v>640</v>
       </c>
       <c r="N66" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O66" s="74" t="str">
         <f t="shared" si="4"/>
@@ -18765,7 +18775,7 @@
         <v>640</v>
       </c>
       <c r="N67" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O67" s="74" t="str">
         <f t="shared" si="4"/>
@@ -18854,7 +18864,7 @@
         <v>640</v>
       </c>
       <c r="N68" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O68" s="74" t="str">
         <f t="shared" si="4"/>
@@ -18943,7 +18953,7 @@
         <v>640</v>
       </c>
       <c r="N69" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O69" s="74" t="str">
         <f t="shared" si="4"/>
@@ -19032,7 +19042,7 @@
         <v>640</v>
       </c>
       <c r="N70" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O70" s="74" t="str">
         <f t="shared" si="4"/>
@@ -19121,7 +19131,7 @@
         <v>640</v>
       </c>
       <c r="N71" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O71" s="74" t="str">
         <f t="shared" ref="O71:O102" si="6">SUBSTITUTE(F71,"hazr-","")&amp;"-osdisk"</f>
@@ -19210,7 +19220,7 @@
         <v>640</v>
       </c>
       <c r="N72" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O72" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19299,7 +19309,7 @@
         <v>640</v>
       </c>
       <c r="N73" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O73" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19388,7 +19398,7 @@
         <v>640</v>
       </c>
       <c r="N74" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O74" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19477,7 +19487,7 @@
         <v>640</v>
       </c>
       <c r="N75" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O75" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19566,7 +19576,7 @@
         <v>640</v>
       </c>
       <c r="N76" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O76" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19655,7 +19665,7 @@
         <v>640</v>
       </c>
       <c r="N77" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O77" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19744,7 +19754,7 @@
         <v>640</v>
       </c>
       <c r="N78" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O78" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19833,7 +19843,7 @@
         <v>640</v>
       </c>
       <c r="N79" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O79" s="74" t="str">
         <f t="shared" si="6"/>
@@ -19922,7 +19932,7 @@
         <v>640</v>
       </c>
       <c r="N80" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O80" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20011,7 +20021,7 @@
         <v>640</v>
       </c>
       <c r="N81" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O81" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20100,7 +20110,7 @@
         <v>640</v>
       </c>
       <c r="N82" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O82" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20189,7 +20199,7 @@
         <v>640</v>
       </c>
       <c r="N83" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O83" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20278,7 +20288,7 @@
         <v>640</v>
       </c>
       <c r="N84" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O84" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20367,7 +20377,7 @@
         <v>640</v>
       </c>
       <c r="N85" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O85" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20456,7 +20466,7 @@
         <v>640</v>
       </c>
       <c r="N86" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O86" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20545,7 +20555,7 @@
         <v>640</v>
       </c>
       <c r="N87" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O87" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20634,7 +20644,7 @@
         <v>640</v>
       </c>
       <c r="N88" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O88" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20702,7 +20712,7 @@
         <v>438</v>
       </c>
       <c r="G89" s="80" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H89" s="80" t="s">
         <v>638</v>
@@ -20723,7 +20733,7 @@
         <v>640</v>
       </c>
       <c r="N89" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O89" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20812,7 +20822,7 @@
         <v>640</v>
       </c>
       <c r="N90" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O90" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20901,7 +20911,7 @@
         <v>640</v>
       </c>
       <c r="N91" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O91" s="74" t="str">
         <f t="shared" si="6"/>
@@ -20990,7 +21000,7 @@
         <v>640</v>
       </c>
       <c r="N92" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O92" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21079,7 +21089,7 @@
         <v>640</v>
       </c>
       <c r="N93" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O93" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21168,7 +21178,7 @@
         <v>640</v>
       </c>
       <c r="N94" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O94" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21257,7 +21267,7 @@
         <v>640</v>
       </c>
       <c r="N95" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O95" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21346,7 +21356,7 @@
         <v>640</v>
       </c>
       <c r="N96" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O96" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21435,7 +21445,7 @@
         <v>640</v>
       </c>
       <c r="N97" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O97" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21524,7 +21534,7 @@
         <v>640</v>
       </c>
       <c r="N98" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O98" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21613,7 +21623,7 @@
         <v>640</v>
       </c>
       <c r="N99" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O99" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21702,7 +21712,7 @@
         <v>640</v>
       </c>
       <c r="N100" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O100" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21791,7 +21801,7 @@
         <v>640</v>
       </c>
       <c r="N101" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O101" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21880,7 +21890,7 @@
         <v>640</v>
       </c>
       <c r="N102" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O102" s="74" t="str">
         <f t="shared" si="6"/>
@@ -21969,7 +21979,7 @@
         <v>640</v>
       </c>
       <c r="N103" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O103" s="74" t="str">
         <f t="shared" ref="O103:O134" si="8">SUBSTITUTE(F103,"hazr-","")&amp;"-osdisk"</f>
@@ -22058,7 +22068,7 @@
         <v>640</v>
       </c>
       <c r="N104" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O104" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22147,7 +22157,7 @@
         <v>640</v>
       </c>
       <c r="N105" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O105" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22236,7 +22246,7 @@
         <v>640</v>
       </c>
       <c r="N106" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O106" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22325,7 +22335,7 @@
         <v>640</v>
       </c>
       <c r="N107" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O107" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22414,7 +22424,7 @@
         <v>640</v>
       </c>
       <c r="N108" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O108" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22503,7 +22513,7 @@
         <v>640</v>
       </c>
       <c r="N109" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O109" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22592,7 +22602,7 @@
         <v>640</v>
       </c>
       <c r="N110" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O110" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22681,7 +22691,7 @@
         <v>640</v>
       </c>
       <c r="N111" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O111" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22770,7 +22780,7 @@
         <v>640</v>
       </c>
       <c r="N112" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O112" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22859,7 +22869,7 @@
         <v>640</v>
       </c>
       <c r="N113" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O113" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22948,7 +22958,7 @@
         <v>640</v>
       </c>
       <c r="N114" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O114" s="74" t="str">
         <f t="shared" si="8"/>
@@ -22998,170 +23008,182 @@
       <c r="AF114" s="74"/>
     </row>
     <row r="115" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B115" s="102" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C115" s="102"/>
-      <c r="D115" s="104" t="s">
+      <c r="A115" s="90"/>
+      <c r="B115" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="C115" s="74" t="str" cm="1">
+        <f t="array" ref="C115">UPPER(INDEX(_xlfn.TEXTSPLIT($D115, "-"), 3))</f>
+        <v>IF</v>
+      </c>
+      <c r="D115" s="74" t="s">
         <v>323</v>
       </c>
-      <c r="E115" s="102" t="s">
+      <c r="E115" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F115" s="102" t="s">
+      <c r="F115" s="74" t="s">
         <v>464</v>
       </c>
-      <c r="G115" s="104" t="s">
+      <c r="G115" s="74" t="s">
         <v>607</v>
       </c>
-      <c r="H115" s="104" t="s">
+      <c r="H115" s="74" t="s">
         <v>630</v>
       </c>
-      <c r="I115" s="104">
+      <c r="I115" s="74">
         <v>2</v>
       </c>
-      <c r="J115" s="104">
+      <c r="J115" s="74">
         <v>8</v>
       </c>
-      <c r="K115" s="102" t="s">
+      <c r="K115" s="74" t="s">
         <v>181</v>
       </c>
-      <c r="L115" s="102" t="s">
+      <c r="L115" s="74" t="s">
         <v>227</v>
       </c>
-      <c r="M115" s="104" t="s">
+      <c r="M115" s="74" t="s">
         <v>640</v>
       </c>
-      <c r="N115" s="105"/>
-      <c r="O115" s="102" t="str">
+      <c r="N115" s="74" t="s">
+        <v>1110</v>
+      </c>
+      <c r="O115" s="74" t="str">
         <f t="shared" si="8"/>
         <v>p-if-proxy01-osdisk</v>
       </c>
-      <c r="P115" s="106">
+      <c r="P115" s="74">
         <v>64</v>
       </c>
-      <c r="Q115" s="102" t="s">
+      <c r="Q115" s="74" t="s">
         <v>180</v>
       </c>
-      <c r="R115" s="102"/>
-      <c r="S115" s="102"/>
-      <c r="T115" s="102"/>
-      <c r="U115" s="102" t="str">
+      <c r="R115" s="74"/>
+      <c r="S115" s="74"/>
+      <c r="T115" s="74"/>
+      <c r="U115" s="74" t="str">
         <f t="shared" si="9"/>
         <v>p-if-proxy01-nic</v>
       </c>
-      <c r="V115" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="W115" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="X115" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="Y115" s="102" t="s">
+      <c r="V115" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="W115" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="X115" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y115" s="74" t="s">
         <v>240</v>
       </c>
-      <c r="Z115" s="102" t="s">
+      <c r="Z115" s="74" t="s">
         <v>249</v>
       </c>
-      <c r="AA115" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB115" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="AC115" s="102" t="s">
+      <c r="AA115" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB115" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="AC115" s="74" t="s">
         <v>327</v>
       </c>
-      <c r="AD115" s="104">
-        <v>1</v>
-      </c>
-      <c r="AE115" s="102"/>
-      <c r="AF115" s="102"/>
+      <c r="AD115" s="74">
+        <v>1</v>
+      </c>
+      <c r="AE115" s="74"/>
+      <c r="AF115" s="74"/>
     </row>
     <row r="116" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B116" s="102" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C116" s="102"/>
-      <c r="D116" s="104" t="s">
+      <c r="A116" s="90"/>
+      <c r="B116" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="C116" s="74" t="str" cm="1">
+        <f t="array" ref="C116">UPPER(INDEX(_xlfn.TEXTSPLIT($D116, "-"), 3))</f>
+        <v>IF</v>
+      </c>
+      <c r="D116" s="74" t="s">
         <v>323</v>
       </c>
-      <c r="E116" s="102" t="s">
+      <c r="E116" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F116" s="102" t="s">
+      <c r="F116" s="74" t="s">
         <v>465</v>
       </c>
-      <c r="G116" s="104" t="s">
+      <c r="G116" s="74" t="s">
         <v>608</v>
       </c>
-      <c r="H116" s="104" t="s">
+      <c r="H116" s="74" t="s">
         <v>630</v>
       </c>
-      <c r="I116" s="104">
+      <c r="I116" s="74">
         <v>2</v>
       </c>
-      <c r="J116" s="104">
+      <c r="J116" s="74">
         <v>8</v>
       </c>
-      <c r="K116" s="102" t="s">
+      <c r="K116" s="74" t="s">
         <v>181</v>
       </c>
-      <c r="L116" s="102" t="s">
+      <c r="L116" s="74" t="s">
         <v>227</v>
       </c>
-      <c r="M116" s="104" t="s">
+      <c r="M116" s="74" t="s">
         <v>640</v>
       </c>
-      <c r="N116" s="105"/>
-      <c r="O116" s="102" t="str">
+      <c r="N116" s="74" t="s">
+        <v>1088</v>
+      </c>
+      <c r="O116" s="74" t="str">
         <f t="shared" si="8"/>
         <v>p-if-proxy02-osdisk</v>
       </c>
-      <c r="P116" s="106">
+      <c r="P116" s="74">
         <v>64</v>
       </c>
-      <c r="Q116" s="102" t="s">
+      <c r="Q116" s="74" t="s">
         <v>180</v>
       </c>
-      <c r="R116" s="102"/>
-      <c r="S116" s="102"/>
-      <c r="T116" s="102"/>
-      <c r="U116" s="102" t="str">
+      <c r="R116" s="74"/>
+      <c r="S116" s="74"/>
+      <c r="T116" s="74"/>
+      <c r="U116" s="74" t="str">
         <f t="shared" si="9"/>
         <v>p-if-proxy02-nic</v>
       </c>
-      <c r="V116" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="W116" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="X116" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="Y116" s="102" t="s">
+      <c r="V116" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="W116" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="X116" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y116" s="74" t="s">
         <v>240</v>
       </c>
-      <c r="Z116" s="102" t="s">
+      <c r="Z116" s="74" t="s">
         <v>249</v>
       </c>
-      <c r="AA116" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB116" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="AC116" s="102" t="s">
+      <c r="AA116" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB116" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="AC116" s="74" t="s">
         <v>327</v>
       </c>
-      <c r="AD116" s="104">
+      <c r="AD116" s="74">
         <v>2</v>
       </c>
-      <c r="AE116" s="102"/>
-      <c r="AF116" s="102"/>
+      <c r="AE116" s="74"/>
+      <c r="AF116" s="74"/>
     </row>
     <row r="117" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A117" s="90"/>
@@ -23185,7 +23207,7 @@
         <v>609</v>
       </c>
       <c r="H117" s="80" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="I117" s="80">
         <v>2</v>
@@ -23203,7 +23225,7 @@
         <v>640</v>
       </c>
       <c r="N117" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O117" s="74" t="str">
         <f t="shared" si="8"/>
@@ -23292,7 +23314,7 @@
         <v>640</v>
       </c>
       <c r="N118" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O118" s="74" t="str">
         <f t="shared" si="8"/>
@@ -23342,92 +23364,98 @@
       <c r="AF118" s="74"/>
     </row>
     <row r="119" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B119" s="102" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C119" s="102"/>
-      <c r="D119" s="104" t="s">
+      <c r="A119" s="90"/>
+      <c r="B119" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="C119" s="74" t="str" cm="1">
+        <f t="array" ref="C119">UPPER(INDEX(_xlfn.TEXTSPLIT($D119, "-"), 3))</f>
+        <v>IF</v>
+      </c>
+      <c r="D119" s="80" t="s">
         <v>323</v>
       </c>
-      <c r="E119" s="102" t="s">
+      <c r="E119" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F119" s="102" t="s">
+      <c r="F119" s="74" t="s">
         <v>468</v>
       </c>
-      <c r="G119" s="104" t="s">
+      <c r="G119" s="80" t="s">
         <v>611</v>
       </c>
-      <c r="H119" s="104" t="s">
-        <v>633</v>
-      </c>
-      <c r="I119" s="104">
+      <c r="H119" s="80" t="s">
+        <v>1111</v>
+      </c>
+      <c r="I119" s="80">
         <v>4</v>
       </c>
-      <c r="J119" s="104">
+      <c r="J119" s="80">
         <v>16</v>
       </c>
-      <c r="K119" s="102" t="s">
+      <c r="K119" s="74" t="s">
         <v>181</v>
       </c>
-      <c r="L119" s="102" t="s">
+      <c r="L119" s="74" t="s">
         <v>227</v>
       </c>
-      <c r="M119" s="104" t="s">
+      <c r="M119" s="80" t="s">
         <v>640</v>
       </c>
-      <c r="N119" s="105"/>
-      <c r="O119" s="102" t="str">
+      <c r="N119" s="98" t="s">
+        <v>1088</v>
+      </c>
+      <c r="O119" s="74" t="str">
         <f t="shared" si="8"/>
         <v>p-if-stryweb01-osdisk</v>
       </c>
-      <c r="P119" s="106">
+      <c r="P119" s="97">
         <v>64</v>
       </c>
-      <c r="Q119" s="102" t="s">
+      <c r="Q119" s="74" t="s">
         <v>180</v>
       </c>
-      <c r="R119" s="102"/>
-      <c r="S119" s="102"/>
-      <c r="T119" s="102"/>
-      <c r="U119" s="102" t="str">
+      <c r="R119" s="74"/>
+      <c r="S119" s="74"/>
+      <c r="T119" s="74"/>
+      <c r="U119" s="74" t="str">
         <f t="shared" si="9"/>
         <v>p-if-stryweb01-nic</v>
       </c>
-      <c r="V119" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="W119" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="X119" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="Y119" s="102" t="s">
+      <c r="V119" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="W119" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="X119" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y119" s="74" t="s">
         <v>241</v>
       </c>
-      <c r="Z119" s="102" t="s">
+      <c r="Z119" s="74" t="s">
         <v>272</v>
       </c>
-      <c r="AA119" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB119" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="AC119" s="102" t="s">
+      <c r="AA119" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB119" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="AC119" s="74" t="s">
         <v>327</v>
       </c>
-      <c r="AD119" s="104">
-        <v>1</v>
-      </c>
-      <c r="AE119" s="102"/>
-      <c r="AF119" s="102"/>
+      <c r="AD119" s="80">
+        <v>1</v>
+      </c>
+      <c r="AE119" s="74"/>
+      <c r="AF119" s="74"/>
     </row>
     <row r="120" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A120" s="90"/>
       <c r="B120" s="74" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C120" s="74" t="str" cm="1">
         <f t="array" ref="C120">UPPER(INDEX(_xlfn.TEXTSPLIT($D120, "-"), 3))</f>
@@ -23464,7 +23492,7 @@
         <v>640</v>
       </c>
       <c r="N120" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O120" s="74" t="str">
         <f t="shared" si="8"/>
@@ -23516,7 +23544,7 @@
     <row r="121" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A121" s="90"/>
       <c r="B121" s="74" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C121" s="74" t="str" cm="1">
         <f t="array" ref="C121">UPPER(INDEX(_xlfn.TEXTSPLIT($D121, "-"), 3))</f>
@@ -23553,7 +23581,7 @@
         <v>640</v>
       </c>
       <c r="N121" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O121" s="74" t="str">
         <f t="shared" si="8"/>
@@ -23605,7 +23633,7 @@
     <row r="122" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A122" s="90"/>
       <c r="B122" s="74" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C122" s="74" t="str" cm="1">
         <f t="array" ref="C122">UPPER(INDEX(_xlfn.TEXTSPLIT($D122, "-"), 3))</f>
@@ -23642,7 +23670,7 @@
         <v>640</v>
       </c>
       <c r="N122" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O122" s="74" t="str">
         <f t="shared" si="8"/>
@@ -23731,7 +23759,7 @@
         <v>640</v>
       </c>
       <c r="N123" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O123" s="74" t="str">
         <f t="shared" si="8"/>
@@ -23782,7 +23810,7 @@
     </row>
     <row r="124" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B124" s="102" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C124" s="102"/>
       <c r="D124" s="102" t="s">
@@ -23795,10 +23823,10 @@
         <v>470</v>
       </c>
       <c r="G124" s="102" t="s">
+        <v>1093</v>
+      </c>
+      <c r="H124" s="102" t="s">
         <v>1094</v>
-      </c>
-      <c r="H124" s="102" t="s">
-        <v>1095</v>
       </c>
       <c r="I124" s="102">
         <v>2</v>
@@ -23813,7 +23841,7 @@
         <v>179</v>
       </c>
       <c r="M124" s="102" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="N124" s="102"/>
       <c r="O124" s="102" t="str">
@@ -23865,7 +23893,7 @@
     </row>
     <row r="125" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B125" s="102" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C125" s="102"/>
       <c r="D125" s="102" t="s">
@@ -23878,10 +23906,10 @@
         <v>471</v>
       </c>
       <c r="G125" s="102" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H125" s="102" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="I125" s="102">
         <v>2</v>
@@ -23896,7 +23924,7 @@
         <v>179</v>
       </c>
       <c r="M125" s="102" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="N125" s="102"/>
       <c r="O125" s="102" t="str">
@@ -23986,7 +24014,7 @@
         <v>640</v>
       </c>
       <c r="N126" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O126" s="74" t="str">
         <f t="shared" si="8"/>
@@ -24075,7 +24103,7 @@
         <v>640</v>
       </c>
       <c r="N127" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O127" s="74" t="str">
         <f t="shared" si="8"/>
@@ -24164,7 +24192,7 @@
         <v>640</v>
       </c>
       <c r="N128" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O128" s="74" t="str">
         <f t="shared" si="8"/>
@@ -24253,7 +24281,7 @@
         <v>640</v>
       </c>
       <c r="N129" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O129" s="74" t="str">
         <f t="shared" si="8"/>
@@ -24342,7 +24370,7 @@
         <v>640</v>
       </c>
       <c r="N130" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O130" s="74" t="str">
         <f t="shared" si="8"/>
@@ -24431,7 +24459,7 @@
         <v>640</v>
       </c>
       <c r="N131" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O131" s="74" t="str">
         <f t="shared" si="8"/>
@@ -24481,502 +24509,538 @@
       <c r="AF131" s="74"/>
     </row>
     <row r="132" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B132" s="102" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C132" s="102"/>
-      <c r="D132" s="102" t="s">
+      <c r="A132" s="90"/>
+      <c r="B132" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="C132" s="74" t="str" cm="1">
+        <f t="array" ref="C132">UPPER(INDEX(_xlfn.TEXTSPLIT($D132, "-"), 3))</f>
+        <v>DOIP</v>
+      </c>
+      <c r="D132" s="74" t="s">
         <v>1013</v>
       </c>
-      <c r="E132" s="102" t="s">
+      <c r="E132" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F132" s="102" t="s">
+      <c r="F132" s="74" t="s">
         <v>478</v>
       </c>
-      <c r="G132" s="102" t="s">
-        <v>1098</v>
-      </c>
-      <c r="H132" s="102" t="s">
+      <c r="G132" s="74" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H132" s="74" t="s">
+        <v>1094</v>
+      </c>
+      <c r="I132" s="74">
+        <v>2</v>
+      </c>
+      <c r="J132" s="74">
+        <v>16</v>
+      </c>
+      <c r="K132" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="L132" s="74" t="s">
+        <v>179</v>
+      </c>
+      <c r="M132" s="74" t="s">
         <v>1095</v>
       </c>
-      <c r="I132" s="102">
-        <v>2</v>
-      </c>
-      <c r="J132" s="102">
-        <v>16</v>
-      </c>
-      <c r="K132" s="102" t="s">
-        <v>181</v>
-      </c>
-      <c r="L132" s="102" t="s">
-        <v>179</v>
-      </c>
-      <c r="M132" s="102" t="s">
-        <v>1096</v>
-      </c>
-      <c r="N132" s="102"/>
-      <c r="O132" s="102" t="str">
+      <c r="N132" s="112" t="s">
+        <v>1110</v>
+      </c>
+      <c r="O132" s="74" t="str">
         <f t="shared" si="8"/>
         <v>p-doip-web01-osdisk</v>
       </c>
-      <c r="P132" s="102">
+      <c r="P132" s="74">
         <v>64</v>
       </c>
-      <c r="Q132" s="102" t="s">
+      <c r="Q132" s="74" t="s">
         <v>180</v>
       </c>
-      <c r="R132" s="102"/>
-      <c r="S132" s="102"/>
-      <c r="T132" s="102"/>
-      <c r="U132" s="102" t="str">
+      <c r="R132" s="74"/>
+      <c r="S132" s="74"/>
+      <c r="T132" s="74"/>
+      <c r="U132" s="74" t="str">
         <f t="shared" si="9"/>
         <v>p-doip-web01-nic</v>
       </c>
-      <c r="V132" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="W132" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="X132" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="Y132" s="102" t="s">
+      <c r="V132" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="W132" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="X132" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y132" s="74" t="s">
         <v>347</v>
       </c>
-      <c r="Z132" s="102" t="s">
+      <c r="Z132" s="74" t="s">
         <v>1062</v>
       </c>
-      <c r="AA132" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB132" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="AC132" s="102" t="s">
+      <c r="AA132" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB132" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="AC132" s="74" t="s">
         <v>327</v>
       </c>
-      <c r="AD132" s="102">
-        <v>1</v>
-      </c>
-      <c r="AE132" s="102"/>
-      <c r="AF132" s="102"/>
+      <c r="AD132" s="74">
+        <v>1</v>
+      </c>
+      <c r="AE132" s="74"/>
+      <c r="AF132" s="74"/>
     </row>
     <row r="133" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B133" s="102" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C133" s="102"/>
-      <c r="D133" s="102" t="s">
+      <c r="A133" s="90"/>
+      <c r="B133" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="C133" s="74" t="str" cm="1">
+        <f t="array" ref="C133">UPPER(INDEX(_xlfn.TEXTSPLIT($D133, "-"), 3))</f>
+        <v>DOIP</v>
+      </c>
+      <c r="D133" s="74" t="s">
         <v>1013</v>
       </c>
-      <c r="E133" s="102" t="s">
+      <c r="E133" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F133" s="102" t="s">
+      <c r="F133" s="74" t="s">
         <v>479</v>
       </c>
-      <c r="G133" s="102" t="s">
-        <v>1099</v>
-      </c>
-      <c r="H133" s="102" t="s">
+      <c r="G133" s="74" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H133" s="74" t="s">
+        <v>1094</v>
+      </c>
+      <c r="I133" s="74">
+        <v>2</v>
+      </c>
+      <c r="J133" s="74">
+        <v>16</v>
+      </c>
+      <c r="K133" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="L133" s="74" t="s">
+        <v>179</v>
+      </c>
+      <c r="M133" s="74" t="s">
         <v>1095</v>
       </c>
-      <c r="I133" s="102">
-        <v>2</v>
-      </c>
-      <c r="J133" s="102">
-        <v>16</v>
-      </c>
-      <c r="K133" s="102" t="s">
-        <v>181</v>
-      </c>
-      <c r="L133" s="102" t="s">
-        <v>179</v>
-      </c>
-      <c r="M133" s="102" t="s">
-        <v>1096</v>
-      </c>
-      <c r="N133" s="102"/>
-      <c r="O133" s="102" t="str">
+      <c r="N133" s="112" t="s">
+        <v>1110</v>
+      </c>
+      <c r="O133" s="74" t="str">
         <f t="shared" si="8"/>
         <v>p-doip-web02-osdisk</v>
       </c>
-      <c r="P133" s="102">
+      <c r="P133" s="74">
         <v>64</v>
       </c>
-      <c r="Q133" s="102" t="s">
+      <c r="Q133" s="74" t="s">
         <v>180</v>
       </c>
-      <c r="R133" s="102"/>
-      <c r="S133" s="102"/>
-      <c r="T133" s="102"/>
-      <c r="U133" s="102" t="str">
+      <c r="R133" s="74"/>
+      <c r="S133" s="74"/>
+      <c r="T133" s="74"/>
+      <c r="U133" s="74" t="str">
         <f t="shared" si="9"/>
         <v>p-doip-web02-nic</v>
       </c>
-      <c r="V133" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="W133" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="X133" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="Y133" s="102" t="s">
+      <c r="V133" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="W133" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="X133" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y133" s="74" t="s">
         <v>347</v>
       </c>
-      <c r="Z133" s="102" t="s">
+      <c r="Z133" s="74" t="s">
         <v>1062</v>
       </c>
-      <c r="AA133" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB133" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="AC133" s="102" t="s">
+      <c r="AA133" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB133" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="AC133" s="74" t="s">
         <v>327</v>
       </c>
-      <c r="AD133" s="102">
+      <c r="AD133" s="74">
         <v>2</v>
       </c>
-      <c r="AE133" s="102"/>
-      <c r="AF133" s="102"/>
+      <c r="AE133" s="74"/>
+      <c r="AF133" s="74"/>
     </row>
     <row r="134" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B134" s="102" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C134" s="102"/>
-      <c r="D134" s="102" t="s">
+      <c r="A134" s="90"/>
+      <c r="B134" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="C134" s="74" t="str" cm="1">
+        <f t="array" ref="C134">UPPER(INDEX(_xlfn.TEXTSPLIT($D134, "-"), 3))</f>
+        <v>DOIP</v>
+      </c>
+      <c r="D134" s="74" t="s">
         <v>1013</v>
       </c>
-      <c r="E134" s="102" t="s">
+      <c r="E134" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F134" s="102" t="s">
+      <c r="F134" s="74" t="s">
         <v>480</v>
       </c>
-      <c r="G134" s="102" t="s">
-        <v>1100</v>
-      </c>
-      <c r="H134" s="102" t="s">
+      <c r="G134" s="74" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H134" s="74" t="s">
+        <v>1094</v>
+      </c>
+      <c r="I134" s="74">
+        <v>2</v>
+      </c>
+      <c r="J134" s="74">
+        <v>16</v>
+      </c>
+      <c r="K134" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="L134" s="74" t="s">
+        <v>179</v>
+      </c>
+      <c r="M134" s="74" t="s">
         <v>1095</v>
       </c>
-      <c r="I134" s="102">
-        <v>2</v>
-      </c>
-      <c r="J134" s="102">
-        <v>16</v>
-      </c>
-      <c r="K134" s="102" t="s">
-        <v>181</v>
-      </c>
-      <c r="L134" s="102" t="s">
-        <v>179</v>
-      </c>
-      <c r="M134" s="102" t="s">
-        <v>1096</v>
-      </c>
-      <c r="N134" s="102"/>
-      <c r="O134" s="102" t="str">
+      <c r="N134" s="112" t="s">
+        <v>1112</v>
+      </c>
+      <c r="O134" s="74" t="str">
         <f t="shared" si="8"/>
         <v>p-doip-ap01-osdisk</v>
       </c>
-      <c r="P134" s="102">
+      <c r="P134" s="74">
         <v>64</v>
       </c>
-      <c r="Q134" s="102" t="s">
+      <c r="Q134" s="74" t="s">
         <v>180</v>
       </c>
-      <c r="R134" s="102"/>
-      <c r="S134" s="102"/>
-      <c r="T134" s="102"/>
-      <c r="U134" s="102" t="str">
+      <c r="R134" s="74"/>
+      <c r="S134" s="74"/>
+      <c r="T134" s="74"/>
+      <c r="U134" s="74" t="str">
         <f t="shared" si="9"/>
         <v>p-doip-ap01-nic</v>
       </c>
-      <c r="V134" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="W134" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="X134" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="Y134" s="102" t="s">
+      <c r="V134" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="W134" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="X134" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y134" s="74" t="s">
         <v>347</v>
       </c>
-      <c r="Z134" s="102" t="s">
+      <c r="Z134" s="74" t="s">
         <v>1062</v>
       </c>
-      <c r="AA134" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB134" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="AC134" s="102" t="s">
+      <c r="AA134" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB134" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="AC134" s="74" t="s">
         <v>327</v>
       </c>
-      <c r="AD134" s="102">
-        <v>1</v>
-      </c>
-      <c r="AE134" s="102"/>
-      <c r="AF134" s="102"/>
+      <c r="AD134" s="74">
+        <v>1</v>
+      </c>
+      <c r="AE134" s="74"/>
+      <c r="AF134" s="74"/>
     </row>
     <row r="135" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B135" s="102" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C135" s="102"/>
-      <c r="D135" s="102" t="s">
+      <c r="A135" s="90"/>
+      <c r="B135" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="C135" s="74" t="str" cm="1">
+        <f t="array" ref="C135">UPPER(INDEX(_xlfn.TEXTSPLIT($D135, "-"), 3))</f>
+        <v>DOIP</v>
+      </c>
+      <c r="D135" s="74" t="s">
         <v>1013</v>
       </c>
-      <c r="E135" s="102" t="s">
+      <c r="E135" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F135" s="102" t="s">
+      <c r="F135" s="74" t="s">
         <v>481</v>
       </c>
-      <c r="G135" s="102" t="s">
-        <v>1101</v>
-      </c>
-      <c r="H135" s="102" t="s">
+      <c r="G135" s="74" t="s">
+        <v>1100</v>
+      </c>
+      <c r="H135" s="74" t="s">
+        <v>1094</v>
+      </c>
+      <c r="I135" s="74">
+        <v>2</v>
+      </c>
+      <c r="J135" s="74">
+        <v>16</v>
+      </c>
+      <c r="K135" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="L135" s="74" t="s">
+        <v>179</v>
+      </c>
+      <c r="M135" s="74" t="s">
         <v>1095</v>
       </c>
-      <c r="I135" s="102">
-        <v>2</v>
-      </c>
-      <c r="J135" s="102">
-        <v>16</v>
-      </c>
-      <c r="K135" s="102" t="s">
-        <v>181</v>
-      </c>
-      <c r="L135" s="102" t="s">
-        <v>179</v>
-      </c>
-      <c r="M135" s="102" t="s">
-        <v>1096</v>
-      </c>
-      <c r="N135" s="102"/>
-      <c r="O135" s="102" t="str">
+      <c r="N135" s="112" t="s">
+        <v>1112</v>
+      </c>
+      <c r="O135" s="74" t="str">
         <f t="shared" ref="O135:O146" si="10">SUBSTITUTE(F135,"hazr-","")&amp;"-osdisk"</f>
         <v>p-doip-ap02-osdisk</v>
       </c>
-      <c r="P135" s="102">
+      <c r="P135" s="74">
         <v>64</v>
       </c>
-      <c r="Q135" s="102" t="s">
+      <c r="Q135" s="74" t="s">
         <v>180</v>
       </c>
-      <c r="R135" s="102"/>
-      <c r="S135" s="102"/>
-      <c r="T135" s="102"/>
-      <c r="U135" s="102" t="str">
+      <c r="R135" s="74"/>
+      <c r="S135" s="74"/>
+      <c r="T135" s="74"/>
+      <c r="U135" s="74" t="str">
         <f t="shared" ref="U135:U146" si="11">SUBSTITUTE(F135,"hazr-","")&amp;"-nic"</f>
         <v>p-doip-ap02-nic</v>
       </c>
-      <c r="V135" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="W135" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="X135" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="Y135" s="102" t="s">
+      <c r="V135" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="W135" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="X135" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y135" s="74" t="s">
         <v>347</v>
       </c>
-      <c r="Z135" s="102" t="s">
+      <c r="Z135" s="74" t="s">
         <v>1062</v>
       </c>
-      <c r="AA135" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB135" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="AC135" s="102" t="s">
+      <c r="AA135" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB135" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="AC135" s="74" t="s">
         <v>327</v>
       </c>
-      <c r="AD135" s="102">
+      <c r="AD135" s="74">
         <v>2</v>
       </c>
-      <c r="AE135" s="102"/>
-      <c r="AF135" s="102"/>
+      <c r="AE135" s="74"/>
+      <c r="AF135" s="74"/>
     </row>
     <row r="136" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B136" s="102" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C136" s="102"/>
-      <c r="D136" s="102" t="s">
+      <c r="A136" s="90"/>
+      <c r="B136" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="C136" s="74" t="str" cm="1">
+        <f t="array" ref="C136">UPPER(INDEX(_xlfn.TEXTSPLIT($D136, "-"), 3))</f>
+        <v>DOIP</v>
+      </c>
+      <c r="D136" s="74" t="s">
         <v>1013</v>
       </c>
-      <c r="E136" s="102" t="s">
+      <c r="E136" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F136" s="102" t="s">
+      <c r="F136" s="74" t="s">
         <v>482</v>
       </c>
-      <c r="G136" s="102" t="s">
-        <v>1102</v>
-      </c>
-      <c r="H136" s="102" t="s">
+      <c r="G136" s="74" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H136" s="74" t="s">
+        <v>1094</v>
+      </c>
+      <c r="I136" s="74">
+        <v>2</v>
+      </c>
+      <c r="J136" s="74">
+        <v>16</v>
+      </c>
+      <c r="K136" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="L136" s="74" t="s">
+        <v>179</v>
+      </c>
+      <c r="M136" s="74" t="s">
         <v>1095</v>
       </c>
-      <c r="I136" s="102">
-        <v>2</v>
-      </c>
-      <c r="J136" s="102">
-        <v>16</v>
-      </c>
-      <c r="K136" s="102" t="s">
-        <v>181</v>
-      </c>
-      <c r="L136" s="102" t="s">
-        <v>179</v>
-      </c>
-      <c r="M136" s="102" t="s">
-        <v>1096</v>
-      </c>
-      <c r="N136" s="102"/>
-      <c r="O136" s="102" t="str">
+      <c r="N136" s="112" t="s">
+        <v>1112</v>
+      </c>
+      <c r="O136" s="74" t="str">
         <f t="shared" si="10"/>
         <v>p-doip-adm01-osdisk</v>
       </c>
-      <c r="P136" s="102">
+      <c r="P136" s="74">
         <v>64</v>
       </c>
-      <c r="Q136" s="102" t="s">
+      <c r="Q136" s="74" t="s">
         <v>180</v>
       </c>
-      <c r="R136" s="102"/>
-      <c r="S136" s="102"/>
-      <c r="T136" s="102"/>
-      <c r="U136" s="102" t="str">
+      <c r="R136" s="74"/>
+      <c r="S136" s="74"/>
+      <c r="T136" s="74"/>
+      <c r="U136" s="74" t="str">
         <f t="shared" si="11"/>
         <v>p-doip-adm01-nic</v>
       </c>
-      <c r="V136" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="W136" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="X136" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="Y136" s="102" t="s">
+      <c r="V136" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="W136" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="X136" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y136" s="74" t="s">
         <v>347</v>
       </c>
-      <c r="Z136" s="102" t="s">
+      <c r="Z136" s="74" t="s">
         <v>1062</v>
       </c>
-      <c r="AA136" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB136" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="AC136" s="102" t="s">
+      <c r="AA136" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB136" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="AC136" s="74" t="s">
         <v>327</v>
       </c>
-      <c r="AD136" s="102">
-        <v>1</v>
-      </c>
-      <c r="AE136" s="102"/>
-      <c r="AF136" s="102"/>
+      <c r="AD136" s="74">
+        <v>1</v>
+      </c>
+      <c r="AE136" s="74"/>
+      <c r="AF136" s="74"/>
     </row>
     <row r="137" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B137" s="102" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C137" s="102"/>
-      <c r="D137" s="102" t="s">
+      <c r="A137" s="90"/>
+      <c r="B137" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="C137" s="74" t="str" cm="1">
+        <f t="array" ref="C137">UPPER(INDEX(_xlfn.TEXTSPLIT($D137, "-"), 3))</f>
+        <v>DOIP</v>
+      </c>
+      <c r="D137" s="74" t="s">
         <v>1013</v>
       </c>
-      <c r="E137" s="102" t="s">
+      <c r="E137" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F137" s="102" t="s">
+      <c r="F137" s="74" t="s">
         <v>483</v>
       </c>
-      <c r="G137" s="102" t="s">
-        <v>1103</v>
-      </c>
-      <c r="H137" s="102" t="s">
+      <c r="G137" s="74" t="s">
+        <v>1102</v>
+      </c>
+      <c r="H137" s="74" t="s">
+        <v>1094</v>
+      </c>
+      <c r="I137" s="74">
+        <v>2</v>
+      </c>
+      <c r="J137" s="74">
+        <v>16</v>
+      </c>
+      <c r="K137" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="L137" s="74" t="s">
+        <v>179</v>
+      </c>
+      <c r="M137" s="74" t="s">
         <v>1095</v>
       </c>
-      <c r="I137" s="102">
-        <v>2</v>
-      </c>
-      <c r="J137" s="102">
-        <v>16</v>
-      </c>
-      <c r="K137" s="102" t="s">
-        <v>181</v>
-      </c>
-      <c r="L137" s="102" t="s">
-        <v>179</v>
-      </c>
-      <c r="M137" s="102" t="s">
-        <v>1096</v>
-      </c>
-      <c r="N137" s="102"/>
-      <c r="O137" s="102" t="str">
+      <c r="N137" s="112" t="s">
+        <v>1112</v>
+      </c>
+      <c r="O137" s="74" t="str">
         <f t="shared" si="10"/>
         <v>p-doip-adm02-osdisk</v>
       </c>
-      <c r="P137" s="102">
+      <c r="P137" s="74">
         <v>64</v>
       </c>
-      <c r="Q137" s="102" t="s">
+      <c r="Q137" s="74" t="s">
         <v>180</v>
       </c>
-      <c r="R137" s="102"/>
-      <c r="S137" s="102"/>
-      <c r="T137" s="102"/>
-      <c r="U137" s="102" t="str">
+      <c r="R137" s="74"/>
+      <c r="S137" s="74"/>
+      <c r="T137" s="74"/>
+      <c r="U137" s="74" t="str">
         <f t="shared" si="11"/>
         <v>p-doip-adm02-nic</v>
       </c>
-      <c r="V137" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="W137" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="X137" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="Y137" s="102" t="s">
+      <c r="V137" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="W137" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="X137" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y137" s="74" t="s">
         <v>347</v>
       </c>
-      <c r="Z137" s="102" t="s">
+      <c r="Z137" s="74" t="s">
         <v>1062</v>
       </c>
-      <c r="AA137" s="102" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB137" s="102" t="s">
-        <v>326</v>
-      </c>
-      <c r="AC137" s="102" t="s">
+      <c r="AA137" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB137" s="74" t="s">
+        <v>326</v>
+      </c>
+      <c r="AC137" s="74" t="s">
         <v>327</v>
       </c>
-      <c r="AD137" s="102">
+      <c r="AD137" s="74">
         <v>2</v>
       </c>
-      <c r="AE137" s="102"/>
-      <c r="AF137" s="102"/>
+      <c r="AE137" s="74"/>
+      <c r="AF137" s="74"/>
     </row>
     <row r="138" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A138" s="90"/>
@@ -25018,7 +25082,7 @@
         <v>640</v>
       </c>
       <c r="N138" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O138" s="74" t="str">
         <f t="shared" si="10"/>
@@ -25107,7 +25171,7 @@
         <v>640</v>
       </c>
       <c r="N139" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O139" s="74" t="str">
         <f t="shared" si="10"/>
@@ -25196,7 +25260,7 @@
         <v>640</v>
       </c>
       <c r="N140" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O140" s="74" t="str">
         <f t="shared" si="10"/>
@@ -25285,7 +25349,7 @@
         <v>640</v>
       </c>
       <c r="N141" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O141" s="74" t="str">
         <f t="shared" si="10"/>
@@ -25374,7 +25438,7 @@
         <v>640</v>
       </c>
       <c r="N142" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O142" s="74" t="str">
         <f t="shared" si="10"/>
@@ -25463,7 +25527,7 @@
         <v>640</v>
       </c>
       <c r="N143" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O143" s="74" t="str">
         <f t="shared" si="10"/>
@@ -25552,7 +25616,7 @@
         <v>640</v>
       </c>
       <c r="N144" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O144" s="74" t="str">
         <f t="shared" si="10"/>
@@ -25604,7 +25668,7 @@
     <row r="145" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A145" s="90"/>
       <c r="B145" s="74" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C145" s="74" t="str" cm="1">
         <f t="array" ref="C145">UPPER(INDEX(_xlfn.TEXTSPLIT($D145, "-"), 3))</f>
@@ -25620,7 +25684,7 @@
         <v>491</v>
       </c>
       <c r="G145" s="80" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H145" s="80" t="s">
         <v>634</v>
@@ -25641,7 +25705,7 @@
         <v>640</v>
       </c>
       <c r="N145" s="98" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="O145" s="74" t="str">
         <f t="shared" si="10"/>
@@ -25673,7 +25737,7 @@
         <v>225</v>
       </c>
       <c r="Z145" s="74" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="AA145" s="74" t="b">
         <v>1</v>
@@ -25693,7 +25757,7 @@
     <row r="146" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A146" s="90"/>
       <c r="B146" s="74" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C146" s="74" t="str" cm="1">
         <f t="array" ref="C146">UPPER(INDEX(_xlfn.TEXTSPLIT($D146, "-"), 3))</f>
@@ -25709,7 +25773,7 @@
         <v>492</v>
       </c>
       <c r="G146" s="80" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H146" s="80" t="s">
         <v>630</v>
@@ -25730,7 +25794,7 @@
         <v>640</v>
       </c>
       <c r="N146" s="98" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="O146" s="74" t="str">
         <f t="shared" si="10"/>
@@ -25762,7 +25826,7 @@
         <v>225</v>
       </c>
       <c r="Z146" s="74" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="AA146" s="74" t="b">
         <v>1</v>
@@ -25870,7 +25934,7 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="113"/>
+      <c r="A2" s="110"/>
       <c r="B2" s="73" t="s">
         <v>23</v>
       </c>
@@ -25923,7 +25987,7 @@
       <c r="R2" s="73"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="113"/>
+      <c r="A3" s="110"/>
       <c r="B3" s="74" t="s">
         <v>23</v>
       </c>
@@ -25976,7 +26040,7 @@
       <c r="R3" s="74"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="113"/>
+      <c r="A4" s="110"/>
       <c r="B4" s="73" t="s">
         <v>23</v>
       </c>
@@ -26029,7 +26093,7 @@
       <c r="R4" s="73"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="113"/>
+      <c r="A5" s="110"/>
       <c r="B5" s="74" t="s">
         <v>23</v>
       </c>
@@ -29538,7 +29602,7 @@
       <c r="D71" s="100" t="s">
         <v>322</v>
       </c>
-      <c r="E71" s="109" t="s">
+      <c r="E71" s="106" t="s">
         <v>24</v>
       </c>
       <c r="F71" s="100" t="s">
@@ -29593,7 +29657,7 @@
       <c r="D72" s="100" t="s">
         <v>322</v>
       </c>
-      <c r="E72" s="109" t="s">
+      <c r="E72" s="106" t="s">
         <v>24</v>
       </c>
       <c r="F72" s="100" t="s">
@@ -29646,7 +29710,7 @@
       <c r="D73" s="100" t="s">
         <v>322</v>
       </c>
-      <c r="E73" s="109" t="s">
+      <c r="E73" s="106" t="s">
         <v>24</v>
       </c>
       <c r="F73" s="100" t="s">
@@ -29699,7 +29763,7 @@
       <c r="D74" s="101" t="s">
         <v>322</v>
       </c>
-      <c r="E74" s="108" t="s">
+      <c r="E74" s="105" t="s">
         <v>24</v>
       </c>
       <c r="F74" s="101" t="s">
@@ -29754,7 +29818,7 @@
       <c r="D75" s="101" t="s">
         <v>322</v>
       </c>
-      <c r="E75" s="108" t="s">
+      <c r="E75" s="105" t="s">
         <v>24</v>
       </c>
       <c r="F75" s="101" t="s">
@@ -29807,7 +29871,7 @@
       <c r="D76" s="101" t="s">
         <v>322</v>
       </c>
-      <c r="E76" s="108" t="s">
+      <c r="E76" s="105" t="s">
         <v>24</v>
       </c>
       <c r="F76" s="101" t="s">
@@ -29860,7 +29924,7 @@
       <c r="D77" s="100" t="s">
         <v>322</v>
       </c>
-      <c r="E77" s="109" t="s">
+      <c r="E77" s="106" t="s">
         <v>24</v>
       </c>
       <c r="F77" s="100" t="s">
@@ -29915,7 +29979,7 @@
       <c r="D78" s="100" t="s">
         <v>322</v>
       </c>
-      <c r="E78" s="109" t="s">
+      <c r="E78" s="106" t="s">
         <v>24</v>
       </c>
       <c r="F78" s="100" t="s">
@@ -29968,7 +30032,7 @@
       <c r="D79" s="100" t="s">
         <v>322</v>
       </c>
-      <c r="E79" s="109" t="s">
+      <c r="E79" s="106" t="s">
         <v>24</v>
       </c>
       <c r="F79" s="100" t="s">
@@ -30021,7 +30085,7 @@
       <c r="D80" s="101" t="s">
         <v>322</v>
       </c>
-      <c r="E80" s="108" t="s">
+      <c r="E80" s="105" t="s">
         <v>24</v>
       </c>
       <c r="F80" s="101" t="s">
@@ -30076,7 +30140,7 @@
       <c r="D81" s="101" t="s">
         <v>322</v>
       </c>
-      <c r="E81" s="108" t="s">
+      <c r="E81" s="105" t="s">
         <v>24</v>
       </c>
       <c r="F81" s="101" t="s">
@@ -30129,7 +30193,7 @@
       <c r="D82" s="101" t="s">
         <v>322</v>
       </c>
-      <c r="E82" s="108" t="s">
+      <c r="E82" s="105" t="s">
         <v>24</v>
       </c>
       <c r="F82" s="101" t="s">
@@ -32461,7 +32525,7 @@
       <c r="D126" s="101" t="s">
         <v>323</v>
       </c>
-      <c r="E126" s="108" t="s">
+      <c r="E126" s="105" t="s">
         <v>24</v>
       </c>
       <c r="F126" s="101" t="s">
@@ -32516,7 +32580,7 @@
       <c r="D127" s="101" t="s">
         <v>323</v>
       </c>
-      <c r="E127" s="108" t="s">
+      <c r="E127" s="105" t="s">
         <v>24</v>
       </c>
       <c r="F127" s="101" t="s">
@@ -32569,7 +32633,7 @@
       <c r="D128" s="101" t="s">
         <v>323</v>
       </c>
-      <c r="E128" s="108" t="s">
+      <c r="E128" s="105" t="s">
         <v>24</v>
       </c>
       <c r="F128" s="101" t="s">
@@ -32666,7 +32730,7 @@
     <row r="130" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A130" s="99"/>
       <c r="B130" s="73" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C130" s="73" t="str" cm="1">
         <f t="array" ref="C130">UPPER(INDEX(_xlfn.TEXTSPLIT($D130, "-"), 3))</f>
@@ -32719,7 +32783,7 @@
     <row r="131" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A131" s="99"/>
       <c r="B131" s="74" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C131" s="74" t="str" cm="1">
         <f t="array" ref="C131">UPPER(INDEX(_xlfn.TEXTSPLIT($D131, "-"), 3))</f>
@@ -32772,7 +32836,7 @@
     <row r="132" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A132" s="99"/>
       <c r="B132" s="73" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C132" s="73" t="str" cm="1">
         <f t="array" ref="C132">UPPER(INDEX(_xlfn.TEXTSPLIT($D132, "-"), 3))</f>
@@ -32834,7 +32898,7 @@
       <c r="D133" s="100" t="s">
         <v>323</v>
       </c>
-      <c r="E133" s="109" t="s">
+      <c r="E133" s="106" t="s">
         <v>24</v>
       </c>
       <c r="F133" s="100" t="s">
@@ -32889,7 +32953,7 @@
       <c r="D134" s="100" t="s">
         <v>323</v>
       </c>
-      <c r="E134" s="109" t="s">
+      <c r="E134" s="106" t="s">
         <v>24</v>
       </c>
       <c r="F134" s="100" t="s">
@@ -32942,7 +33006,7 @@
       <c r="D135" s="100" t="s">
         <v>323</v>
       </c>
-      <c r="E135" s="109" t="s">
+      <c r="E135" s="106" t="s">
         <v>24</v>
       </c>
       <c r="F135" s="100" t="s">
@@ -32995,7 +33059,7 @@
       <c r="D136" s="100" t="s">
         <v>323</v>
       </c>
-      <c r="E136" s="109" t="s">
+      <c r="E136" s="106" t="s">
         <v>24</v>
       </c>
       <c r="F136" s="100" t="s">
@@ -33048,7 +33112,7 @@
       <c r="D137" s="100" t="s">
         <v>323</v>
       </c>
-      <c r="E137" s="109" t="s">
+      <c r="E137" s="106" t="s">
         <v>24</v>
       </c>
       <c r="F137" s="100" t="s">
@@ -33101,7 +33165,7 @@
       <c r="D138" s="100" t="s">
         <v>323</v>
       </c>
-      <c r="E138" s="109" t="s">
+      <c r="E138" s="106" t="s">
         <v>24</v>
       </c>
       <c r="F138" s="100" t="s">
@@ -34152,7 +34216,7 @@
     <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158" s="99"/>
       <c r="B158" s="74" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C158" s="74" t="str" cm="1">
         <f t="array" ref="C158">UPPER(INDEX(_xlfn.TEXTSPLIT($D158, "-"), 3))</f>
@@ -34205,7 +34269,7 @@
     <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A159" s="99"/>
       <c r="B159" s="73" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C159" s="73" t="str" cm="1">
         <f t="array" ref="C159">UPPER(INDEX(_xlfn.TEXTSPLIT($D159, "-"), 3))</f>
@@ -34320,7 +34384,7 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="114"/>
+      <c r="A2" s="111"/>
       <c r="B2" s="78" t="s">
         <v>23</v>
       </c>
@@ -34360,7 +34424,7 @@
       <c r="M2" s="79"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="114"/>
+      <c r="A3" s="111"/>
       <c r="B3" s="80" t="s">
         <v>23</v>
       </c>
@@ -34400,7 +34464,7 @@
       <c r="M3" s="81"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="114"/>
+      <c r="A4" s="111"/>
       <c r="B4" s="78" t="s">
         <v>23</v>
       </c>
@@ -37102,7 +37166,7 @@
         <v>241</v>
       </c>
       <c r="H71" s="74" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="I71" s="74" t="s">
         <v>420</v>
@@ -37142,7 +37206,7 @@
         <v>241</v>
       </c>
       <c r="H72" s="73" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="I72" s="73" t="s">
         <v>421</v>
@@ -37182,7 +37246,7 @@
         <v>241</v>
       </c>
       <c r="H73" s="74" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="I73" s="74" t="s">
         <v>422</v>
@@ -37222,7 +37286,7 @@
         <v>241</v>
       </c>
       <c r="H74" s="73" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="I74" s="73" t="s">
         <v>423</v>
@@ -37560,7 +37624,7 @@
       <c r="M82" s="73"/>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A83" s="111"/>
+      <c r="A83" s="108"/>
       <c r="B83" s="80" t="s">
         <v>23</v>
       </c>
@@ -37600,7 +37664,7 @@
       <c r="M83" s="74"/>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A84" s="111"/>
+      <c r="A84" s="108"/>
       <c r="B84" s="78" t="s">
         <v>23</v>
       </c>
@@ -38880,6 +38944,7 @@
       <c r="M115" s="74"/>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A116" s="90"/>
       <c r="B116" s="78" t="s">
         <v>23</v>
       </c>
@@ -38919,6 +38984,7 @@
       <c r="M116" s="73"/>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A117" s="90"/>
       <c r="B117" s="80" t="s">
         <v>23</v>
       </c>
@@ -38998,6 +39064,7 @@
       <c r="M118" s="73"/>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A119" s="90"/>
       <c r="B119" s="80" t="s">
         <v>23</v>
       </c>
@@ -39039,7 +39106,7 @@
     <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="90"/>
       <c r="B120" s="73" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C120" s="78" t="str" cm="1">
         <f t="array" ref="C120">UPPER(INDEX(_xlfn.TEXTSPLIT($E120, "-"), 2))</f>
@@ -39059,7 +39126,7 @@
         <v>241</v>
       </c>
       <c r="H120" s="73" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="I120" s="73" t="s">
         <v>233</v>
@@ -39079,7 +39146,7 @@
     <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="90"/>
       <c r="B121" s="74" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C121" s="80" t="str" cm="1">
         <f t="array" ref="C121">UPPER(INDEX(_xlfn.TEXTSPLIT($E121, "-"), 2))</f>
@@ -39099,7 +39166,7 @@
         <v>241</v>
       </c>
       <c r="H121" s="74" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="I121" s="74" t="s">
         <v>232</v>
@@ -39119,7 +39186,7 @@
     <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="90"/>
       <c r="B122" s="73" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C122" s="78" t="str" cm="1">
         <f t="array" ref="C122">UPPER(INDEX(_xlfn.TEXTSPLIT($E122, "-"), 2))</f>
@@ -39139,7 +39206,7 @@
         <v>241</v>
       </c>
       <c r="H122" s="73" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="I122" s="73" t="s">
         <v>236</v>
@@ -39515,6 +39582,7 @@
       <c r="M131" s="74"/>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A132" s="90"/>
       <c r="B132" s="78" t="s">
         <v>23</v>
       </c>
@@ -39554,6 +39622,7 @@
       <c r="M132" s="73"/>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A133" s="90"/>
       <c r="B133" s="80" t="s">
         <v>23</v>
       </c>
@@ -39593,6 +39662,7 @@
       <c r="M133" s="74"/>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A134" s="90"/>
       <c r="B134" s="78" t="s">
         <v>23</v>
       </c>
@@ -39632,6 +39702,7 @@
       <c r="M134" s="73"/>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A135" s="90"/>
       <c r="B135" s="80" t="s">
         <v>23</v>
       </c>
@@ -39671,6 +39742,7 @@
       <c r="M135" s="74"/>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A136" s="90"/>
       <c r="B136" s="78" t="s">
         <v>23</v>
       </c>
@@ -39710,6 +39782,7 @@
       <c r="M136" s="73"/>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A137" s="90"/>
       <c r="B137" s="80" t="s">
         <v>23</v>
       </c>
@@ -40031,10 +40104,10 @@
     <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" s="90"/>
       <c r="B145" s="80" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C145" s="80" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="D145" s="80" t="s">
         <v>234</v>
@@ -40050,7 +40123,7 @@
         <v>225</v>
       </c>
       <c r="H145" s="74" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="I145" s="74" t="s">
         <v>491</v>
@@ -40070,10 +40143,10 @@
     <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" s="90"/>
       <c r="B146" s="78" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C146" s="78" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="D146" s="78" t="s">
         <v>234</v>
@@ -40089,7 +40162,7 @@
         <v>225</v>
       </c>
       <c r="H146" s="73" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="I146" s="73" t="s">
         <v>492</v>
@@ -40173,6 +40246,7 @@
       <c r="M148" s="73"/>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A149" s="90"/>
       <c r="B149" s="80" t="s">
         <v>23</v>
       </c>
@@ -40205,6 +40279,7 @@
       <c r="M149" s="74"/>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A150" s="90"/>
       <c r="B150" s="78" t="s">
         <v>23</v>
       </c>
@@ -40237,6 +40312,7 @@
       <c r="M150" s="73"/>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A151" s="90"/>
       <c r="B151" s="80" t="s">
         <v>23</v>
       </c>
@@ -40269,6 +40345,7 @@
       <c r="M151" s="74"/>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A152" s="90"/>
       <c r="B152" s="78" t="s">
         <v>23</v>
       </c>
@@ -40433,6 +40510,7 @@
       <c r="M156" s="73"/>
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A157" s="90"/>
       <c r="B157" s="80" t="s">
         <v>23</v>
       </c>
@@ -40465,6 +40543,7 @@
       <c r="M157" s="74"/>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A158" s="90"/>
       <c r="B158" s="78" t="s">
         <v>23</v>
       </c>
@@ -40497,6 +40576,7 @@
       <c r="M158" s="73"/>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A159" s="90"/>
       <c r="B159" s="80" t="s">
         <v>23</v>
       </c>
@@ -40529,6 +40609,7 @@
       <c r="M159" s="74"/>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A160" s="90"/>
       <c r="B160" s="78" t="s">
         <v>23</v>
       </c>
@@ -41945,7 +42026,7 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="110"/>
+      <c r="A2" s="107"/>
       <c r="B2" s="74" t="s">
         <v>23</v>
       </c>
@@ -41976,7 +42057,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="110"/>
+      <c r="A3" s="107"/>
       <c r="B3" s="82" t="s">
         <v>23</v>
       </c>
@@ -42007,7 +42088,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="110"/>
+      <c r="A4" s="107"/>
       <c r="B4" s="74" t="s">
         <v>23</v>
       </c>
@@ -42038,7 +42119,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="110"/>
+      <c r="A5" s="107"/>
       <c r="B5" s="82" t="s">
         <v>23</v>
       </c>
@@ -42069,7 +42150,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="110"/>
+      <c r="A6" s="107"/>
       <c r="B6" s="74" t="s">
         <v>23</v>
       </c>
@@ -42100,7 +42181,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="110"/>
+      <c r="A7" s="107"/>
       <c r="B7" s="82" t="s">
         <v>23</v>
       </c>
@@ -42131,7 +42212,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="110"/>
+      <c r="A8" s="107"/>
       <c r="B8" s="74" t="s">
         <v>23</v>
       </c>
@@ -42152,7 +42233,7 @@
         <v>332</v>
       </c>
       <c r="H8" s="74" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>222</v>
@@ -42162,7 +42243,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="110"/>
+      <c r="A9" s="107"/>
       <c r="B9" s="82" t="s">
         <v>23</v>
       </c>
@@ -42193,7 +42274,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="110"/>
+      <c r="A10" s="107"/>
       <c r="B10" s="74" t="s">
         <v>23</v>
       </c>
@@ -42224,7 +42305,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="110"/>
+      <c r="A11" s="107"/>
       <c r="B11" s="82" t="s">
         <v>23</v>
       </c>
@@ -42255,7 +42336,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="110"/>
+      <c r="A12" s="107"/>
       <c r="B12" s="74" t="s">
         <v>23</v>
       </c>
@@ -42286,7 +42367,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="110"/>
+      <c r="A13" s="107"/>
       <c r="B13" s="82" t="s">
         <v>23</v>
       </c>
@@ -42317,7 +42398,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="110"/>
+      <c r="A14" s="107"/>
       <c r="B14" s="74" t="s">
         <v>23</v>
       </c>
@@ -42348,7 +42429,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="110"/>
+      <c r="A15" s="107"/>
       <c r="B15" s="82" t="s">
         <v>23</v>
       </c>
@@ -42379,7 +42460,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="110"/>
+      <c r="A16" s="107"/>
       <c r="B16" s="74" t="s">
         <v>23</v>
       </c>
@@ -42410,7 +42491,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="110"/>
+      <c r="A17" s="107"/>
       <c r="B17" s="82" t="s">
         <v>23</v>
       </c>
@@ -42441,7 +42522,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="110"/>
+      <c r="A18" s="107"/>
       <c r="B18" s="74" t="s">
         <v>23</v>
       </c>
@@ -42472,7 +42553,7 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="110"/>
+      <c r="A19" s="107"/>
       <c r="B19" s="82" t="s">
         <v>23</v>
       </c>
@@ -42503,7 +42584,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="110"/>
+      <c r="A20" s="107"/>
       <c r="B20" s="74" t="s">
         <v>23</v>
       </c>
@@ -42534,7 +42615,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="110"/>
+      <c r="A21" s="107"/>
       <c r="B21" s="82" t="s">
         <v>23</v>
       </c>
@@ -42576,7 +42657,7 @@
       <c r="J22" s="87"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="110"/>
+      <c r="A23" s="107"/>
       <c r="B23" s="82" t="s">
         <v>23</v>
       </c>
@@ -42607,7 +42688,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="110"/>
+      <c r="A24" s="107"/>
       <c r="B24" s="74" t="s">
         <v>23</v>
       </c>
@@ -42638,7 +42719,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="110"/>
+      <c r="A25" s="107"/>
       <c r="B25" s="82" t="s">
         <v>23</v>
       </c>
@@ -42669,7 +42750,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="110"/>
+      <c r="A26" s="107"/>
       <c r="B26" s="74" t="s">
         <v>23</v>
       </c>
@@ -42700,7 +42781,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="110"/>
+      <c r="A27" s="107"/>
       <c r="B27" s="82" t="s">
         <v>23</v>
       </c>
@@ -42731,7 +42812,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="110"/>
+      <c r="A28" s="107"/>
       <c r="B28" s="74" t="s">
         <v>23</v>
       </c>
@@ -42762,7 +42843,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="110"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="82" t="s">
         <v>23</v>
       </c>
@@ -42783,7 +42864,7 @@
         <v>332</v>
       </c>
       <c r="H29" s="82" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="I29" s="82" t="s">
         <v>222</v>
@@ -42793,7 +42874,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="110"/>
+      <c r="A30" s="107"/>
       <c r="B30" s="74" t="s">
         <v>23</v>
       </c>
@@ -42824,7 +42905,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="110"/>
+      <c r="A31" s="107"/>
       <c r="B31" s="82" t="s">
         <v>23</v>
       </c>
@@ -42855,7 +42936,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="110"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="74" t="s">
         <v>23</v>
       </c>
@@ -42886,7 +42967,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="110"/>
+      <c r="A33" s="107"/>
       <c r="B33" s="82" t="s">
         <v>23</v>
       </c>
@@ -42917,7 +42998,7 @@
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="110"/>
+      <c r="A34" s="107"/>
       <c r="B34" s="74" t="s">
         <v>23</v>
       </c>
@@ -42948,7 +43029,7 @@
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="110"/>
+      <c r="A35" s="107"/>
       <c r="B35" s="82" t="s">
         <v>23</v>
       </c>
@@ -42979,7 +43060,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="110"/>
+      <c r="A36" s="107"/>
       <c r="B36" s="74" t="s">
         <v>23</v>
       </c>
@@ -43010,7 +43091,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="110"/>
+      <c r="A37" s="107"/>
       <c r="B37" s="82" t="s">
         <v>23</v>
       </c>
@@ -43041,7 +43122,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="110"/>
+      <c r="A38" s="107"/>
       <c r="B38" s="74" t="s">
         <v>23</v>
       </c>
@@ -43072,7 +43153,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="110"/>
+      <c r="A39" s="107"/>
       <c r="B39" s="82" t="s">
         <v>23</v>
       </c>
@@ -43103,7 +43184,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="110"/>
+      <c r="A40" s="107"/>
       <c r="B40" s="74" t="s">
         <v>23</v>
       </c>
@@ -45916,7 +45997,7 @@
         <v>1008</v>
       </c>
       <c r="E15" s="82" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F15" s="51" t="str">
         <f t="shared" si="0"/>
@@ -46531,31 +46612,34 @@
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B34" s="102" t="s">
+      <c r="A34" s="90"/>
+      <c r="B34" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="82" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D34" s="82" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E34" s="82" t="s">
         <v>1073</v>
       </c>
-      <c r="C34" s="102"/>
-      <c r="D34" s="102" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E34" s="102" t="s">
-        <v>1074</v>
-      </c>
-      <c r="F34" s="107" t="str">
+      <c r="F34" s="51" t="str">
         <f t="shared" si="0"/>
-        <v>p-dtg-cdmlap-lb-pb?</v>
-      </c>
-      <c r="G34" s="102" t="s">
+        <v>p-dtg-cdmlap-lb-pb3000</v>
+      </c>
+      <c r="G34" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="H34" s="102" t="s">
-        <v>1082</v>
-      </c>
-      <c r="I34" s="102"/>
-      <c r="J34" s="102">
+      <c r="H34" s="82">
+        <v>3000</v>
+      </c>
+      <c r="I34" s="82"/>
+      <c r="J34" s="82">
         <v>5</v>
       </c>
-      <c r="K34" s="102">
+      <c r="K34" s="82">
         <v>2</v>
       </c>
     </row>
@@ -46638,7 +46722,7 @@
         <v>1009</v>
       </c>
       <c r="E37" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F37" s="51" t="str">
         <f t="shared" si="0"/>
@@ -46671,7 +46755,7 @@
         <v>1009</v>
       </c>
       <c r="E38" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F38" s="51" t="str">
         <f t="shared" ref="F38:F41" si="9">SUBSTITUTE(E38, "hazr-", "")&amp;"-pb"&amp;H38</f>
@@ -46704,7 +46788,7 @@
         <v>1009</v>
       </c>
       <c r="E39" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F39" s="51" t="str">
         <f t="shared" si="9"/>
@@ -46737,7 +46821,7 @@
         <v>1009</v>
       </c>
       <c r="E40" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F40" s="51" t="str">
         <f t="shared" si="9"/>
@@ -46770,7 +46854,7 @@
         <v>1009</v>
       </c>
       <c r="E41" s="82" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F41" s="51" t="str">
         <f t="shared" si="9"/>
@@ -46836,7 +46920,7 @@
         <v>1009</v>
       </c>
       <c r="E43" s="82" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="F43" s="51" t="str">
         <f t="shared" si="0"/>
@@ -46902,7 +46986,7 @@
         <v>1009</v>
       </c>
       <c r="E45" s="82" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F45" s="51" t="str">
         <f t="shared" si="0"/>
@@ -46968,7 +47052,7 @@
         <v>1010</v>
       </c>
       <c r="E47" s="82" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="F47" s="51" t="str">
         <f t="shared" si="0"/>
@@ -47100,7 +47184,7 @@
         <v>1011</v>
       </c>
       <c r="E51" s="82" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F51" s="51" t="str">
         <f t="shared" ref="F51:F62" si="11">SUBSTITUTE(E51, "hazr-", "")&amp;"-pb"&amp;H51</f>
@@ -47133,14 +47217,14 @@
         <v>1011</v>
       </c>
       <c r="E52" s="82" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F52" s="51" t="str">
         <f t="shared" ref="F52" si="12">SUBSTITUTE(E52, "hazr-", "")&amp;"-pb"&amp;H52</f>
         <v>p-if-proxy-lb-pb8080</v>
       </c>
       <c r="G52" s="82" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H52" s="82">
         <v>8080</v>
@@ -47151,7 +47235,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B53" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C53" s="102"/>
       <c r="D53" s="102" t="s">
@@ -47160,7 +47244,7 @@
       <c r="E53" s="102" t="s">
         <v>997</v>
       </c>
-      <c r="F53" s="107" t="str">
+      <c r="F53" s="104" t="str">
         <f t="shared" si="11"/>
         <v>p-cs-chtap-lb-pb?</v>
       </c>
@@ -47168,7 +47252,7 @@
         <v>57</v>
       </c>
       <c r="H53" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="I53" s="102"/>
       <c r="J53" s="102">
@@ -47180,16 +47264,16 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B54" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C54" s="102"/>
       <c r="D54" s="102" t="s">
         <v>1012</v>
       </c>
       <c r="E54" s="102" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F54" s="107" t="str">
+        <v>1083</v>
+      </c>
+      <c r="F54" s="104" t="str">
         <f t="shared" si="11"/>
         <v>p-cs-chtweb-lb-pb?</v>
       </c>
@@ -47197,7 +47281,7 @@
         <v>57</v>
       </c>
       <c r="H54" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="I54" s="102"/>
       <c r="J54" s="102">
@@ -47209,7 +47293,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B55" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C55" s="102"/>
       <c r="D55" s="102" t="s">
@@ -47218,7 +47302,7 @@
       <c r="E55" s="102" t="s">
         <v>999</v>
       </c>
-      <c r="F55" s="107" t="str">
+      <c r="F55" s="104" t="str">
         <f t="shared" si="11"/>
         <v>p-cs-chtintweb-lb-pb?</v>
       </c>
@@ -47226,7 +47310,7 @@
         <v>57</v>
       </c>
       <c r="H55" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="I55" s="102"/>
       <c r="J55" s="102">
@@ -47238,16 +47322,16 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B56" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C56" s="102"/>
       <c r="D56" s="102" t="s">
         <v>1013</v>
       </c>
       <c r="E56" s="102" t="s">
-        <v>1085</v>
-      </c>
-      <c r="F56" s="107" t="str">
+        <v>1084</v>
+      </c>
+      <c r="F56" s="104" t="str">
         <f t="shared" si="11"/>
         <v>p-doip-web-lb-pb?</v>
       </c>
@@ -47255,7 +47339,7 @@
         <v>57</v>
       </c>
       <c r="H56" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="I56" s="102"/>
       <c r="J56" s="102">
@@ -47267,7 +47351,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B57" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C57" s="102"/>
       <c r="D57" s="102" t="s">
@@ -47276,7 +47360,7 @@
       <c r="E57" s="102" t="s">
         <v>1001</v>
       </c>
-      <c r="F57" s="107" t="str">
+      <c r="F57" s="104" t="str">
         <f t="shared" si="11"/>
         <v>p-doip-ap-lb-pb?</v>
       </c>
@@ -47284,7 +47368,7 @@
         <v>57</v>
       </c>
       <c r="H57" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="I57" s="102"/>
       <c r="J57" s="102">
@@ -47296,16 +47380,16 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B58" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C58" s="102"/>
       <c r="D58" s="102" t="s">
         <v>1013</v>
       </c>
       <c r="E58" s="102" t="s">
-        <v>1086</v>
-      </c>
-      <c r="F58" s="107" t="str">
+        <v>1085</v>
+      </c>
+      <c r="F58" s="104" t="str">
         <f t="shared" si="11"/>
         <v>p-doip-adm-lb-pb?</v>
       </c>
@@ -47313,7 +47397,7 @@
         <v>57</v>
       </c>
       <c r="H58" s="102" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="I58" s="102"/>
       <c r="J58" s="102">
@@ -47458,12 +47542,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -47611,15 +47692,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -47643,17 +47735,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260617_리소스배포_운영.xlsx
+++ b/서버정보/20260617_리소스배포_운영.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079525FD-DE85-4507-A401-2DECB9486534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566D12D2-34B8-4E26-A300-805D0C97A908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5173,9 +5173,6 @@
     <t>hazr-p-dis-walkap-lb</t>
   </si>
   <si>
-    <t>hazr-t-dis-drvcltap-lb</t>
-  </si>
-  <si>
     <t>hazr-p-dis-walkweb-lb</t>
   </si>
   <si>
@@ -5765,6 +5762,10 @@
   </si>
   <si>
     <t>ZoneRedundant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-p-dis-drvcltap-lb</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6252,7 +6253,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6591,6 +6592,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8871,10 +8878,10 @@
         <v>DIS</v>
       </c>
       <c r="D2" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E2" s="82" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F2" s="82" t="str">
         <f t="shared" ref="F2:F20" si="0">SUBSTITUTE(E2, "hazr-", "")&amp;"-rule"&amp;O2</f>
@@ -8933,10 +8940,10 @@
         <v>DIS</v>
       </c>
       <c r="D3" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E3" s="74" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F3" s="74" t="str">
         <f t="shared" si="0"/>
@@ -8995,10 +9002,10 @@
         <v>DIS</v>
       </c>
       <c r="D4" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E4" s="82" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F4" s="82" t="str">
         <f t="shared" si="0"/>
@@ -9057,7 +9064,7 @@
         <v>DIS</v>
       </c>
       <c r="D5" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E5" s="74" t="s">
         <v>958</v>
@@ -9119,7 +9126,7 @@
         <v>DIS</v>
       </c>
       <c r="D6" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E6" s="74" t="s">
         <v>958</v>
@@ -9181,7 +9188,7 @@
         <v>DIS</v>
       </c>
       <c r="D7" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E7" s="74" t="s">
         <v>958</v>
@@ -9243,10 +9250,10 @@
         <v>DIS</v>
       </c>
       <c r="D8" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E8" s="82" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F8" s="82" t="str">
         <f t="shared" si="0"/>
@@ -9305,7 +9312,7 @@
         <v>DIS</v>
       </c>
       <c r="D9" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E9" s="74" t="s">
         <v>960</v>
@@ -9367,7 +9374,7 @@
         <v>DIS</v>
       </c>
       <c r="D10" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E10" s="82" t="s">
         <v>224</v>
@@ -9429,10 +9436,10 @@
         <v>DIS</v>
       </c>
       <c r="D11" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E11" s="74" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F11" s="74" t="str">
         <f t="shared" si="0"/>
@@ -9491,10 +9498,10 @@
         <v>DIS</v>
       </c>
       <c r="D12" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E12" s="82" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="F12" s="82" t="str">
         <f t="shared" si="0"/>
@@ -9553,10 +9560,10 @@
         <v>DIS</v>
       </c>
       <c r="D13" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E13" s="74" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F13" s="74" t="str">
         <f t="shared" si="0"/>
@@ -9615,10 +9622,10 @@
         <v>DIS</v>
       </c>
       <c r="D14" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E14" s="74" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F14" s="74" t="str">
         <f t="shared" si="0"/>
@@ -9677,10 +9684,10 @@
         <v>DIS</v>
       </c>
       <c r="D15" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E15" s="82" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="F15" s="82" t="str">
         <f t="shared" si="0"/>
@@ -9739,10 +9746,10 @@
         <v>DIS</v>
       </c>
       <c r="D16" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E16" s="74" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F16" s="74" t="str">
         <f t="shared" si="0"/>
@@ -9801,10 +9808,10 @@
         <v>DIS</v>
       </c>
       <c r="D17" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E17" s="82" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F17" s="82" t="str">
         <f t="shared" si="0"/>
@@ -9863,10 +9870,10 @@
         <v>DIS</v>
       </c>
       <c r="D18" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E18" s="82" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F18" s="82" t="str">
         <f t="shared" si="0"/>
@@ -9925,10 +9932,10 @@
         <v>DIS</v>
       </c>
       <c r="D19" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E19" s="74" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F19" s="74" t="str">
         <f t="shared" si="0"/>
@@ -9987,10 +9994,10 @@
         <v>DTG</v>
       </c>
       <c r="D20" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E20" s="82" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="F20" s="82" t="str">
         <f t="shared" si="0"/>
@@ -10049,10 +10056,10 @@
         <v>DTG</v>
       </c>
       <c r="D21" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E21" s="74" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F21" s="74" t="str">
         <f t="shared" ref="F21:F34" si="4">SUBSTITUTE(E21, "hazr-", "")&amp;"-rule"&amp;O21</f>
@@ -10111,10 +10118,10 @@
         <v>DTG</v>
       </c>
       <c r="D22" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E22" s="74" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F22" s="74" t="str">
         <f t="shared" si="4"/>
@@ -10173,10 +10180,10 @@
         <v>DTG</v>
       </c>
       <c r="D23" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E23" s="82" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F23" s="82" t="str">
         <f t="shared" si="4"/>
@@ -10235,10 +10242,10 @@
         <v>DTG</v>
       </c>
       <c r="D24" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E24" s="82" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F24" s="82" t="str">
         <f t="shared" si="4"/>
@@ -10297,10 +10304,10 @@
         <v>DTG</v>
       </c>
       <c r="D25" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E25" s="74" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F25" s="74" t="str">
         <f t="shared" si="4"/>
@@ -10359,10 +10366,10 @@
         <v>DTG</v>
       </c>
       <c r="D26" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E26" s="74" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F26" s="74" t="str">
         <f t="shared" si="4"/>
@@ -10421,10 +10428,10 @@
         <v>DTG</v>
       </c>
       <c r="D27" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E27" s="82" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F27" s="82" t="str">
         <f t="shared" si="4"/>
@@ -10483,10 +10490,10 @@
         <v>DTG</v>
       </c>
       <c r="D28" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E28" s="82" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F28" s="82" t="str">
         <f t="shared" si="4"/>
@@ -10545,10 +10552,10 @@
         <v>DTG</v>
       </c>
       <c r="D29" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E29" s="74" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F29" s="74" t="str">
         <f t="shared" ref="F29:F32" si="6">SUBSTITUTE(E29, "hazr-", "")&amp;"-rule"&amp;O29</f>
@@ -10607,10 +10614,10 @@
         <v>DTG</v>
       </c>
       <c r="D30" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E30" s="74" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F30" s="74" t="str">
         <f t="shared" si="6"/>
@@ -10669,10 +10676,10 @@
         <v>DTG</v>
       </c>
       <c r="D31" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E31" s="82" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="F31" s="82" t="str">
         <f t="shared" si="6"/>
@@ -10731,10 +10738,10 @@
         <v>DTG</v>
       </c>
       <c r="D32" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E32" s="82" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="F32" s="82" t="str">
         <f t="shared" si="6"/>
@@ -10793,10 +10800,10 @@
         <v>DTG</v>
       </c>
       <c r="D33" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E33" s="74" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F33" s="74" t="str">
         <f t="shared" si="4"/>
@@ -10855,10 +10862,10 @@
         <v>DTG</v>
       </c>
       <c r="D34" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E34" s="82" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="F34" s="82" t="str">
         <f t="shared" si="4"/>
@@ -10917,10 +10924,10 @@
         <v>DTG</v>
       </c>
       <c r="D35" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E35" s="82" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="F35" s="82" t="str">
         <f t="shared" ref="F35:F66" si="10">SUBSTITUTE(E35, "hazr-", "")&amp;"-rule"&amp;O35</f>
@@ -10979,10 +10986,10 @@
         <v>DTG</v>
       </c>
       <c r="D36" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E36" s="74" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="F36" s="74" t="str">
         <f t="shared" si="10"/>
@@ -11041,10 +11048,10 @@
         <v>DTG</v>
       </c>
       <c r="D37" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E37" s="74" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="F37" s="74" t="str">
         <f t="shared" si="10"/>
@@ -11103,10 +11110,10 @@
         <v>DTG</v>
       </c>
       <c r="D38" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E38" s="82" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="F38" s="82" t="str">
         <f t="shared" si="10"/>
@@ -11165,10 +11172,10 @@
         <v>DTG</v>
       </c>
       <c r="D39" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E39" s="74" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F39" s="74" t="str">
         <f t="shared" si="10"/>
@@ -11227,10 +11234,10 @@
         <v>DTG</v>
       </c>
       <c r="D40" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E40" s="74" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F40" s="74" t="str">
         <f t="shared" si="10"/>
@@ -11289,10 +11296,10 @@
         <v>DTG</v>
       </c>
       <c r="D41" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E41" s="82" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F41" s="82" t="str">
         <f t="shared" si="10"/>
@@ -11351,10 +11358,10 @@
         <v>DTG</v>
       </c>
       <c r="D42" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E42" s="82" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F42" s="82" t="str">
         <f t="shared" si="10"/>
@@ -11413,10 +11420,10 @@
         <v>DTG</v>
       </c>
       <c r="D43" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E43" s="82" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F43" s="82" t="str">
         <f t="shared" si="10"/>
@@ -11475,10 +11482,10 @@
         <v>DTG</v>
       </c>
       <c r="D44" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E44" s="82" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F44" s="82" t="str">
         <f t="shared" si="10"/>
@@ -11537,10 +11544,10 @@
         <v>DTG</v>
       </c>
       <c r="D45" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E45" s="82" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F45" s="82" t="str">
         <f t="shared" si="10"/>
@@ -11599,10 +11606,10 @@
         <v>DTG</v>
       </c>
       <c r="D46" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E46" s="74" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="F46" s="74" t="str">
         <f t="shared" si="10"/>
@@ -11661,10 +11668,10 @@
         <v>DTG</v>
       </c>
       <c r="D47" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E47" s="82" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F47" s="82" t="str">
         <f t="shared" si="10"/>
@@ -11723,10 +11730,10 @@
         <v>DTG</v>
       </c>
       <c r="D48" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E48" s="74" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F48" s="74" t="str">
         <f t="shared" si="10"/>
@@ -11785,10 +11792,10 @@
         <v>DTG</v>
       </c>
       <c r="D49" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E49" s="82" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F49" s="82" t="str">
         <f t="shared" si="10"/>
@@ -11847,10 +11854,10 @@
         <v>BDP</v>
       </c>
       <c r="D50" s="74" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E50" s="74" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F50" s="74" t="str">
         <f t="shared" si="10"/>
@@ -11909,10 +11916,10 @@
         <v>BDP</v>
       </c>
       <c r="D51" s="82" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E51" s="82" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F51" s="82" t="str">
         <f t="shared" si="10"/>
@@ -11971,10 +11978,10 @@
         <v>IF</v>
       </c>
       <c r="D52" s="74" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E52" s="74" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F52" s="74" t="str">
         <f t="shared" si="10"/>
@@ -12033,10 +12040,10 @@
         <v>IF</v>
       </c>
       <c r="D53" s="74" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E53" s="74" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F53" s="74" t="str">
         <f t="shared" si="10"/>
@@ -12095,10 +12102,10 @@
         <v>IF</v>
       </c>
       <c r="D54" s="74" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E54" s="74" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F54" s="74" t="str">
         <f t="shared" si="10"/>
@@ -12157,10 +12164,10 @@
         <v>IF</v>
       </c>
       <c r="D55" s="82" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E55" s="82" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="F55" s="82" t="str">
         <f t="shared" si="10"/>
@@ -12219,10 +12226,10 @@
         <v>IF</v>
       </c>
       <c r="D56" s="82" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E56" s="82" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="F56" s="82" t="str">
         <f t="shared" si="10"/>
@@ -12273,14 +12280,14 @@
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B57" s="102" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C57" s="102"/>
       <c r="D57" s="102" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E57" s="102" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="F57" s="102" t="str">
         <f t="shared" si="10"/>
@@ -12294,7 +12301,7 @@
         <v>57</v>
       </c>
       <c r="I57" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="J57" s="102" t="b">
         <v>0</v>
@@ -12304,7 +12311,7 @@
         <v>p-cs-chtap-lb-bp</v>
       </c>
       <c r="L57" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M57" s="102" t="str">
         <f t="shared" si="11"/>
@@ -12314,7 +12321,7 @@
         <v>57</v>
       </c>
       <c r="O57" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="P57" s="102">
         <v>4</v>
@@ -12331,14 +12338,14 @@
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B58" s="102" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C58" s="102"/>
       <c r="D58" s="102" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E58" s="102" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="F58" s="102" t="str">
         <f t="shared" si="10"/>
@@ -12352,7 +12359,7 @@
         <v>57</v>
       </c>
       <c r="I58" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="J58" s="102" t="b">
         <v>0</v>
@@ -12362,7 +12369,7 @@
         <v>p-cs-chtweb-lb-bp</v>
       </c>
       <c r="L58" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M58" s="102" t="str">
         <f t="shared" si="11"/>
@@ -12372,7 +12379,7 @@
         <v>57</v>
       </c>
       <c r="O58" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="P58" s="102">
         <v>4</v>
@@ -12389,14 +12396,14 @@
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B59" s="102" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C59" s="102"/>
       <c r="D59" s="102" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E59" s="102" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F59" s="102" t="str">
         <f t="shared" si="10"/>
@@ -12410,7 +12417,7 @@
         <v>57</v>
       </c>
       <c r="I59" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="J59" s="102" t="b">
         <v>0</v>
@@ -12420,7 +12427,7 @@
         <v>p-cs-chtintweb-lb-bp</v>
       </c>
       <c r="L59" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M59" s="102" t="str">
         <f t="shared" si="11"/>
@@ -12430,7 +12437,7 @@
         <v>57</v>
       </c>
       <c r="O59" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="P59" s="102">
         <v>4</v>
@@ -12447,14 +12454,14 @@
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B60" s="102" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C60" s="102"/>
       <c r="D60" s="102" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E60" s="102" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="F60" s="102" t="str">
         <f t="shared" si="10"/>
@@ -12468,7 +12475,7 @@
         <v>57</v>
       </c>
       <c r="I60" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="J60" s="102" t="b">
         <v>0</v>
@@ -12478,7 +12485,7 @@
         <v>p-doip-web-lb-bp</v>
       </c>
       <c r="L60" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M60" s="102" t="str">
         <f t="shared" si="11"/>
@@ -12488,7 +12495,7 @@
         <v>57</v>
       </c>
       <c r="O60" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="P60" s="102">
         <v>4</v>
@@ -12505,14 +12512,14 @@
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B61" s="102" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C61" s="102"/>
       <c r="D61" s="102" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E61" s="102" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F61" s="102" t="str">
         <f t="shared" si="10"/>
@@ -12526,7 +12533,7 @@
         <v>57</v>
       </c>
       <c r="I61" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="J61" s="102" t="b">
         <v>0</v>
@@ -12536,7 +12543,7 @@
         <v>p-doip-ap-lb-bp</v>
       </c>
       <c r="L61" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M61" s="102" t="str">
         <f t="shared" si="11"/>
@@ -12546,7 +12553,7 @@
         <v>57</v>
       </c>
       <c r="O61" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="P61" s="102">
         <v>4</v>
@@ -12563,14 +12570,14 @@
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B62" s="102" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C62" s="102"/>
       <c r="D62" s="102" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E62" s="102" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="F62" s="102" t="str">
         <f t="shared" si="10"/>
@@ -12584,7 +12591,7 @@
         <v>57</v>
       </c>
       <c r="I62" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="J62" s="102" t="b">
         <v>0</v>
@@ -12594,7 +12601,7 @@
         <v>p-doip-adm-lb-bp</v>
       </c>
       <c r="L62" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M62" s="102" t="str">
         <f t="shared" si="11"/>
@@ -12604,7 +12611,7 @@
         <v>57</v>
       </c>
       <c r="O62" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="P62" s="102">
         <v>4</v>
@@ -12629,10 +12636,10 @@
         <v>BDP</v>
       </c>
       <c r="D63" s="74" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E63" s="74" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F63" s="74" t="str">
         <f t="shared" si="10"/>
@@ -12691,10 +12698,10 @@
         <v>BDP</v>
       </c>
       <c r="D64" s="74" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E64" s="74" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F64" s="74" t="str">
         <f t="shared" si="10"/>
@@ -12753,10 +12760,10 @@
         <v>BDP</v>
       </c>
       <c r="D65" s="82" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E65" s="82" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="F65" s="82" t="str">
         <f t="shared" si="10"/>
@@ -12815,10 +12822,10 @@
         <v>BDP</v>
       </c>
       <c r="D66" s="74" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E66" s="74" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="F66" s="74" t="str">
         <f t="shared" si="10"/>
@@ -19968,7 +19975,7 @@
     <row r="130" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A130" s="99"/>
       <c r="B130" s="73" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C130" s="73" t="str" cm="1">
         <f t="array" ref="C130">UPPER(INDEX(_xlfn.TEXTSPLIT($D130, "-"), 3))</f>
@@ -20021,7 +20028,7 @@
     <row r="131" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A131" s="99"/>
       <c r="B131" s="74" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C131" s="74" t="str" cm="1">
         <f t="array" ref="C131">UPPER(INDEX(_xlfn.TEXTSPLIT($D131, "-"), 3))</f>
@@ -20074,7 +20081,7 @@
     <row r="132" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A132" s="99"/>
       <c r="B132" s="73" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C132" s="73" t="str" cm="1">
         <f t="array" ref="C132">UPPER(INDEX(_xlfn.TEXTSPLIT($D132, "-"), 3))</f>
@@ -21454,7 +21461,7 @@
     <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158" s="99"/>
       <c r="B158" s="74" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C158" s="74" t="str" cm="1">
         <f t="array" ref="C158">UPPER(INDEX(_xlfn.TEXTSPLIT($D158, "-"), 3))</f>
@@ -21507,7 +21514,7 @@
     <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A159" s="99"/>
       <c r="B159" s="73" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C159" s="73" t="str" cm="1">
         <f t="array" ref="C159">UPPER(INDEX(_xlfn.TEXTSPLIT($D159, "-"), 3))</f>
@@ -21739,7 +21746,7 @@
         <v>632</v>
       </c>
       <c r="N2" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O2" s="74" t="str">
         <f t="shared" ref="O2:O6" si="0">SUBSTITUTE(F2,"hazr-","")&amp;"-osdisk"</f>
@@ -21828,7 +21835,7 @@
         <v>632</v>
       </c>
       <c r="N3" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O3" s="74" t="str">
         <f t="shared" si="0"/>
@@ -21917,7 +21924,7 @@
         <v>632</v>
       </c>
       <c r="N4" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O4" s="74" t="str">
         <f t="shared" si="0"/>
@@ -22006,7 +22013,7 @@
         <v>632</v>
       </c>
       <c r="N5" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O5" s="74" t="str">
         <f t="shared" si="0"/>
@@ -22077,7 +22084,7 @@
         <v>497</v>
       </c>
       <c r="H6" s="80" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="I6" s="80">
         <v>2</v>
@@ -22095,7 +22102,7 @@
         <v>632</v>
       </c>
       <c r="N6" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O6" s="74" t="str">
         <f t="shared" si="0"/>
@@ -22166,7 +22173,7 @@
         <v>498</v>
       </c>
       <c r="H7" s="80" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="I7" s="80">
         <v>2</v>
@@ -22184,7 +22191,7 @@
         <v>632</v>
       </c>
       <c r="N7" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O7" s="74" t="str">
         <f>SUBSTITUTE(F7,"hazr-","")&amp;"-osdisk"</f>
@@ -22273,7 +22280,7 @@
         <v>632</v>
       </c>
       <c r="N8" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O8" s="74" t="str">
         <f t="shared" ref="O8:O39" si="2">SUBSTITUTE(F8,"hazr-","")&amp;"-osdisk"</f>
@@ -22362,7 +22369,7 @@
         <v>632</v>
       </c>
       <c r="N9" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O9" s="74" t="str">
         <f t="shared" si="2"/>
@@ -22451,7 +22458,7 @@
         <v>632</v>
       </c>
       <c r="N10" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O10" s="74" t="str">
         <f t="shared" si="2"/>
@@ -22540,7 +22547,7 @@
         <v>632</v>
       </c>
       <c r="N11" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O11" s="74" t="str">
         <f t="shared" si="2"/>
@@ -22629,7 +22636,7 @@
         <v>632</v>
       </c>
       <c r="N12" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O12" s="74" t="str">
         <f t="shared" si="2"/>
@@ -22718,7 +22725,7 @@
         <v>632</v>
       </c>
       <c r="N13" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O13" s="74" t="str">
         <f t="shared" si="2"/>
@@ -22807,7 +22814,7 @@
         <v>632</v>
       </c>
       <c r="N14" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O14" s="74" t="str">
         <f t="shared" si="2"/>
@@ -22896,7 +22903,7 @@
         <v>632</v>
       </c>
       <c r="N15" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O15" s="74" t="str">
         <f t="shared" si="2"/>
@@ -22985,7 +22992,7 @@
         <v>632</v>
       </c>
       <c r="N16" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O16" s="74" t="str">
         <f t="shared" si="2"/>
@@ -23056,7 +23063,7 @@
         <v>508</v>
       </c>
       <c r="H17" s="80" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="I17" s="80">
         <v>2</v>
@@ -23074,7 +23081,7 @@
         <v>632</v>
       </c>
       <c r="N17" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O17" s="74" t="str">
         <f t="shared" si="2"/>
@@ -23145,7 +23152,7 @@
         <v>509</v>
       </c>
       <c r="H18" s="80" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="I18" s="80">
         <v>2</v>
@@ -23163,7 +23170,7 @@
         <v>632</v>
       </c>
       <c r="N18" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O18" s="74" t="str">
         <f t="shared" si="2"/>
@@ -23234,7 +23241,7 @@
         <v>510</v>
       </c>
       <c r="H19" s="80" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="I19" s="80">
         <v>2</v>
@@ -23252,7 +23259,7 @@
         <v>632</v>
       </c>
       <c r="N19" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O19" s="74" t="str">
         <f t="shared" si="2"/>
@@ -23323,7 +23330,7 @@
         <v>511</v>
       </c>
       <c r="H20" s="80" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="I20" s="80">
         <v>2</v>
@@ -23341,7 +23348,7 @@
         <v>632</v>
       </c>
       <c r="N20" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O20" s="74" t="str">
         <f t="shared" si="2"/>
@@ -23430,7 +23437,7 @@
         <v>632</v>
       </c>
       <c r="N21" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O21" s="74" t="str">
         <f t="shared" si="2"/>
@@ -23519,7 +23526,7 @@
         <v>632</v>
       </c>
       <c r="N22" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O22" s="74" t="str">
         <f t="shared" si="2"/>
@@ -23608,7 +23615,7 @@
         <v>632</v>
       </c>
       <c r="N23" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O23" s="74" t="str">
         <f t="shared" si="2"/>
@@ -23697,7 +23704,7 @@
         <v>632</v>
       </c>
       <c r="N24" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O24" s="74" t="str">
         <f t="shared" si="2"/>
@@ -23786,7 +23793,7 @@
         <v>632</v>
       </c>
       <c r="N25" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O25" s="74" t="str">
         <f t="shared" si="2"/>
@@ -23875,7 +23882,7 @@
         <v>632</v>
       </c>
       <c r="N26" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O26" s="74" t="str">
         <f t="shared" si="2"/>
@@ -23964,7 +23971,7 @@
         <v>632</v>
       </c>
       <c r="N27" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O27" s="74" t="str">
         <f t="shared" si="2"/>
@@ -24053,7 +24060,7 @@
         <v>632</v>
       </c>
       <c r="N28" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O28" s="74" t="str">
         <f t="shared" si="2"/>
@@ -24142,7 +24149,7 @@
         <v>632</v>
       </c>
       <c r="N29" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O29" s="74" t="str">
         <f t="shared" si="2"/>
@@ -24231,7 +24238,7 @@
         <v>632</v>
       </c>
       <c r="N30" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O30" s="74" t="str">
         <f t="shared" si="2"/>
@@ -24320,7 +24327,7 @@
         <v>632</v>
       </c>
       <c r="N31" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O31" s="74" t="str">
         <f t="shared" si="2"/>
@@ -24409,7 +24416,7 @@
         <v>632</v>
       </c>
       <c r="N32" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O32" s="74" t="str">
         <f t="shared" si="2"/>
@@ -24498,7 +24505,7 @@
         <v>632</v>
       </c>
       <c r="N33" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O33" s="74" t="str">
         <f t="shared" si="2"/>
@@ -24587,7 +24594,7 @@
         <v>632</v>
       </c>
       <c r="N34" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O34" s="74" t="str">
         <f t="shared" si="2"/>
@@ -24676,7 +24683,7 @@
         <v>633</v>
       </c>
       <c r="N35" s="98" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="O35" s="74" t="str">
         <f t="shared" si="2"/>
@@ -24765,7 +24772,7 @@
         <v>632</v>
       </c>
       <c r="N36" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O36" s="74" t="str">
         <f t="shared" si="2"/>
@@ -24854,7 +24861,7 @@
         <v>632</v>
       </c>
       <c r="N37" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O37" s="74" t="str">
         <f t="shared" si="2"/>
@@ -24943,7 +24950,7 @@
         <v>632</v>
       </c>
       <c r="N38" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O38" s="74" t="str">
         <f t="shared" si="2"/>
@@ -25032,7 +25039,7 @@
         <v>632</v>
       </c>
       <c r="N39" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O39" s="74" t="str">
         <f t="shared" si="2"/>
@@ -25121,7 +25128,7 @@
         <v>632</v>
       </c>
       <c r="N40" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O40" s="74" t="str">
         <f t="shared" ref="O40:O64" si="3">SUBSTITUTE(F40,"hazr-","")&amp;"-osdisk"</f>
@@ -25210,7 +25217,7 @@
         <v>632</v>
       </c>
       <c r="N41" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O41" s="74" t="str">
         <f t="shared" si="3"/>
@@ -25299,7 +25306,7 @@
         <v>632</v>
       </c>
       <c r="N42" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O42" s="74" t="str">
         <f t="shared" si="3"/>
@@ -25388,7 +25395,7 @@
         <v>632</v>
       </c>
       <c r="N43" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O43" s="74" t="str">
         <f t="shared" si="3"/>
@@ -25477,7 +25484,7 @@
         <v>632</v>
       </c>
       <c r="N44" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O44" s="74" t="str">
         <f t="shared" si="3"/>
@@ -25566,7 +25573,7 @@
         <v>632</v>
       </c>
       <c r="N45" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O45" s="74" t="str">
         <f t="shared" si="3"/>
@@ -25655,7 +25662,7 @@
         <v>632</v>
       </c>
       <c r="N46" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O46" s="74" t="str">
         <f t="shared" si="3"/>
@@ -25744,7 +25751,7 @@
         <v>632</v>
       </c>
       <c r="N47" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O47" s="74" t="str">
         <f t="shared" si="3"/>
@@ -25833,7 +25840,7 @@
         <v>632</v>
       </c>
       <c r="N48" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O48" s="74" t="str">
         <f t="shared" si="3"/>
@@ -25922,7 +25929,7 @@
         <v>632</v>
       </c>
       <c r="N49" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O49" s="74" t="str">
         <f t="shared" si="3"/>
@@ -26011,7 +26018,7 @@
         <v>632</v>
       </c>
       <c r="N50" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O50" s="74" t="str">
         <f t="shared" si="3"/>
@@ -26100,7 +26107,7 @@
         <v>632</v>
       </c>
       <c r="N51" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O51" s="74" t="str">
         <f t="shared" si="3"/>
@@ -26189,7 +26196,7 @@
         <v>632</v>
       </c>
       <c r="N52" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O52" s="74" t="str">
         <f t="shared" si="3"/>
@@ -26278,7 +26285,7 @@
         <v>632</v>
       </c>
       <c r="N53" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O53" s="74" t="str">
         <f t="shared" si="3"/>
@@ -26367,7 +26374,7 @@
         <v>632</v>
       </c>
       <c r="N54" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O54" s="74" t="str">
         <f t="shared" si="3"/>
@@ -26456,7 +26463,7 @@
         <v>632</v>
       </c>
       <c r="N55" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O55" s="74" t="str">
         <f t="shared" si="3"/>
@@ -26545,7 +26552,7 @@
         <v>632</v>
       </c>
       <c r="N56" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O56" s="74" t="str">
         <f t="shared" si="3"/>
@@ -26634,7 +26641,7 @@
         <v>632</v>
       </c>
       <c r="N57" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O57" s="74" t="str">
         <f t="shared" si="3"/>
@@ -26723,7 +26730,7 @@
         <v>632</v>
       </c>
       <c r="N58" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O58" s="74" t="str">
         <f t="shared" si="3"/>
@@ -26812,7 +26819,7 @@
         <v>632</v>
       </c>
       <c r="N59" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O59" s="74" t="str">
         <f t="shared" si="3"/>
@@ -26880,7 +26887,7 @@
         <v>407</v>
       </c>
       <c r="G60" s="80" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H60" s="80" t="s">
         <v>625</v>
@@ -26901,7 +26908,7 @@
         <v>632</v>
       </c>
       <c r="N60" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O60" s="74" t="str">
         <f t="shared" si="3"/>
@@ -26969,7 +26976,7 @@
         <v>408</v>
       </c>
       <c r="G61" s="80" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H61" s="80" t="s">
         <v>625</v>
@@ -26990,7 +26997,7 @@
         <v>632</v>
       </c>
       <c r="N61" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O61" s="74" t="str">
         <f t="shared" si="3"/>
@@ -27058,7 +27065,7 @@
         <v>409</v>
       </c>
       <c r="G62" s="80" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H62" s="80" t="s">
         <v>625</v>
@@ -27079,7 +27086,7 @@
         <v>632</v>
       </c>
       <c r="N62" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O62" s="74" t="str">
         <f t="shared" si="3"/>
@@ -27147,7 +27154,7 @@
         <v>410</v>
       </c>
       <c r="G63" s="80" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H63" s="80" t="s">
         <v>625</v>
@@ -27168,7 +27175,7 @@
         <v>632</v>
       </c>
       <c r="N63" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O63" s="74" t="str">
         <f t="shared" si="3"/>
@@ -27236,7 +27243,7 @@
         <v>411</v>
       </c>
       <c r="G64" s="80" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H64" s="80" t="s">
         <v>625</v>
@@ -27257,7 +27264,7 @@
         <v>632</v>
       </c>
       <c r="N64" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O64" s="74" t="str">
         <f t="shared" si="3"/>
@@ -27325,7 +27332,7 @@
         <v>412</v>
       </c>
       <c r="G65" s="80" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H65" s="80" t="s">
         <v>625</v>
@@ -27346,7 +27353,7 @@
         <v>632</v>
       </c>
       <c r="N65" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O65" s="74" t="str">
         <f t="shared" ref="O65:O70" si="4">SUBSTITUTE(F65,"hazr-","")&amp;"-osdisk"</f>
@@ -27435,7 +27442,7 @@
         <v>632</v>
       </c>
       <c r="N66" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O66" s="74" t="str">
         <f t="shared" si="4"/>
@@ -27524,7 +27531,7 @@
         <v>632</v>
       </c>
       <c r="N67" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O67" s="74" t="str">
         <f t="shared" si="4"/>
@@ -27613,7 +27620,7 @@
         <v>632</v>
       </c>
       <c r="N68" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O68" s="74" t="str">
         <f t="shared" si="4"/>
@@ -27702,7 +27709,7 @@
         <v>632</v>
       </c>
       <c r="N69" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O69" s="74" t="str">
         <f t="shared" si="4"/>
@@ -27791,7 +27798,7 @@
         <v>632</v>
       </c>
       <c r="N70" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O70" s="74" t="str">
         <f t="shared" si="4"/>
@@ -27880,7 +27887,7 @@
         <v>632</v>
       </c>
       <c r="N71" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O71" s="74" t="str">
         <f t="shared" ref="O71:O102" si="6">SUBSTITUTE(F71,"hazr-","")&amp;"-osdisk"</f>
@@ -27969,7 +27976,7 @@
         <v>632</v>
       </c>
       <c r="N72" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O72" s="74" t="str">
         <f t="shared" si="6"/>
@@ -28058,7 +28065,7 @@
         <v>632</v>
       </c>
       <c r="N73" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O73" s="74" t="str">
         <f t="shared" si="6"/>
@@ -28147,7 +28154,7 @@
         <v>632</v>
       </c>
       <c r="N74" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O74" s="74" t="str">
         <f t="shared" si="6"/>
@@ -28236,7 +28243,7 @@
         <v>632</v>
       </c>
       <c r="N75" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O75" s="74" t="str">
         <f t="shared" si="6"/>
@@ -28325,7 +28332,7 @@
         <v>632</v>
       </c>
       <c r="N76" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O76" s="74" t="str">
         <f t="shared" si="6"/>
@@ -28414,7 +28421,7 @@
         <v>632</v>
       </c>
       <c r="N77" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O77" s="74" t="str">
         <f t="shared" si="6"/>
@@ -28503,7 +28510,7 @@
         <v>632</v>
       </c>
       <c r="N78" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O78" s="74" t="str">
         <f t="shared" si="6"/>
@@ -28592,7 +28599,7 @@
         <v>632</v>
       </c>
       <c r="N79" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O79" s="74" t="str">
         <f t="shared" si="6"/>
@@ -28681,7 +28688,7 @@
         <v>632</v>
       </c>
       <c r="N80" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O80" s="74" t="str">
         <f t="shared" si="6"/>
@@ -28770,7 +28777,7 @@
         <v>632</v>
       </c>
       <c r="N81" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O81" s="74" t="str">
         <f t="shared" si="6"/>
@@ -28859,7 +28866,7 @@
         <v>632</v>
       </c>
       <c r="N82" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O82" s="74" t="str">
         <f t="shared" si="6"/>
@@ -28948,7 +28955,7 @@
         <v>632</v>
       </c>
       <c r="N83" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O83" s="74" t="str">
         <f t="shared" si="6"/>
@@ -29037,7 +29044,7 @@
         <v>632</v>
       </c>
       <c r="N84" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O84" s="74" t="str">
         <f t="shared" si="6"/>
@@ -29126,7 +29133,7 @@
         <v>632</v>
       </c>
       <c r="N85" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O85" s="74" t="str">
         <f t="shared" si="6"/>
@@ -29215,7 +29222,7 @@
         <v>632</v>
       </c>
       <c r="N86" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O86" s="74" t="str">
         <f t="shared" si="6"/>
@@ -29304,7 +29311,7 @@
         <v>632</v>
       </c>
       <c r="N87" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O87" s="74" t="str">
         <f t="shared" si="6"/>
@@ -29393,7 +29400,7 @@
         <v>632</v>
       </c>
       <c r="N88" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O88" s="74" t="str">
         <f t="shared" si="6"/>
@@ -29461,7 +29468,7 @@
         <v>436</v>
       </c>
       <c r="G89" s="80" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H89" s="80" t="s">
         <v>630</v>
@@ -29482,7 +29489,7 @@
         <v>632</v>
       </c>
       <c r="N89" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O89" s="74" t="str">
         <f t="shared" si="6"/>
@@ -29571,7 +29578,7 @@
         <v>632</v>
       </c>
       <c r="N90" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O90" s="74" t="str">
         <f t="shared" si="6"/>
@@ -29660,7 +29667,7 @@
         <v>632</v>
       </c>
       <c r="N91" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O91" s="74" t="str">
         <f t="shared" si="6"/>
@@ -29749,7 +29756,7 @@
         <v>632</v>
       </c>
       <c r="N92" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O92" s="74" t="str">
         <f t="shared" si="6"/>
@@ -29838,7 +29845,7 @@
         <v>632</v>
       </c>
       <c r="N93" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O93" s="74" t="str">
         <f t="shared" si="6"/>
@@ -29927,7 +29934,7 @@
         <v>632</v>
       </c>
       <c r="N94" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O94" s="74" t="str">
         <f t="shared" si="6"/>
@@ -30016,7 +30023,7 @@
         <v>632</v>
       </c>
       <c r="N95" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O95" s="74" t="str">
         <f t="shared" si="6"/>
@@ -30105,7 +30112,7 @@
         <v>632</v>
       </c>
       <c r="N96" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O96" s="74" t="str">
         <f t="shared" si="6"/>
@@ -30194,7 +30201,7 @@
         <v>632</v>
       </c>
       <c r="N97" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O97" s="74" t="str">
         <f t="shared" si="6"/>
@@ -30283,7 +30290,7 @@
         <v>632</v>
       </c>
       <c r="N98" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O98" s="74" t="str">
         <f t="shared" si="6"/>
@@ -30372,7 +30379,7 @@
         <v>632</v>
       </c>
       <c r="N99" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O99" s="74" t="str">
         <f t="shared" si="6"/>
@@ -30461,7 +30468,7 @@
         <v>632</v>
       </c>
       <c r="N100" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O100" s="74" t="str">
         <f t="shared" si="6"/>
@@ -30550,7 +30557,7 @@
         <v>632</v>
       </c>
       <c r="N101" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O101" s="74" t="str">
         <f t="shared" si="6"/>
@@ -30639,7 +30646,7 @@
         <v>632</v>
       </c>
       <c r="N102" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O102" s="74" t="str">
         <f t="shared" si="6"/>
@@ -30728,7 +30735,7 @@
         <v>632</v>
       </c>
       <c r="N103" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O103" s="74" t="str">
         <f t="shared" ref="O103:O134" si="8">SUBSTITUTE(F103,"hazr-","")&amp;"-osdisk"</f>
@@ -30817,7 +30824,7 @@
         <v>632</v>
       </c>
       <c r="N104" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O104" s="74" t="str">
         <f t="shared" si="8"/>
@@ -30906,7 +30913,7 @@
         <v>632</v>
       </c>
       <c r="N105" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O105" s="74" t="str">
         <f t="shared" si="8"/>
@@ -30995,7 +31002,7 @@
         <v>632</v>
       </c>
       <c r="N106" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O106" s="74" t="str">
         <f t="shared" si="8"/>
@@ -31084,7 +31091,7 @@
         <v>632</v>
       </c>
       <c r="N107" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O107" s="74" t="str">
         <f t="shared" si="8"/>
@@ -31173,7 +31180,7 @@
         <v>632</v>
       </c>
       <c r="N108" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O108" s="74" t="str">
         <f t="shared" si="8"/>
@@ -31262,7 +31269,7 @@
         <v>632</v>
       </c>
       <c r="N109" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O109" s="74" t="str">
         <f t="shared" si="8"/>
@@ -31351,7 +31358,7 @@
         <v>632</v>
       </c>
       <c r="N110" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O110" s="74" t="str">
         <f t="shared" si="8"/>
@@ -31440,7 +31447,7 @@
         <v>632</v>
       </c>
       <c r="N111" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O111" s="74" t="str">
         <f t="shared" si="8"/>
@@ -31529,7 +31536,7 @@
         <v>632</v>
       </c>
       <c r="N112" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O112" s="74" t="str">
         <f t="shared" si="8"/>
@@ -31618,7 +31625,7 @@
         <v>632</v>
       </c>
       <c r="N113" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O113" s="74" t="str">
         <f t="shared" si="8"/>
@@ -31707,7 +31714,7 @@
         <v>632</v>
       </c>
       <c r="N114" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O114" s="74" t="str">
         <f t="shared" si="8"/>
@@ -31796,7 +31803,7 @@
         <v>632</v>
       </c>
       <c r="N115" s="74" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="O115" s="74" t="str">
         <f t="shared" si="8"/>
@@ -31885,7 +31892,7 @@
         <v>632</v>
       </c>
       <c r="N116" s="74" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O116" s="74" t="str">
         <f t="shared" si="8"/>
@@ -31956,7 +31963,7 @@
         <v>601</v>
       </c>
       <c r="H117" s="80" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="I117" s="80">
         <v>2</v>
@@ -31974,7 +31981,7 @@
         <v>632</v>
       </c>
       <c r="N117" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O117" s="74" t="str">
         <f t="shared" si="8"/>
@@ -32063,7 +32070,7 @@
         <v>632</v>
       </c>
       <c r="N118" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O118" s="74" t="str">
         <f t="shared" si="8"/>
@@ -32134,7 +32141,7 @@
         <v>603</v>
       </c>
       <c r="H119" s="80" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="I119" s="80">
         <v>4</v>
@@ -32152,7 +32159,7 @@
         <v>632</v>
       </c>
       <c r="N119" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O119" s="74" t="str">
         <f t="shared" si="8"/>
@@ -32204,7 +32211,7 @@
     <row r="120" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A120" s="90"/>
       <c r="B120" s="74" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C120" s="74" t="str" cm="1">
         <f t="array" ref="C120">UPPER(INDEX(_xlfn.TEXTSPLIT($D120, "-"), 3))</f>
@@ -32241,7 +32248,7 @@
         <v>632</v>
       </c>
       <c r="N120" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O120" s="74" t="str">
         <f t="shared" si="8"/>
@@ -32293,7 +32300,7 @@
     <row r="121" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A121" s="90"/>
       <c r="B121" s="74" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C121" s="74" t="str" cm="1">
         <f t="array" ref="C121">UPPER(INDEX(_xlfn.TEXTSPLIT($D121, "-"), 3))</f>
@@ -32330,7 +32337,7 @@
         <v>632</v>
       </c>
       <c r="N121" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O121" s="74" t="str">
         <f t="shared" si="8"/>
@@ -32382,7 +32389,7 @@
     <row r="122" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A122" s="90"/>
       <c r="B122" s="74" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C122" s="74" t="str" cm="1">
         <f t="array" ref="C122">UPPER(INDEX(_xlfn.TEXTSPLIT($D122, "-"), 3))</f>
@@ -32419,7 +32426,7 @@
         <v>632</v>
       </c>
       <c r="N122" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O122" s="74" t="str">
         <f t="shared" si="8"/>
@@ -32508,7 +32515,7 @@
         <v>632</v>
       </c>
       <c r="N123" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O123" s="74" t="str">
         <f t="shared" si="8"/>
@@ -32559,11 +32566,11 @@
     </row>
     <row r="124" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B124" s="102" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C124" s="102"/>
       <c r="D124" s="102" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E124" s="102" t="s">
         <v>24</v>
@@ -32572,10 +32579,10 @@
         <v>468</v>
       </c>
       <c r="G124" s="102" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H124" s="102" t="s">
         <v>1082</v>
-      </c>
-      <c r="H124" s="102" t="s">
-        <v>1083</v>
       </c>
       <c r="I124" s="102">
         <v>2</v>
@@ -32590,7 +32597,7 @@
         <v>178</v>
       </c>
       <c r="M124" s="102" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="N124" s="102"/>
       <c r="O124" s="102" t="str">
@@ -32623,7 +32630,7 @@
         <v>345</v>
       </c>
       <c r="Z124" s="102" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="AA124" s="102" t="b">
         <v>1</v>
@@ -32642,11 +32649,11 @@
     </row>
     <row r="125" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B125" s="102" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C125" s="102"/>
       <c r="D125" s="102" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E125" s="102" t="s">
         <v>24</v>
@@ -32655,10 +32662,10 @@
         <v>469</v>
       </c>
       <c r="G125" s="102" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H125" s="102" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="I125" s="102">
         <v>2</v>
@@ -32673,7 +32680,7 @@
         <v>178</v>
       </c>
       <c r="M125" s="102" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="N125" s="102"/>
       <c r="O125" s="102" t="str">
@@ -32706,7 +32713,7 @@
         <v>345</v>
       </c>
       <c r="Z125" s="102" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="AA125" s="102" t="b">
         <v>1</v>
@@ -32763,7 +32770,7 @@
         <v>632</v>
       </c>
       <c r="N126" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O126" s="74" t="str">
         <f t="shared" si="8"/>
@@ -32852,7 +32859,7 @@
         <v>632</v>
       </c>
       <c r="N127" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O127" s="74" t="str">
         <f t="shared" si="8"/>
@@ -32941,7 +32948,7 @@
         <v>632</v>
       </c>
       <c r="N128" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O128" s="74" t="str">
         <f t="shared" si="8"/>
@@ -33030,7 +33037,7 @@
         <v>632</v>
       </c>
       <c r="N129" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O129" s="74" t="str">
         <f t="shared" si="8"/>
@@ -33119,7 +33126,7 @@
         <v>632</v>
       </c>
       <c r="N130" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O130" s="74" t="str">
         <f t="shared" si="8"/>
@@ -33208,7 +33215,7 @@
         <v>632</v>
       </c>
       <c r="N131" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O131" s="74" t="str">
         <f t="shared" si="8"/>
@@ -33267,7 +33274,7 @@
         <v>DOIP</v>
       </c>
       <c r="D132" s="74" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E132" s="74" t="s">
         <v>24</v>
@@ -33276,10 +33283,10 @@
         <v>476</v>
       </c>
       <c r="G132" s="74" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H132" s="74" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="I132" s="74">
         <v>2</v>
@@ -33294,10 +33301,10 @@
         <v>178</v>
       </c>
       <c r="M132" s="74" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="N132" s="112" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="O132" s="74" t="str">
         <f t="shared" si="8"/>
@@ -33329,7 +33336,7 @@
         <v>345</v>
       </c>
       <c r="Z132" s="74" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="AA132" s="74" t="b">
         <v>1</v>
@@ -33356,7 +33363,7 @@
         <v>DOIP</v>
       </c>
       <c r="D133" s="74" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E133" s="74" t="s">
         <v>24</v>
@@ -33365,10 +33372,10 @@
         <v>477</v>
       </c>
       <c r="G133" s="74" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H133" s="74" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="I133" s="74">
         <v>2</v>
@@ -33383,10 +33390,10 @@
         <v>178</v>
       </c>
       <c r="M133" s="74" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="N133" s="112" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="O133" s="74" t="str">
         <f t="shared" si="8"/>
@@ -33418,7 +33425,7 @@
         <v>345</v>
       </c>
       <c r="Z133" s="74" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="AA133" s="74" t="b">
         <v>1</v>
@@ -33445,7 +33452,7 @@
         <v>DOIP</v>
       </c>
       <c r="D134" s="74" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E134" s="74" t="s">
         <v>24</v>
@@ -33454,10 +33461,10 @@
         <v>478</v>
       </c>
       <c r="G134" s="74" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H134" s="74" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="I134" s="74">
         <v>2</v>
@@ -33472,10 +33479,10 @@
         <v>178</v>
       </c>
       <c r="M134" s="74" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="N134" s="112" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="O134" s="74" t="str">
         <f t="shared" si="8"/>
@@ -33507,7 +33514,7 @@
         <v>345</v>
       </c>
       <c r="Z134" s="74" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="AA134" s="74" t="b">
         <v>1</v>
@@ -33534,7 +33541,7 @@
         <v>DOIP</v>
       </c>
       <c r="D135" s="74" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E135" s="74" t="s">
         <v>24</v>
@@ -33543,10 +33550,10 @@
         <v>479</v>
       </c>
       <c r="G135" s="74" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H135" s="74" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="I135" s="74">
         <v>2</v>
@@ -33561,10 +33568,10 @@
         <v>178</v>
       </c>
       <c r="M135" s="74" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="N135" s="112" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="O135" s="74" t="str">
         <f t="shared" ref="O135:O146" si="10">SUBSTITUTE(F135,"hazr-","")&amp;"-osdisk"</f>
@@ -33596,7 +33603,7 @@
         <v>345</v>
       </c>
       <c r="Z135" s="74" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="AA135" s="74" t="b">
         <v>1</v>
@@ -33623,7 +33630,7 @@
         <v>DOIP</v>
       </c>
       <c r="D136" s="74" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E136" s="74" t="s">
         <v>24</v>
@@ -33632,10 +33639,10 @@
         <v>480</v>
       </c>
       <c r="G136" s="74" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H136" s="74" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="I136" s="74">
         <v>2</v>
@@ -33650,10 +33657,10 @@
         <v>178</v>
       </c>
       <c r="M136" s="74" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="N136" s="112" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="O136" s="74" t="str">
         <f t="shared" si="10"/>
@@ -33685,7 +33692,7 @@
         <v>345</v>
       </c>
       <c r="Z136" s="74" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="AA136" s="74" t="b">
         <v>1</v>
@@ -33712,7 +33719,7 @@
         <v>DOIP</v>
       </c>
       <c r="D137" s="74" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E137" s="74" t="s">
         <v>24</v>
@@ -33721,10 +33728,10 @@
         <v>481</v>
       </c>
       <c r="G137" s="74" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H137" s="74" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="I137" s="74">
         <v>2</v>
@@ -33739,10 +33746,10 @@
         <v>178</v>
       </c>
       <c r="M137" s="74" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="N137" s="112" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="O137" s="74" t="str">
         <f t="shared" si="10"/>
@@ -33774,7 +33781,7 @@
         <v>345</v>
       </c>
       <c r="Z137" s="74" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="AA137" s="74" t="b">
         <v>1</v>
@@ -33831,7 +33838,7 @@
         <v>632</v>
       </c>
       <c r="N138" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O138" s="74" t="str">
         <f t="shared" si="10"/>
@@ -33920,7 +33927,7 @@
         <v>632</v>
       </c>
       <c r="N139" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O139" s="74" t="str">
         <f t="shared" si="10"/>
@@ -34009,7 +34016,7 @@
         <v>632</v>
       </c>
       <c r="N140" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O140" s="74" t="str">
         <f t="shared" si="10"/>
@@ -34098,7 +34105,7 @@
         <v>632</v>
       </c>
       <c r="N141" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O141" s="74" t="str">
         <f t="shared" si="10"/>
@@ -34187,7 +34194,7 @@
         <v>632</v>
       </c>
       <c r="N142" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O142" s="74" t="str">
         <f t="shared" si="10"/>
@@ -34276,7 +34283,7 @@
         <v>632</v>
       </c>
       <c r="N143" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O143" s="74" t="str">
         <f t="shared" si="10"/>
@@ -34365,7 +34372,7 @@
         <v>632</v>
       </c>
       <c r="N144" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O144" s="74" t="str">
         <f t="shared" si="10"/>
@@ -34417,7 +34424,7 @@
     <row r="145" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A145" s="90"/>
       <c r="B145" s="74" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C145" s="74" t="str" cm="1">
         <f t="array" ref="C145">UPPER(INDEX(_xlfn.TEXTSPLIT($D145, "-"), 3))</f>
@@ -34433,7 +34440,7 @@
         <v>489</v>
       </c>
       <c r="G145" s="80" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H145" s="80" t="s">
         <v>626</v>
@@ -34454,7 +34461,7 @@
         <v>632</v>
       </c>
       <c r="N145" s="98" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O145" s="74" t="str">
         <f t="shared" si="10"/>
@@ -34486,7 +34493,7 @@
         <v>223</v>
       </c>
       <c r="Z145" s="74" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AA145" s="74" t="b">
         <v>1</v>
@@ -34506,7 +34513,7 @@
     <row r="146" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A146" s="90"/>
       <c r="B146" s="74" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C146" s="74" t="str" cm="1">
         <f t="array" ref="C146">UPPER(INDEX(_xlfn.TEXTSPLIT($D146, "-"), 3))</f>
@@ -34522,7 +34529,7 @@
         <v>490</v>
       </c>
       <c r="G146" s="80" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H146" s="80" t="s">
         <v>622</v>
@@ -34543,7 +34550,7 @@
         <v>632</v>
       </c>
       <c r="N146" s="98" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O146" s="74" t="str">
         <f t="shared" si="10"/>
@@ -34575,7 +34582,7 @@
         <v>223</v>
       </c>
       <c r="Z146" s="74" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AA146" s="74" t="b">
         <v>1</v>
@@ -36043,7 +36050,7 @@
         <v>239</v>
       </c>
       <c r="H36" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I36" s="73" t="s">
         <v>383</v>
@@ -36083,7 +36090,7 @@
         <v>239</v>
       </c>
       <c r="H37" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I37" s="74" t="s">
         <v>384</v>
@@ -36123,7 +36130,7 @@
         <v>239</v>
       </c>
       <c r="H38" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I38" s="73" t="s">
         <v>385</v>
@@ -36163,7 +36170,7 @@
         <v>239</v>
       </c>
       <c r="H39" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I39" s="74" t="s">
         <v>386</v>
@@ -36203,7 +36210,7 @@
         <v>238</v>
       </c>
       <c r="H40" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I40" s="73" t="s">
         <v>387</v>
@@ -36243,7 +36250,7 @@
         <v>238</v>
       </c>
       <c r="H41" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I41" s="74" t="s">
         <v>388</v>
@@ -36283,7 +36290,7 @@
         <v>239</v>
       </c>
       <c r="H42" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I42" s="73" t="s">
         <v>389</v>
@@ -36323,7 +36330,7 @@
         <v>239</v>
       </c>
       <c r="H43" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I43" s="74" t="s">
         <v>390</v>
@@ -36363,7 +36370,7 @@
         <v>238</v>
       </c>
       <c r="H44" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I44" s="73" t="s">
         <v>391</v>
@@ -36403,7 +36410,7 @@
         <v>238</v>
       </c>
       <c r="H45" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I45" s="74" t="s">
         <v>392</v>
@@ -36443,7 +36450,7 @@
         <v>238</v>
       </c>
       <c r="H46" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I46" s="73" t="s">
         <v>393</v>
@@ -36483,7 +36490,7 @@
         <v>238</v>
       </c>
       <c r="H47" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I47" s="74" t="s">
         <v>394</v>
@@ -36523,7 +36530,7 @@
         <v>239</v>
       </c>
       <c r="H48" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I48" s="73" t="s">
         <v>395</v>
@@ -36563,7 +36570,7 @@
         <v>239</v>
       </c>
       <c r="H49" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I49" s="74" t="s">
         <v>396</v>
@@ -36603,7 +36610,7 @@
         <v>239</v>
       </c>
       <c r="H50" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I50" s="73" t="s">
         <v>397</v>
@@ -36643,7 +36650,7 @@
         <v>239</v>
       </c>
       <c r="H51" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I51" s="74" t="s">
         <v>398</v>
@@ -36683,7 +36690,7 @@
         <v>238</v>
       </c>
       <c r="H52" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I52" s="73" t="s">
         <v>399</v>
@@ -36723,7 +36730,7 @@
         <v>238</v>
       </c>
       <c r="H53" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I53" s="74" t="s">
         <v>400</v>
@@ -36763,7 +36770,7 @@
         <v>239</v>
       </c>
       <c r="H54" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I54" s="73" t="s">
         <v>401</v>
@@ -36803,7 +36810,7 @@
         <v>239</v>
       </c>
       <c r="H55" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I55" s="74" t="s">
         <v>402</v>
@@ -36843,7 +36850,7 @@
         <v>239</v>
       </c>
       <c r="H56" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I56" s="73" t="s">
         <v>403</v>
@@ -36883,7 +36890,7 @@
         <v>239</v>
       </c>
       <c r="H57" s="74" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I57" s="74" t="s">
         <v>404</v>
@@ -36923,7 +36930,7 @@
         <v>239</v>
       </c>
       <c r="H58" s="73" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I58" s="73" t="s">
         <v>405</v>
@@ -36963,7 +36970,7 @@
         <v>239</v>
       </c>
       <c r="H59" s="74" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I59" s="74" t="s">
         <v>406</v>
@@ -37003,7 +37010,7 @@
         <v>239</v>
       </c>
       <c r="H60" s="73" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I60" s="73" t="s">
         <v>407</v>
@@ -37043,7 +37050,7 @@
         <v>239</v>
       </c>
       <c r="H61" s="74" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I61" s="74" t="s">
         <v>408</v>
@@ -37083,7 +37090,7 @@
         <v>239</v>
       </c>
       <c r="H62" s="73" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I62" s="73" t="s">
         <v>409</v>
@@ -37123,7 +37130,7 @@
         <v>239</v>
       </c>
       <c r="H63" s="74" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I63" s="74" t="s">
         <v>410</v>
@@ -37163,7 +37170,7 @@
         <v>239</v>
       </c>
       <c r="H64" s="73" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I64" s="73" t="s">
         <v>411</v>
@@ -37203,7 +37210,7 @@
         <v>239</v>
       </c>
       <c r="H65" s="74" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I65" s="74" t="s">
         <v>412</v>
@@ -37243,7 +37250,7 @@
         <v>239</v>
       </c>
       <c r="H66" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I66" s="73" t="s">
         <v>413</v>
@@ -37283,7 +37290,7 @@
         <v>239</v>
       </c>
       <c r="H67" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I67" s="74" t="s">
         <v>414</v>
@@ -37323,7 +37330,7 @@
         <v>239</v>
       </c>
       <c r="H68" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I68" s="73" t="s">
         <v>415</v>
@@ -37363,7 +37370,7 @@
         <v>239</v>
       </c>
       <c r="H69" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I69" s="74" t="s">
         <v>416</v>
@@ -37403,7 +37410,7 @@
         <v>239</v>
       </c>
       <c r="H70" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I70" s="73" t="s">
         <v>417</v>
@@ -37443,7 +37450,7 @@
         <v>239</v>
       </c>
       <c r="H71" s="74" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="I71" s="74" t="s">
         <v>418</v>
@@ -37483,7 +37490,7 @@
         <v>239</v>
       </c>
       <c r="H72" s="73" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="I72" s="73" t="s">
         <v>419</v>
@@ -37523,7 +37530,7 @@
         <v>239</v>
       </c>
       <c r="H73" s="74" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="I73" s="74" t="s">
         <v>420</v>
@@ -37563,7 +37570,7 @@
         <v>239</v>
       </c>
       <c r="H74" s="73" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="I74" s="73" t="s">
         <v>421</v>
@@ -37603,7 +37610,7 @@
         <v>239</v>
       </c>
       <c r="H75" s="74" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I75" s="74" t="s">
         <v>422</v>
@@ -37643,7 +37650,7 @@
         <v>239</v>
       </c>
       <c r="H76" s="73" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I76" s="73" t="s">
         <v>423</v>
@@ -37683,7 +37690,7 @@
         <v>239</v>
       </c>
       <c r="H77" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I77" s="74" t="s">
         <v>424</v>
@@ -37723,7 +37730,7 @@
         <v>238</v>
       </c>
       <c r="H78" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I78" s="73" t="s">
         <v>425</v>
@@ -37763,7 +37770,7 @@
         <v>238</v>
       </c>
       <c r="H79" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I79" s="74" t="s">
         <v>426</v>
@@ -37803,7 +37810,7 @@
         <v>238</v>
       </c>
       <c r="H80" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I80" s="73" t="s">
         <v>427</v>
@@ -37843,7 +37850,7 @@
         <v>238</v>
       </c>
       <c r="H81" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I81" s="74" t="s">
         <v>428</v>
@@ -37883,7 +37890,7 @@
         <v>238</v>
       </c>
       <c r="H82" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I82" s="73" t="s">
         <v>429</v>
@@ -37923,7 +37930,7 @@
         <v>238</v>
       </c>
       <c r="H83" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I83" s="74" t="s">
         <v>430</v>
@@ -37963,7 +37970,7 @@
         <v>238</v>
       </c>
       <c r="H84" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I84" s="73" t="s">
         <v>431</v>
@@ -38003,7 +38010,7 @@
         <v>238</v>
       </c>
       <c r="H85" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I85" s="74" t="s">
         <v>432</v>
@@ -38043,7 +38050,7 @@
         <v>238</v>
       </c>
       <c r="H86" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I86" s="73" t="s">
         <v>433</v>
@@ -38083,7 +38090,7 @@
         <v>239</v>
       </c>
       <c r="H87" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I87" s="74" t="s">
         <v>434</v>
@@ -38123,7 +38130,7 @@
         <v>239</v>
       </c>
       <c r="H88" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I88" s="73" t="s">
         <v>435</v>
@@ -38163,7 +38170,7 @@
         <v>239</v>
       </c>
       <c r="H89" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I89" s="74" t="s">
         <v>436</v>
@@ -38203,7 +38210,7 @@
         <v>239</v>
       </c>
       <c r="H90" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I90" s="73" t="s">
         <v>437</v>
@@ -38243,7 +38250,7 @@
         <v>239</v>
       </c>
       <c r="H91" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I91" s="74" t="s">
         <v>438</v>
@@ -38283,7 +38290,7 @@
         <v>239</v>
       </c>
       <c r="H92" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I92" s="73" t="s">
         <v>439</v>
@@ -38323,7 +38330,7 @@
         <v>239</v>
       </c>
       <c r="H93" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I93" s="74" t="s">
         <v>440</v>
@@ -38363,7 +38370,7 @@
         <v>239</v>
       </c>
       <c r="H94" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I94" s="73" t="s">
         <v>441</v>
@@ -38403,7 +38410,7 @@
         <v>239</v>
       </c>
       <c r="H95" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I95" s="74" t="s">
         <v>442</v>
@@ -38443,7 +38450,7 @@
         <v>238</v>
       </c>
       <c r="H96" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I96" s="73" t="s">
         <v>443</v>
@@ -38483,7 +38490,7 @@
         <v>238</v>
       </c>
       <c r="H97" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I97" s="74" t="s">
         <v>444</v>
@@ -38523,7 +38530,7 @@
         <v>239</v>
       </c>
       <c r="H98" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I98" s="73" t="s">
         <v>445</v>
@@ -38563,7 +38570,7 @@
         <v>239</v>
       </c>
       <c r="H99" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I99" s="74" t="s">
         <v>446</v>
@@ -38603,7 +38610,7 @@
         <v>239</v>
       </c>
       <c r="H100" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I100" s="73" t="s">
         <v>447</v>
@@ -38643,7 +38650,7 @@
         <v>239</v>
       </c>
       <c r="H101" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I101" s="74" t="s">
         <v>448</v>
@@ -38683,7 +38690,7 @@
         <v>239</v>
       </c>
       <c r="H102" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I102" s="73" t="s">
         <v>449</v>
@@ -38723,7 +38730,7 @@
         <v>239</v>
       </c>
       <c r="H103" s="74" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I103" s="74" t="s">
         <v>450</v>
@@ -38763,7 +38770,7 @@
         <v>239</v>
       </c>
       <c r="H104" s="73" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="I104" s="73" t="s">
         <v>451</v>
@@ -38803,7 +38810,7 @@
         <v>239</v>
       </c>
       <c r="H105" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I105" s="74" t="s">
         <v>452</v>
@@ -38843,7 +38850,7 @@
         <v>239</v>
       </c>
       <c r="H106" s="73" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I106" s="73" t="s">
         <v>453</v>
@@ -38883,7 +38890,7 @@
         <v>239</v>
       </c>
       <c r="H107" s="74" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="I107" s="74" t="s">
         <v>454</v>
@@ -38923,7 +38930,7 @@
         <v>239</v>
       </c>
       <c r="H108" s="73" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="I108" s="73" t="s">
         <v>455</v>
@@ -38963,7 +38970,7 @@
         <v>239</v>
       </c>
       <c r="H109" s="74" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="I109" s="74" t="s">
         <v>456</v>
@@ -39003,7 +39010,7 @@
         <v>239</v>
       </c>
       <c r="H110" s="73" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="I110" s="73" t="s">
         <v>457</v>
@@ -39043,7 +39050,7 @@
         <v>239</v>
       </c>
       <c r="H111" s="74" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="I111" s="74" t="s">
         <v>458</v>
@@ -39083,7 +39090,7 @@
         <v>239</v>
       </c>
       <c r="H112" s="73" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="I112" s="73" t="s">
         <v>459</v>
@@ -39123,7 +39130,7 @@
         <v>239</v>
       </c>
       <c r="H113" s="74" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="I113" s="74" t="s">
         <v>460</v>
@@ -39163,7 +39170,7 @@
         <v>239</v>
       </c>
       <c r="H114" s="73" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="I114" s="73" t="s">
         <v>461</v>
@@ -39203,7 +39210,7 @@
         <v>239</v>
       </c>
       <c r="H115" s="74" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="I115" s="74" t="s">
         <v>462</v>
@@ -39243,7 +39250,7 @@
         <v>239</v>
       </c>
       <c r="H116" s="73" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="I116" s="73" t="s">
         <v>463</v>
@@ -39283,7 +39290,7 @@
         <v>239</v>
       </c>
       <c r="H117" s="74" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="I117" s="74" t="s">
         <v>464</v>
@@ -39323,7 +39330,7 @@
         <v>239</v>
       </c>
       <c r="H118" s="73" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="I118" s="73" t="s">
         <v>465</v>
@@ -39363,7 +39370,7 @@
         <v>239</v>
       </c>
       <c r="H119" s="74" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="I119" s="74" t="s">
         <v>466</v>
@@ -39383,7 +39390,7 @@
     <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="90"/>
       <c r="B120" s="73" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C120" s="78" t="str" cm="1">
         <f t="array" ref="C120">UPPER(INDEX(_xlfn.TEXTSPLIT($E120, "-"), 2))</f>
@@ -39403,7 +39410,7 @@
         <v>239</v>
       </c>
       <c r="H120" s="73" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="I120" s="73" t="s">
         <v>231</v>
@@ -39423,7 +39430,7 @@
     <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="90"/>
       <c r="B121" s="74" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C121" s="80" t="str" cm="1">
         <f t="array" ref="C121">UPPER(INDEX(_xlfn.TEXTSPLIT($E121, "-"), 2))</f>
@@ -39443,7 +39450,7 @@
         <v>239</v>
       </c>
       <c r="H121" s="74" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="I121" s="74" t="s">
         <v>230</v>
@@ -39463,7 +39470,7 @@
     <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="90"/>
       <c r="B122" s="73" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C122" s="78" t="str" cm="1">
         <f t="array" ref="C122">UPPER(INDEX(_xlfn.TEXTSPLIT($E122, "-"), 2))</f>
@@ -39483,7 +39490,7 @@
         <v>239</v>
       </c>
       <c r="H122" s="73" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="I122" s="73" t="s">
         <v>234</v>
@@ -39523,7 +39530,7 @@
         <v>239</v>
       </c>
       <c r="H123" s="74" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="I123" s="74" t="s">
         <v>467</v>
@@ -39562,7 +39569,7 @@
         <v>238</v>
       </c>
       <c r="H124" s="73" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="I124" s="73" t="s">
         <v>468</v>
@@ -39601,7 +39608,7 @@
         <v>238</v>
       </c>
       <c r="H125" s="74" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="I125" s="74" t="s">
         <v>469</v>
@@ -39641,7 +39648,7 @@
         <v>239</v>
       </c>
       <c r="H126" s="73" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="I126" s="73" t="s">
         <v>470</v>
@@ -39681,7 +39688,7 @@
         <v>239</v>
       </c>
       <c r="H127" s="74" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="I127" s="74" t="s">
         <v>471</v>
@@ -39721,7 +39728,7 @@
         <v>239</v>
       </c>
       <c r="H128" s="73" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="I128" s="73" t="s">
         <v>472</v>
@@ -39761,7 +39768,7 @@
         <v>239</v>
       </c>
       <c r="H129" s="74" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="I129" s="74" t="s">
         <v>473</v>
@@ -39801,7 +39808,7 @@
         <v>239</v>
       </c>
       <c r="H130" s="73" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="I130" s="73" t="s">
         <v>474</v>
@@ -39841,7 +39848,7 @@
         <v>239</v>
       </c>
       <c r="H131" s="74" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="I131" s="74" t="s">
         <v>475</v>
@@ -39881,7 +39888,7 @@
         <v>239</v>
       </c>
       <c r="H132" s="73" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="I132" s="73" t="s">
         <v>476</v>
@@ -39921,7 +39928,7 @@
         <v>239</v>
       </c>
       <c r="H133" s="74" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="I133" s="74" t="s">
         <v>477</v>
@@ -39961,7 +39968,7 @@
         <v>239</v>
       </c>
       <c r="H134" s="73" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="I134" s="73" t="s">
         <v>478</v>
@@ -40001,7 +40008,7 @@
         <v>239</v>
       </c>
       <c r="H135" s="74" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="I135" s="74" t="s">
         <v>479</v>
@@ -40041,7 +40048,7 @@
         <v>238</v>
       </c>
       <c r="H136" s="73" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="I136" s="73" t="s">
         <v>480</v>
@@ -40081,7 +40088,7 @@
         <v>238</v>
       </c>
       <c r="H137" s="74" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="I137" s="74" t="s">
         <v>481</v>
@@ -40121,7 +40128,7 @@
         <v>239</v>
       </c>
       <c r="H138" s="73" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="I138" s="73" t="s">
         <v>482</v>
@@ -40161,7 +40168,7 @@
         <v>239</v>
       </c>
       <c r="H139" s="74" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="I139" s="74" t="s">
         <v>483</v>
@@ -40201,7 +40208,7 @@
         <v>239</v>
       </c>
       <c r="H140" s="73" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="I140" s="73" t="s">
         <v>484</v>
@@ -40241,7 +40248,7 @@
         <v>202</v>
       </c>
       <c r="H141" s="74" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="I141" s="74" t="s">
         <v>485</v>
@@ -40281,7 +40288,7 @@
         <v>202</v>
       </c>
       <c r="H142" s="73" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="I142" s="73" t="s">
         <v>486</v>
@@ -40321,7 +40328,7 @@
         <v>202</v>
       </c>
       <c r="H143" s="74" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="I143" s="74" t="s">
         <v>487</v>
@@ -40361,7 +40368,7 @@
         <v>239</v>
       </c>
       <c r="H144" s="73" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="I144" s="73" t="s">
         <v>488</v>
@@ -40381,10 +40388,10 @@
     <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" s="90"/>
       <c r="B145" s="80" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C145" s="80" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="D145" s="80" t="s">
         <v>232</v>
@@ -40400,7 +40407,7 @@
         <v>223</v>
       </c>
       <c r="H145" s="74" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="I145" s="74" t="s">
         <v>489</v>
@@ -40420,10 +40427,10 @@
     <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" s="90"/>
       <c r="B146" s="78" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C146" s="78" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="D146" s="78" t="s">
         <v>232</v>
@@ -40439,7 +40446,7 @@
         <v>223</v>
       </c>
       <c r="H146" s="73" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="I146" s="73" t="s">
         <v>490</v>
@@ -42330,7 +42337,7 @@
         <v>221</v>
       </c>
       <c r="J2" s="74" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -42361,7 +42368,7 @@
         <v>221</v>
       </c>
       <c r="J3" s="82" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -42392,7 +42399,7 @@
         <v>221</v>
       </c>
       <c r="J4" s="74" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -42423,7 +42430,7 @@
         <v>221</v>
       </c>
       <c r="J5" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -42454,7 +42461,7 @@
         <v>221</v>
       </c>
       <c r="J6" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -42485,7 +42492,7 @@
         <v>221</v>
       </c>
       <c r="J7" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -42510,13 +42517,13 @@
         <v>330</v>
       </c>
       <c r="H8" s="74" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>221</v>
       </c>
       <c r="J8" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -42547,7 +42554,7 @@
         <v>221</v>
       </c>
       <c r="J9" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -42578,7 +42585,7 @@
         <v>221</v>
       </c>
       <c r="J10" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -42609,7 +42616,7 @@
         <v>221</v>
       </c>
       <c r="J11" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -42640,7 +42647,7 @@
         <v>221</v>
       </c>
       <c r="J12" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -42671,7 +42678,7 @@
         <v>221</v>
       </c>
       <c r="J13" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -42702,7 +42709,7 @@
         <v>221</v>
       </c>
       <c r="J14" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -42733,7 +42740,7 @@
         <v>221</v>
       </c>
       <c r="J15" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -42764,7 +42771,7 @@
         <v>221</v>
       </c>
       <c r="J16" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -42795,7 +42802,7 @@
         <v>221</v>
       </c>
       <c r="J17" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -42826,7 +42833,7 @@
         <v>221</v>
       </c>
       <c r="J18" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -42857,7 +42864,7 @@
         <v>221</v>
       </c>
       <c r="J19" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -42888,7 +42895,7 @@
         <v>221</v>
       </c>
       <c r="J20" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -42919,7 +42926,7 @@
         <v>221</v>
       </c>
       <c r="J21" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -42961,7 +42968,7 @@
         <v>221</v>
       </c>
       <c r="J23" s="82" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
@@ -42992,7 +42999,7 @@
         <v>221</v>
       </c>
       <c r="J24" s="74" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -43023,7 +43030,7 @@
         <v>221</v>
       </c>
       <c r="J25" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
@@ -43054,7 +43061,7 @@
         <v>221</v>
       </c>
       <c r="J26" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
@@ -43085,7 +43092,7 @@
         <v>221</v>
       </c>
       <c r="J27" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
@@ -43116,7 +43123,7 @@
         <v>221</v>
       </c>
       <c r="J28" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
@@ -43141,13 +43148,13 @@
         <v>330</v>
       </c>
       <c r="H29" s="82" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="I29" s="82" t="s">
         <v>221</v>
       </c>
       <c r="J29" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
@@ -43178,7 +43185,7 @@
         <v>221</v>
       </c>
       <c r="J30" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
@@ -43209,7 +43216,7 @@
         <v>221</v>
       </c>
       <c r="J31" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
@@ -43240,7 +43247,7 @@
         <v>221</v>
       </c>
       <c r="J32" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
@@ -43271,7 +43278,7 @@
         <v>221</v>
       </c>
       <c r="J33" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
@@ -43302,7 +43309,7 @@
         <v>221</v>
       </c>
       <c r="J34" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
@@ -43333,7 +43340,7 @@
         <v>221</v>
       </c>
       <c r="J35" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
@@ -43364,7 +43371,7 @@
         <v>221</v>
       </c>
       <c r="J36" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
@@ -43395,7 +43402,7 @@
         <v>221</v>
       </c>
       <c r="J37" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
@@ -43426,7 +43433,7 @@
         <v>221</v>
       </c>
       <c r="J38" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
@@ -43457,7 +43464,7 @@
         <v>221</v>
       </c>
       <c r="J39" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
@@ -43488,7 +43495,7 @@
         <v>221</v>
       </c>
       <c r="J40" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
   </sheetData>
@@ -43585,7 +43592,7 @@
         <v>DIS</v>
       </c>
       <c r="D2" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E2" s="82" t="s">
         <v>24</v>
@@ -43597,10 +43604,10 @@
         <v>111</v>
       </c>
       <c r="H2" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I2" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J2" s="82" t="s">
         <v>102</v>
@@ -43622,7 +43629,7 @@
         <v>108</v>
       </c>
       <c r="P2" s="82" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="Q2" s="83" t="str">
         <f>SUBSTITUTE(F2, "hazr-", "")&amp;"-bp"</f>
@@ -43639,7 +43646,7 @@
         <v>DIS</v>
       </c>
       <c r="D3" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E3" s="74" t="s">
         <v>24</v>
@@ -43651,10 +43658,10 @@
         <v>111</v>
       </c>
       <c r="H3" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I3" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J3" s="74" t="s">
         <v>102</v>
@@ -43676,7 +43683,7 @@
         <v>108</v>
       </c>
       <c r="P3" s="74" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="Q3" s="84" t="str">
         <f>SUBSTITUTE(F3, "hazr-", "")&amp;"-bp"</f>
@@ -43693,7 +43700,7 @@
         <v>DIS</v>
       </c>
       <c r="D4" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E4" s="82" t="s">
         <v>24</v>
@@ -43705,10 +43712,10 @@
         <v>111</v>
       </c>
       <c r="H4" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I4" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J4" s="82" t="s">
         <v>102</v>
@@ -43730,7 +43737,7 @@
         <v>108</v>
       </c>
       <c r="P4" s="82" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="Q4" s="83" t="str">
         <f t="shared" ref="Q4:Q45" si="1">SUBSTITUTE(F4, "hazr-", "")&amp;"-bp"</f>
@@ -43747,7 +43754,7 @@
         <v>DIS</v>
       </c>
       <c r="D5" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E5" s="74" t="s">
         <v>24</v>
@@ -43759,10 +43766,10 @@
         <v>111</v>
       </c>
       <c r="H5" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I5" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J5" s="74" t="s">
         <v>102</v>
@@ -43784,7 +43791,7 @@
         <v>108</v>
       </c>
       <c r="P5" s="74" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="Q5" s="84" t="str">
         <f t="shared" si="1"/>
@@ -43801,7 +43808,7 @@
         <v>DIS</v>
       </c>
       <c r="D6" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E6" s="82" t="s">
         <v>24</v>
@@ -43813,10 +43820,10 @@
         <v>111</v>
       </c>
       <c r="H6" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I6" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J6" s="82" t="s">
         <v>102</v>
@@ -43838,7 +43845,7 @@
         <v>108</v>
       </c>
       <c r="P6" s="82" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="Q6" s="83" t="str">
         <f t="shared" si="1"/>
@@ -43855,7 +43862,7 @@
         <v>DIS</v>
       </c>
       <c r="D7" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E7" s="74" t="s">
         <v>24</v>
@@ -43867,10 +43874,10 @@
         <v>111</v>
       </c>
       <c r="H7" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I7" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J7" s="74" t="s">
         <v>102</v>
@@ -43892,7 +43899,7 @@
         <v>108</v>
       </c>
       <c r="P7" s="74" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="Q7" s="84" t="str">
         <f t="shared" si="1"/>
@@ -43909,29 +43916,29 @@
         <v>DIS</v>
       </c>
       <c r="D8" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E8" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F8" s="82" t="s">
-        <v>961</v>
+        <v>1119</v>
       </c>
       <c r="G8" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H8" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I8" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J8" s="82" t="s">
         <v>102</v>
       </c>
       <c r="K8" s="82" t="str">
         <f t="shared" si="0"/>
-        <v>t-dis-drvcltap-lb-fe</v>
+        <v>p-dis-drvcltap-lb-fe</v>
       </c>
       <c r="L8" s="82" t="s">
         <v>237</v>
@@ -43946,11 +43953,11 @@
         <v>108</v>
       </c>
       <c r="P8" s="82" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="Q8" s="83" t="str">
         <f t="shared" si="1"/>
-        <v>t-dis-drvcltap-lb-bp</v>
+        <v>p-dis-drvcltap-lb-bp</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -43963,22 +43970,22 @@
         <v>DIS</v>
       </c>
       <c r="D9" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E9" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F9" s="74" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G9" s="74" t="s">
         <v>111</v>
       </c>
       <c r="H9" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I9" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J9" s="74" t="s">
         <v>102</v>
@@ -44000,7 +44007,7 @@
         <v>108</v>
       </c>
       <c r="P9" s="74" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="Q9" s="84" t="str">
         <f t="shared" si="1"/>
@@ -44017,22 +44024,22 @@
         <v>DIS</v>
       </c>
       <c r="D10" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E10" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F10" s="82" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G10" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H10" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I10" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J10" s="82" t="s">
         <v>102</v>
@@ -44054,7 +44061,7 @@
         <v>108</v>
       </c>
       <c r="P10" s="82" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="Q10" s="83" t="str">
         <f t="shared" si="1"/>
@@ -44071,22 +44078,22 @@
         <v>DIS</v>
       </c>
       <c r="D11" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E11" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="74" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G11" s="74" t="s">
         <v>111</v>
       </c>
       <c r="H11" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I11" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J11" s="74" t="s">
         <v>102</v>
@@ -44108,7 +44115,7 @@
         <v>108</v>
       </c>
       <c r="P11" s="74" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="Q11" s="84" t="str">
         <f t="shared" si="1"/>
@@ -44125,22 +44132,22 @@
         <v>DIS</v>
       </c>
       <c r="D12" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E12" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F12" s="82" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="G12" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H12" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I12" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J12" s="82" t="s">
         <v>102</v>
@@ -44162,7 +44169,7 @@
         <v>108</v>
       </c>
       <c r="P12" s="82" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="Q12" s="83" t="str">
         <f t="shared" si="1"/>
@@ -44179,22 +44186,22 @@
         <v>DIS</v>
       </c>
       <c r="D13" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E13" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F13" s="74" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G13" s="74" t="s">
         <v>111</v>
       </c>
       <c r="H13" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I13" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J13" s="74" t="s">
         <v>102</v>
@@ -44216,7 +44223,7 @@
         <v>108</v>
       </c>
       <c r="P13" s="74" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="Q13" s="84" t="str">
         <f t="shared" si="1"/>
@@ -44233,22 +44240,22 @@
         <v>DIS</v>
       </c>
       <c r="D14" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E14" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F14" s="82" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G14" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H14" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I14" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J14" s="82" t="s">
         <v>102</v>
@@ -44270,7 +44277,7 @@
         <v>108</v>
       </c>
       <c r="P14" s="82" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="Q14" s="83" t="str">
         <f t="shared" si="1"/>
@@ -44287,22 +44294,22 @@
         <v>DIS</v>
       </c>
       <c r="D15" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E15" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F15" s="74" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="G15" s="74" t="s">
         <v>111</v>
       </c>
       <c r="H15" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I15" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J15" s="74" t="s">
         <v>102</v>
@@ -44324,7 +44331,7 @@
         <v>108</v>
       </c>
       <c r="P15" s="74" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="Q15" s="84" t="str">
         <f t="shared" si="1"/>
@@ -44341,22 +44348,22 @@
         <v>DTG</v>
       </c>
       <c r="D16" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E16" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F16" s="82" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="G16" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H16" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I16" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J16" s="82" t="s">
         <v>102</v>
@@ -44372,13 +44379,13 @@
         <v>239</v>
       </c>
       <c r="N16" s="82" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="O16" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P16" s="82" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="Q16" s="83" t="str">
         <f t="shared" si="1"/>
@@ -44395,22 +44402,22 @@
         <v>DTG</v>
       </c>
       <c r="D17" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E17" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F17" s="74" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G17" s="74" t="s">
         <v>111</v>
       </c>
       <c r="H17" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I17" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J17" s="74" t="s">
         <v>102</v>
@@ -44426,13 +44433,13 @@
         <v>239</v>
       </c>
       <c r="N17" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="O17" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P17" s="74" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="Q17" s="84" t="str">
         <f t="shared" si="1"/>
@@ -44449,22 +44456,22 @@
         <v>DTG</v>
       </c>
       <c r="D18" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E18" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F18" s="82" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="G18" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H18" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I18" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J18" s="82" t="s">
         <v>102</v>
@@ -44480,13 +44487,13 @@
         <v>239</v>
       </c>
       <c r="N18" s="82" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="O18" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P18" s="82" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="Q18" s="83" t="str">
         <f t="shared" si="1"/>
@@ -44503,22 +44510,22 @@
         <v>DTG</v>
       </c>
       <c r="D19" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E19" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F19" s="74" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G19" s="74" t="s">
         <v>111</v>
       </c>
       <c r="H19" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I19" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J19" s="74" t="s">
         <v>102</v>
@@ -44534,13 +44541,13 @@
         <v>239</v>
       </c>
       <c r="N19" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="O19" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P19" s="74" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="Q19" s="84" t="str">
         <f t="shared" si="1"/>
@@ -44557,22 +44564,22 @@
         <v>DTG</v>
       </c>
       <c r="D20" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E20" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F20" s="82" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G20" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H20" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I20" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J20" s="82" t="s">
         <v>102</v>
@@ -44588,13 +44595,13 @@
         <v>238</v>
       </c>
       <c r="N20" s="82" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="O20" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P20" s="82" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="Q20" s="83" t="str">
         <f t="shared" si="1"/>
@@ -44603,54 +44610,54 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="90"/>
-      <c r="B21" s="82" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="82" t="str" cm="1">
+      <c r="B21" s="113" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="113" t="str" cm="1">
         <f t="array" ref="C21">UPPER(INDEX(_xlfn.TEXTSPLIT($F21, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="D21" s="82" t="s">
-        <v>999</v>
-      </c>
-      <c r="E21" s="82" t="s">
+      <c r="D21" s="113" t="s">
+        <v>998</v>
+      </c>
+      <c r="E21" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="82" t="s">
-        <v>1103</v>
-      </c>
-      <c r="G21" s="82" t="s">
+      <c r="F21" s="113" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G21" s="113" t="s">
         <v>111</v>
       </c>
-      <c r="H21" s="82" t="s">
-        <v>1119</v>
-      </c>
-      <c r="I21" s="82" t="s">
+      <c r="H21" s="113" t="s">
         <v>1118</v>
       </c>
-      <c r="J21" s="82" t="s">
+      <c r="I21" s="113" t="s">
+        <v>1117</v>
+      </c>
+      <c r="J21" s="113" t="s">
         <v>102</v>
       </c>
-      <c r="K21" s="82" t="str">
+      <c r="K21" s="113" t="str">
         <f t="shared" ref="K21:K22" si="2">SUBSTITUTE(F21, "hazr-", "")&amp;"-fe"</f>
         <v>p-dtg-mq-lb02-fe</v>
       </c>
-      <c r="L21" s="82" t="s">
+      <c r="L21" s="113" t="s">
         <v>237</v>
       </c>
-      <c r="M21" s="82" t="s">
+      <c r="M21" s="113" t="s">
         <v>238</v>
       </c>
-      <c r="N21" s="82" t="s">
-        <v>1046</v>
-      </c>
-      <c r="O21" s="82" t="s">
+      <c r="N21" s="113" t="s">
+        <v>1045</v>
+      </c>
+      <c r="O21" s="113" t="s">
         <v>108</v>
       </c>
-      <c r="P21" s="82" t="s">
-        <v>1105</v>
-      </c>
-      <c r="Q21" s="83" t="str">
+      <c r="P21" s="113" t="s">
+        <v>1104</v>
+      </c>
+      <c r="Q21" s="114" t="str">
         <f t="shared" ref="Q21:Q22" si="3">SUBSTITUTE(F21, "hazr-", "")&amp;"-bp"</f>
         <v>p-dtg-mq-lb02-bp</v>
       </c>
@@ -44665,22 +44672,22 @@
         <v>DTG</v>
       </c>
       <c r="D22" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E22" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F22" s="82" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G22" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H22" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I22" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J22" s="82" t="s">
         <v>102</v>
@@ -44696,13 +44703,13 @@
         <v>238</v>
       </c>
       <c r="N22" s="82" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="O22" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P22" s="82" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="Q22" s="83" t="str">
         <f t="shared" si="3"/>
@@ -44719,22 +44726,22 @@
         <v>DTG</v>
       </c>
       <c r="D23" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E23" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F23" s="74" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="G23" s="74" t="s">
         <v>111</v>
       </c>
       <c r="H23" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I23" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J23" s="74" t="s">
         <v>102</v>
@@ -44750,13 +44757,13 @@
         <v>239</v>
       </c>
       <c r="N23" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="O23" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P23" s="74" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="Q23" s="84" t="str">
         <f t="shared" si="1"/>
@@ -44773,22 +44780,22 @@
         <v>DTG</v>
       </c>
       <c r="D24" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E24" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F24" s="82" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="G24" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H24" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I24" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J24" s="82" t="s">
         <v>102</v>
@@ -44804,13 +44811,13 @@
         <v>239</v>
       </c>
       <c r="N24" s="82" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="O24" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P24" s="82" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="Q24" s="83" t="str">
         <f t="shared" si="1"/>
@@ -44827,22 +44834,22 @@
         <v>DTG</v>
       </c>
       <c r="D25" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E25" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F25" s="74" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="G25" s="74" t="s">
         <v>111</v>
       </c>
       <c r="H25" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I25" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J25" s="74" t="s">
         <v>102</v>
@@ -44858,13 +44865,13 @@
         <v>238</v>
       </c>
       <c r="N25" s="74" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="O25" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P25" s="74" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="Q25" s="84" t="str">
         <f t="shared" si="1"/>
@@ -44881,22 +44888,22 @@
         <v>DTG</v>
       </c>
       <c r="D26" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E26" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F26" s="82" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="G26" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H26" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I26" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J26" s="82" t="s">
         <v>102</v>
@@ -44912,13 +44919,13 @@
         <v>239</v>
       </c>
       <c r="N26" s="82" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="O26" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P26" s="82" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="Q26" s="83" t="str">
         <f t="shared" si="1"/>
@@ -44935,22 +44942,22 @@
         <v>DTG</v>
       </c>
       <c r="D27" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E27" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F27" s="74" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="G27" s="74" t="s">
         <v>111</v>
       </c>
       <c r="H27" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I27" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J27" s="74" t="s">
         <v>102</v>
@@ -44966,13 +44973,13 @@
         <v>239</v>
       </c>
       <c r="N27" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="O27" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P27" s="74" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="Q27" s="84" t="str">
         <f t="shared" si="1"/>
@@ -44989,22 +44996,22 @@
         <v>DTG</v>
       </c>
       <c r="D28" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E28" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F28" s="82" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G28" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H28" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I28" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J28" s="82" t="s">
         <v>102</v>
@@ -45020,13 +45027,13 @@
         <v>239</v>
       </c>
       <c r="N28" s="82" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="O28" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P28" s="82" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="Q28" s="83" t="str">
         <f t="shared" si="1"/>
@@ -45043,22 +45050,22 @@
         <v>DTG</v>
       </c>
       <c r="D29" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E29" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F29" s="74" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="G29" s="74" t="s">
         <v>111</v>
       </c>
       <c r="H29" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I29" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J29" s="74" t="s">
         <v>102</v>
@@ -45074,13 +45081,13 @@
         <v>239</v>
       </c>
       <c r="N29" s="74" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="O29" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P29" s="74" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="Q29" s="84" t="str">
         <f t="shared" si="1"/>
@@ -45097,22 +45104,22 @@
         <v>DTG</v>
       </c>
       <c r="D30" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E30" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F30" s="82" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="G30" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H30" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I30" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J30" s="82" t="s">
         <v>102</v>
@@ -45128,13 +45135,13 @@
         <v>239</v>
       </c>
       <c r="N30" s="82" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="O30" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P30" s="82" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="Q30" s="83" t="str">
         <f t="shared" si="1"/>
@@ -45151,22 +45158,22 @@
         <v>DTG</v>
       </c>
       <c r="D31" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E31" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F31" s="74" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="G31" s="74" t="s">
         <v>111</v>
       </c>
       <c r="H31" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I31" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J31" s="74" t="s">
         <v>102</v>
@@ -45182,13 +45189,13 @@
         <v>238</v>
       </c>
       <c r="N31" s="74" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="O31" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P31" s="74" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="Q31" s="84" t="str">
         <f t="shared" si="1"/>
@@ -45205,22 +45212,22 @@
         <v>DTG</v>
       </c>
       <c r="D32" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E32" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F32" s="82" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="G32" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H32" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I32" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J32" s="82" t="s">
         <v>102</v>
@@ -45236,13 +45243,13 @@
         <v>239</v>
       </c>
       <c r="N32" s="82" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="O32" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P32" s="82" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="Q32" s="83" t="str">
         <f t="shared" si="1"/>
@@ -45259,22 +45266,22 @@
         <v>BDP</v>
       </c>
       <c r="D33" s="74" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E33" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F33" s="74" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="G33" s="74" t="s">
         <v>111</v>
       </c>
       <c r="H33" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I33" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J33" s="74" t="s">
         <v>102</v>
@@ -45290,13 +45297,13 @@
         <v>239</v>
       </c>
       <c r="N33" s="74" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="O33" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P33" s="74" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="Q33" s="84" t="str">
         <f t="shared" si="1"/>
@@ -45313,22 +45320,22 @@
         <v>BDP</v>
       </c>
       <c r="D34" s="82" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E34" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F34" s="82" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="G34" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H34" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I34" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J34" s="82" t="s">
         <v>102</v>
@@ -45344,13 +45351,13 @@
         <v>239</v>
       </c>
       <c r="N34" s="82" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="O34" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P34" s="82" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="Q34" s="83" t="str">
         <f t="shared" si="1"/>
@@ -45367,22 +45374,22 @@
         <v>IF</v>
       </c>
       <c r="D35" s="74" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E35" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F35" s="74" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="G35" s="74" t="s">
         <v>111</v>
       </c>
       <c r="H35" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I35" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J35" s="74" t="s">
         <v>102</v>
@@ -45398,13 +45405,13 @@
         <v>239</v>
       </c>
       <c r="N35" s="74" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="O35" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P35" s="74" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="Q35" s="84" t="str">
         <f t="shared" si="1"/>
@@ -45421,22 +45428,22 @@
         <v>IF</v>
       </c>
       <c r="D36" s="82" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E36" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F36" s="82" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="G36" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H36" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I36" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J36" s="82" t="s">
         <v>102</v>
@@ -45452,13 +45459,13 @@
         <v>238</v>
       </c>
       <c r="N36" s="82" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="O36" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P36" s="82" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="Q36" s="83" t="str">
         <f t="shared" si="1"/>
@@ -45475,22 +45482,22 @@
         <v>CS</v>
       </c>
       <c r="D37" s="74" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E37" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F37" s="74" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G37" s="74" t="s">
         <v>111</v>
       </c>
       <c r="H37" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I37" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J37" s="74" t="s">
         <v>102</v>
@@ -45506,13 +45513,13 @@
         <v>239</v>
       </c>
       <c r="N37" s="74" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="O37" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P37" s="74" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="Q37" s="84" t="str">
         <f t="shared" si="1"/>
@@ -45529,22 +45536,22 @@
         <v>CS</v>
       </c>
       <c r="D38" s="82" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E38" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F38" s="82" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G38" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H38" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I38" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J38" s="82" t="s">
         <v>102</v>
@@ -45560,13 +45567,13 @@
         <v>238</v>
       </c>
       <c r="N38" s="82" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="O38" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P38" s="82" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="Q38" s="83" t="str">
         <f t="shared" si="1"/>
@@ -45583,22 +45590,22 @@
         <v>CS</v>
       </c>
       <c r="D39" s="74" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E39" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F39" s="74" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="G39" s="74" t="s">
         <v>111</v>
       </c>
       <c r="H39" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I39" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J39" s="74" t="s">
         <v>102</v>
@@ -45614,13 +45621,13 @@
         <v>239</v>
       </c>
       <c r="N39" s="74" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="O39" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P39" s="74" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="Q39" s="84" t="str">
         <f t="shared" si="1"/>
@@ -45637,22 +45644,22 @@
         <v>DOIP</v>
       </c>
       <c r="D40" s="82" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E40" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F40" s="82" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="G40" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H40" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I40" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J40" s="82" t="s">
         <v>102</v>
@@ -45668,13 +45675,13 @@
         <v>239</v>
       </c>
       <c r="N40" s="82" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="O40" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P40" s="82" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="Q40" s="83" t="str">
         <f t="shared" si="1"/>
@@ -45691,22 +45698,22 @@
         <v>DOIP</v>
       </c>
       <c r="D41" s="74" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E41" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F41" s="74" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="G41" s="74" t="s">
         <v>111</v>
       </c>
       <c r="H41" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I41" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J41" s="74" t="s">
         <v>102</v>
@@ -45722,13 +45729,13 @@
         <v>239</v>
       </c>
       <c r="N41" s="74" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="O41" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P41" s="74" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="Q41" s="84" t="str">
         <f t="shared" si="1"/>
@@ -45745,22 +45752,22 @@
         <v>DOIP</v>
       </c>
       <c r="D42" s="82" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E42" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F42" s="82" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G42" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H42" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I42" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J42" s="82" t="s">
         <v>102</v>
@@ -45776,13 +45783,13 @@
         <v>239</v>
       </c>
       <c r="N42" s="82" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="O42" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P42" s="82" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="Q42" s="83" t="str">
         <f t="shared" si="1"/>
@@ -45799,22 +45806,22 @@
         <v>BDP</v>
       </c>
       <c r="D43" s="74" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E43" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F43" s="74" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="G43" s="74" t="s">
         <v>111</v>
       </c>
       <c r="H43" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I43" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J43" s="74" t="s">
         <v>102</v>
@@ -45830,13 +45837,13 @@
         <v>238</v>
       </c>
       <c r="N43" s="74" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="O43" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P43" s="74" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="Q43" s="84" t="str">
         <f t="shared" si="1"/>
@@ -45853,22 +45860,22 @@
         <v>BDP</v>
       </c>
       <c r="D44" s="82" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E44" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F44" s="82" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="G44" s="82" t="s">
         <v>111</v>
       </c>
       <c r="H44" s="82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I44" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J44" s="82" t="s">
         <v>102</v>
@@ -45884,13 +45891,13 @@
         <v>239</v>
       </c>
       <c r="N44" s="82" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="O44" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P44" s="82" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="Q44" s="83" t="str">
         <f t="shared" si="1"/>
@@ -45907,22 +45914,22 @@
         <v>BDP</v>
       </c>
       <c r="D45" s="74" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E45" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F45" s="74" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="G45" s="74" t="s">
         <v>111</v>
       </c>
       <c r="H45" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="I45" s="74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J45" s="74" t="s">
         <v>102</v>
@@ -45938,13 +45945,13 @@
         <v>239</v>
       </c>
       <c r="N45" s="74" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="O45" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P45" s="74" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="Q45" s="84" t="str">
         <f t="shared" si="1"/>
@@ -46034,10 +46041,10 @@
         <v>DIS</v>
       </c>
       <c r="D2" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E2" s="82" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F2" s="51" t="str">
         <f t="shared" ref="F2:F52" si="0">SUBSTITUTE(E2, "hazr-", "")&amp;"-pb"&amp;H2</f>
@@ -46067,10 +46074,10 @@
         <v>DIS</v>
       </c>
       <c r="D3" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E3" s="74" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F3" s="50" t="str">
         <f t="shared" si="0"/>
@@ -46100,10 +46107,10 @@
         <v>DIS</v>
       </c>
       <c r="D4" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E4" s="82" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F4" s="51" t="str">
         <f t="shared" si="0"/>
@@ -46133,7 +46140,7 @@
         <v>DIS</v>
       </c>
       <c r="D5" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E5" s="74" t="s">
         <v>958</v>
@@ -46166,7 +46173,7 @@
         <v>DIS</v>
       </c>
       <c r="D6" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E6" s="74" t="s">
         <v>958</v>
@@ -46199,7 +46206,7 @@
         <v>DIS</v>
       </c>
       <c r="D7" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E7" s="74" t="s">
         <v>958</v>
@@ -46232,10 +46239,10 @@
         <v>DIS</v>
       </c>
       <c r="D8" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E8" s="82" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F8" s="51" t="str">
         <f t="shared" si="0"/>
@@ -46265,7 +46272,7 @@
         <v>DIS</v>
       </c>
       <c r="D9" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E9" s="74" t="s">
         <v>960</v>
@@ -46298,7 +46305,7 @@
         <v>DIS</v>
       </c>
       <c r="D10" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E10" s="82" t="s">
         <v>224</v>
@@ -46331,10 +46338,10 @@
         <v>DIS</v>
       </c>
       <c r="D11" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E11" s="74" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F11" s="50" t="str">
         <f t="shared" si="0"/>
@@ -46364,10 +46371,10 @@
         <v>DIS</v>
       </c>
       <c r="D12" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E12" s="82" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="F12" s="51" t="str">
         <f t="shared" si="0"/>
@@ -46397,10 +46404,10 @@
         <v>DIS</v>
       </c>
       <c r="D13" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E13" s="74" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F13" s="50" t="str">
         <f t="shared" si="0"/>
@@ -46430,10 +46437,10 @@
         <v>DIS</v>
       </c>
       <c r="D14" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E14" s="74" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F14" s="50" t="str">
         <f t="shared" si="0"/>
@@ -46463,10 +46470,10 @@
         <v>DIS</v>
       </c>
       <c r="D15" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E15" s="82" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="F15" s="51" t="str">
         <f t="shared" si="0"/>
@@ -46496,10 +46503,10 @@
         <v>DIS</v>
       </c>
       <c r="D16" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E16" s="74" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F16" s="50" t="str">
         <f t="shared" si="0"/>
@@ -46529,10 +46536,10 @@
         <v>DIS</v>
       </c>
       <c r="D17" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E17" s="82" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F17" s="51" t="str">
         <f t="shared" si="0"/>
@@ -46562,10 +46569,10 @@
         <v>DIS</v>
       </c>
       <c r="D18" s="82" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E18" s="82" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F18" s="51" t="str">
         <f t="shared" ref="F18" si="1">SUBSTITUTE(E18, "hazr-", "")&amp;"-pb"&amp;H18</f>
@@ -46595,10 +46602,10 @@
         <v>DIS</v>
       </c>
       <c r="D19" s="74" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E19" s="74" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F19" s="50" t="str">
         <f t="shared" si="0"/>
@@ -46628,10 +46635,10 @@
         <v>DTG</v>
       </c>
       <c r="D20" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E20" s="82" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="F20" s="51" t="str">
         <f t="shared" si="0"/>
@@ -46661,10 +46668,10 @@
         <v>DTG</v>
       </c>
       <c r="D21" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E21" s="74" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F21" s="50" t="str">
         <f t="shared" si="0"/>
@@ -46694,10 +46701,10 @@
         <v>DTG</v>
       </c>
       <c r="D22" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E22" s="74" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F22" s="50" t="str">
         <f t="shared" ref="F22" si="2">SUBSTITUTE(E22, "hazr-", "")&amp;"-pb"&amp;H22</f>
@@ -46727,10 +46734,10 @@
         <v>DTG</v>
       </c>
       <c r="D23" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E23" s="82" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F23" s="51" t="str">
         <f t="shared" si="0"/>
@@ -46760,10 +46767,10 @@
         <v>DTG</v>
       </c>
       <c r="D24" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E24" s="82" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F24" s="51" t="str">
         <f t="shared" ref="F24" si="3">SUBSTITUTE(E24, "hazr-", "")&amp;"-pb"&amp;H24</f>
@@ -46793,10 +46800,10 @@
         <v>DTG</v>
       </c>
       <c r="D25" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E25" s="74" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F25" s="50" t="str">
         <f t="shared" si="0"/>
@@ -46826,10 +46833,10 @@
         <v>DTG</v>
       </c>
       <c r="D26" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E26" s="74" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F26" s="50" t="str">
         <f t="shared" ref="F26" si="4">SUBSTITUTE(E26, "hazr-", "")&amp;"-pb"&amp;H26</f>
@@ -46859,10 +46866,10 @@
         <v>DTG</v>
       </c>
       <c r="D27" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E27" s="82" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F27" s="51" t="str">
         <f t="shared" si="0"/>
@@ -46892,10 +46899,10 @@
         <v>DTG</v>
       </c>
       <c r="D28" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E28" s="82" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F28" s="51" t="str">
         <f t="shared" ref="F28:F29" si="5">SUBSTITUTE(E28, "hazr-", "")&amp;"-pb"&amp;H28</f>
@@ -46925,10 +46932,10 @@
         <v>DTG</v>
       </c>
       <c r="D29" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E29" s="74" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F29" s="50" t="str">
         <f t="shared" si="5"/>
@@ -46958,10 +46965,10 @@
         <v>DTG</v>
       </c>
       <c r="D30" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E30" s="74" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F30" s="50" t="str">
         <f t="shared" ref="F30:F32" si="6">SUBSTITUTE(E30, "hazr-", "")&amp;"-pb"&amp;H30</f>
@@ -46991,10 +46998,10 @@
         <v>DTG</v>
       </c>
       <c r="D31" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E31" s="82" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="F31" s="51" t="str">
         <f t="shared" si="6"/>
@@ -47024,10 +47031,10 @@
         <v>DTG</v>
       </c>
       <c r="D32" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E32" s="82" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="F32" s="51" t="str">
         <f t="shared" si="6"/>
@@ -47057,10 +47064,10 @@
         <v>DTG</v>
       </c>
       <c r="D33" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E33" s="74" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F33" s="50" t="str">
         <f t="shared" si="0"/>
@@ -47090,10 +47097,10 @@
         <v>DTG</v>
       </c>
       <c r="D34" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E34" s="82" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="F34" s="51" t="str">
         <f t="shared" si="0"/>
@@ -47123,10 +47130,10 @@
         <v>DTG</v>
       </c>
       <c r="D35" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E35" s="82" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="F35" s="51" t="str">
         <f t="shared" ref="F35" si="7">SUBSTITUTE(E35, "hazr-", "")&amp;"-pb"&amp;H35</f>
@@ -47156,10 +47163,10 @@
         <v>DTG</v>
       </c>
       <c r="D36" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E36" s="74" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="F36" s="50" t="str">
         <f t="shared" si="0"/>
@@ -47189,10 +47196,10 @@
         <v>DTG</v>
       </c>
       <c r="D37" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E37" s="74" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="F37" s="50" t="str">
         <f t="shared" ref="F37" si="8">SUBSTITUTE(E37, "hazr-", "")&amp;"-pb"&amp;H37</f>
@@ -47222,10 +47229,10 @@
         <v>DTG</v>
       </c>
       <c r="D38" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E38" s="82" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="F38" s="51" t="str">
         <f t="shared" si="0"/>
@@ -47255,10 +47262,10 @@
         <v>DTG</v>
       </c>
       <c r="D39" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E39" s="74" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F39" s="50" t="str">
         <f t="shared" si="0"/>
@@ -47288,10 +47295,10 @@
         <v>DTG</v>
       </c>
       <c r="D40" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E40" s="74" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F40" s="50" t="str">
         <f t="shared" ref="F40" si="9">SUBSTITUTE(E40, "hazr-", "")&amp;"-pb"&amp;H40</f>
@@ -47321,10 +47328,10 @@
         <v>DTG</v>
       </c>
       <c r="D41" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E41" s="82" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F41" s="51" t="str">
         <f t="shared" si="0"/>
@@ -47354,10 +47361,10 @@
         <v>DTG</v>
       </c>
       <c r="D42" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E42" s="82" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F42" s="51" t="str">
         <f t="shared" ref="F42:F45" si="10">SUBSTITUTE(E42, "hazr-", "")&amp;"-pb"&amp;H42</f>
@@ -47387,10 +47394,10 @@
         <v>DTG</v>
       </c>
       <c r="D43" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E43" s="82" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F43" s="51" t="str">
         <f t="shared" si="10"/>
@@ -47420,10 +47427,10 @@
         <v>DTG</v>
       </c>
       <c r="D44" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E44" s="82" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F44" s="51" t="str">
         <f t="shared" si="10"/>
@@ -47453,10 +47460,10 @@
         <v>DTG</v>
       </c>
       <c r="D45" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E45" s="82" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F45" s="51" t="str">
         <f t="shared" si="10"/>
@@ -47486,10 +47493,10 @@
         <v>DTG</v>
       </c>
       <c r="D46" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E46" s="74" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="F46" s="50" t="str">
         <f t="shared" si="0"/>
@@ -47519,10 +47526,10 @@
         <v>DTG</v>
       </c>
       <c r="D47" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E47" s="82" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F47" s="51" t="str">
         <f t="shared" si="0"/>
@@ -47552,10 +47559,10 @@
         <v>DTG</v>
       </c>
       <c r="D48" s="74" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E48" s="74" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F48" s="50" t="str">
         <f t="shared" si="0"/>
@@ -47585,10 +47592,10 @@
         <v>DTG</v>
       </c>
       <c r="D49" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E49" s="82" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F49" s="51" t="str">
         <f t="shared" si="0"/>
@@ -47618,10 +47625,10 @@
         <v>BDP</v>
       </c>
       <c r="D50" s="74" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E50" s="74" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F50" s="50" t="str">
         <f t="shared" si="0"/>
@@ -47651,10 +47658,10 @@
         <v>BDP</v>
       </c>
       <c r="D51" s="82" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E51" s="82" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F51" s="51" t="str">
         <f t="shared" si="0"/>
@@ -47684,10 +47691,10 @@
         <v>IF</v>
       </c>
       <c r="D52" s="74" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E52" s="74" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F52" s="50" t="str">
         <f t="shared" si="0"/>
@@ -47717,10 +47724,10 @@
         <v>IF</v>
       </c>
       <c r="D53" s="74" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E53" s="74" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F53" s="50" t="str">
         <f t="shared" ref="F53:F54" si="11">SUBSTITUTE(E53, "hazr-", "")&amp;"-pb"&amp;H53</f>
@@ -47750,10 +47757,10 @@
         <v>IF</v>
       </c>
       <c r="D54" s="74" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E54" s="74" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F54" s="50" t="str">
         <f t="shared" si="11"/>
@@ -47783,10 +47790,10 @@
         <v>IF</v>
       </c>
       <c r="D55" s="82" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E55" s="82" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="F55" s="51" t="str">
         <f t="shared" ref="F55:F66" si="12">SUBSTITUTE(E55, "hazr-", "")&amp;"-pb"&amp;H55</f>
@@ -47816,17 +47823,17 @@
         <v>IF</v>
       </c>
       <c r="D56" s="82" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E56" s="82" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="F56" s="51" t="str">
         <f t="shared" ref="F56" si="13">SUBSTITUTE(E56, "hazr-", "")&amp;"-pb"&amp;H56</f>
         <v>p-if-proxy-lb-pb8080</v>
       </c>
       <c r="G56" s="82" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H56" s="82">
         <v>8080</v>
@@ -47837,14 +47844,14 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B57" s="102" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C57" s="102"/>
       <c r="D57" s="102" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E57" s="102" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="F57" s="104" t="str">
         <f t="shared" si="12"/>
@@ -47854,7 +47861,7 @@
         <v>57</v>
       </c>
       <c r="H57" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="I57" s="102"/>
       <c r="J57" s="102">
@@ -47866,14 +47873,14 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B58" s="102" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C58" s="102"/>
       <c r="D58" s="102" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E58" s="102" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="F58" s="104" t="str">
         <f t="shared" si="12"/>
@@ -47883,7 +47890,7 @@
         <v>57</v>
       </c>
       <c r="H58" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="I58" s="102"/>
       <c r="J58" s="102">
@@ -47895,14 +47902,14 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B59" s="102" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C59" s="102"/>
       <c r="D59" s="102" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E59" s="102" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F59" s="104" t="str">
         <f t="shared" si="12"/>
@@ -47912,7 +47919,7 @@
         <v>57</v>
       </c>
       <c r="H59" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="I59" s="102"/>
       <c r="J59" s="102">
@@ -47924,14 +47931,14 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B60" s="102" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C60" s="102"/>
       <c r="D60" s="102" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E60" s="102" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="F60" s="104" t="str">
         <f t="shared" si="12"/>
@@ -47941,7 +47948,7 @@
         <v>57</v>
       </c>
       <c r="H60" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="I60" s="102"/>
       <c r="J60" s="102">
@@ -47953,14 +47960,14 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B61" s="102" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C61" s="102"/>
       <c r="D61" s="102" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E61" s="102" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F61" s="104" t="str">
         <f t="shared" si="12"/>
@@ -47970,7 +47977,7 @@
         <v>57</v>
       </c>
       <c r="H61" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="I61" s="102"/>
       <c r="J61" s="102">
@@ -47982,14 +47989,14 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B62" s="102" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C62" s="102"/>
       <c r="D62" s="102" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E62" s="102" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="F62" s="104" t="str">
         <f t="shared" si="12"/>
@@ -47999,7 +48006,7 @@
         <v>57</v>
       </c>
       <c r="H62" s="102" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="I62" s="102"/>
       <c r="J62" s="102">
@@ -48019,10 +48026,10 @@
         <v>BDP</v>
       </c>
       <c r="D63" s="74" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E63" s="74" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F63" s="50" t="str">
         <f t="shared" si="12"/>
@@ -48052,10 +48059,10 @@
         <v>BDP</v>
       </c>
       <c r="D64" s="74" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E64" s="74" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F64" s="50" t="str">
         <f t="shared" ref="F64" si="14">SUBSTITUTE(E64, "hazr-", "")&amp;"-pb"&amp;H64</f>
@@ -48081,10 +48088,10 @@
         <v>BDP</v>
       </c>
       <c r="D65" s="82" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E65" s="82" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="F65" s="51" t="str">
         <f t="shared" si="12"/>
@@ -48114,10 +48121,10 @@
         <v>BDP</v>
       </c>
       <c r="D66" s="74" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E66" s="74" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="F66" s="50" t="str">
         <f t="shared" si="12"/>
@@ -48144,12 +48151,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -48297,15 +48301,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -48329,17 +48344,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>